--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AY112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3226,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137876</v>
+        <v>129125929</v>
       </c>
       <c r="B27" t="n">
-        <v>80167</v>
+        <v>97522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548475</v>
+        <v>548372</v>
       </c>
       <c r="R27" t="n">
-        <v>7015265</v>
+        <v>7014829</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137749</v>
+        <v>129137876</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>80167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548618</v>
+        <v>548475</v>
       </c>
       <c r="R28" t="n">
-        <v>7015211</v>
+        <v>7015265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3394,11 +3394,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3425,10 +3420,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137810</v>
+        <v>129137749</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,21 +3431,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3460,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548538</v>
+        <v>548618</v>
       </c>
       <c r="R29" t="n">
-        <v>7015259</v>
+        <v>7015211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3496,6 +3491,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3522,7 +3522,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137806</v>
+        <v>129137810</v>
       </c>
       <c r="B30" t="n">
         <v>79034</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548632</v>
+        <v>548538</v>
       </c>
       <c r="R30" t="n">
-        <v>7015246</v>
+        <v>7015259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3619,32 +3619,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129125929</v>
+        <v>129137806</v>
       </c>
       <c r="B31" t="n">
-        <v>97522</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548372</v>
+        <v>548632</v>
       </c>
       <c r="R31" t="n">
-        <v>7014829</v>
+        <v>7015246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129126001</v>
+        <v>129137905</v>
       </c>
       <c r="B53" t="n">
         <v>79034</v>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548299</v>
+        <v>548618</v>
       </c>
       <c r="R53" t="n">
-        <v>7014876</v>
+        <v>7015116</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5909,32 +5909,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137905</v>
+        <v>129137877</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>80167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548618</v>
+        <v>548334</v>
       </c>
       <c r="R54" t="n">
-        <v>7015116</v>
+        <v>7015001</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6006,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137877</v>
+        <v>129137739</v>
       </c>
       <c r="B55" t="n">
-        <v>80167</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548334</v>
+        <v>548460</v>
       </c>
       <c r="R55" t="n">
-        <v>7015001</v>
+        <v>7014976</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6077,6 +6077,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6103,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137739</v>
+        <v>129137860</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,21 +6119,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6138,10 +6143,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548460</v>
+        <v>548481</v>
       </c>
       <c r="R56" t="n">
-        <v>7014976</v>
+        <v>7015172</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6178,7 +6183,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6205,7 +6210,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137860</v>
+        <v>129137859</v>
       </c>
       <c r="B57" t="n">
         <v>57883</v>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548481</v>
+        <v>548434</v>
       </c>
       <c r="R57" t="n">
-        <v>7015172</v>
+        <v>7014792</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6307,10 +6312,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137859</v>
+        <v>129137845</v>
       </c>
       <c r="B58" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6318,21 +6323,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6342,10 +6347,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548434</v>
+        <v>548531</v>
       </c>
       <c r="R58" t="n">
-        <v>7014792</v>
+        <v>7014817</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6382,7 +6387,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6409,10 +6414,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137845</v>
+        <v>129137882</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6420,21 +6425,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6444,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548531</v>
+        <v>548510</v>
       </c>
       <c r="R59" t="n">
-        <v>7014817</v>
+        <v>7015191</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6480,11 +6485,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137882</v>
+        <v>129137746</v>
       </c>
       <c r="B60" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548510</v>
+        <v>548355</v>
       </c>
       <c r="R60" t="n">
-        <v>7015191</v>
+        <v>7014874</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6582,6 +6582,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6608,10 +6613,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137746</v>
+        <v>129126001</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,21 +6624,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6648,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548355</v>
+        <v>548299</v>
       </c>
       <c r="R61" t="n">
-        <v>7014874</v>
+        <v>7014876</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6679,11 +6684,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8690,32 +8690,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137898</v>
+        <v>129137745</v>
       </c>
       <c r="B82" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548460</v>
+        <v>548373</v>
       </c>
       <c r="R82" t="n">
-        <v>7015208</v>
+        <v>7014966</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>140 ex</t>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8792,32 +8792,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137745</v>
+        <v>129137900</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>105714</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548373</v>
+        <v>548451</v>
       </c>
       <c r="R83" t="n">
-        <v>7014966</v>
+        <v>7014746</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8863,11 +8863,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8894,32 +8889,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137900</v>
+        <v>129137805</v>
       </c>
       <c r="B84" t="n">
-        <v>105714</v>
+        <v>79034</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8929,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548451</v>
+        <v>548613</v>
       </c>
       <c r="R84" t="n">
-        <v>7014746</v>
+        <v>7015186</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8991,32 +8986,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137805</v>
+        <v>129137871</v>
       </c>
       <c r="B85" t="n">
-        <v>79034</v>
+        <v>97528</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9026,10 +9021,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548613</v>
+        <v>548457</v>
       </c>
       <c r="R85" t="n">
-        <v>7015186</v>
+        <v>7014764</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9088,7 +9083,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137871</v>
+        <v>129137872</v>
       </c>
       <c r="B86" t="n">
         <v>97528</v>
@@ -9123,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548457</v>
+        <v>548477</v>
       </c>
       <c r="R86" t="n">
-        <v>7014764</v>
+        <v>7015144</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9185,32 +9180,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137872</v>
+        <v>129137889</v>
       </c>
       <c r="B87" t="n">
-        <v>97528</v>
+        <v>98651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9220,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548477</v>
+        <v>548440</v>
       </c>
       <c r="R87" t="n">
-        <v>7015144</v>
+        <v>7014752</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9256,6 +9251,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137889</v>
+        <v>129137796</v>
       </c>
       <c r="B88" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548440</v>
+        <v>548559</v>
       </c>
       <c r="R88" t="n">
-        <v>7014752</v>
+        <v>7014776</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,11 +9353,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9384,7 +9379,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137796</v>
+        <v>129137816</v>
       </c>
       <c r="B89" t="n">
         <v>79034</v>
@@ -9419,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548559</v>
+        <v>548400</v>
       </c>
       <c r="R89" t="n">
-        <v>7014776</v>
+        <v>7014970</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9481,32 +9476,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137816</v>
+        <v>129137781</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>98651</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9511,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548400</v>
+        <v>548433</v>
       </c>
       <c r="R90" t="n">
-        <v>7014970</v>
+        <v>7014771</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9552,6 +9547,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9578,32 +9578,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137781</v>
+        <v>129137901</v>
       </c>
       <c r="B91" t="n">
-        <v>98651</v>
+        <v>105714</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548433</v>
+        <v>548281</v>
       </c>
       <c r="R91" t="n">
-        <v>7014771</v>
+        <v>7015128</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9649,11 +9649,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9680,7 +9675,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137901</v>
+        <v>129137790</v>
       </c>
       <c r="B92" t="n">
         <v>105714</v>
@@ -9715,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548281</v>
+        <v>548558</v>
       </c>
       <c r="R92" t="n">
-        <v>7015128</v>
+        <v>7014771</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9777,10 +9772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137790</v>
+        <v>129137778</v>
       </c>
       <c r="B93" t="n">
-        <v>105714</v>
+        <v>57827</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9788,21 +9783,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>103031</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9812,10 +9807,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548558</v>
+        <v>548706</v>
       </c>
       <c r="R93" t="n">
-        <v>7014771</v>
+        <v>7014864</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9848,6 +9843,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9874,10 +9874,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137778</v>
+        <v>129137764</v>
       </c>
       <c r="B94" t="n">
-        <v>57827</v>
+        <v>97528</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9885,21 +9885,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548706</v>
+        <v>548590</v>
       </c>
       <c r="R94" t="n">
-        <v>7014864</v>
+        <v>7015157</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9945,11 +9945,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9976,32 +9971,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137764</v>
+        <v>129137878</v>
       </c>
       <c r="B95" t="n">
-        <v>97528</v>
+        <v>80139</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10011,10 +10006,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548590</v>
+        <v>548705</v>
       </c>
       <c r="R95" t="n">
-        <v>7015157</v>
+        <v>7014750</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10073,10 +10068,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137878</v>
+        <v>129137908</v>
       </c>
       <c r="B96" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10084,21 +10079,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10108,10 +10103,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548705</v>
+        <v>548306</v>
       </c>
       <c r="R96" t="n">
-        <v>7014750</v>
+        <v>7015082</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10170,27 +10165,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>80174</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10205,10 +10200,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R97" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10267,10 +10262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137911</v>
+        <v>129137874</v>
       </c>
       <c r="B98" t="n">
-        <v>80174</v>
+        <v>97528</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10278,21 +10273,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10302,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548512</v>
+        <v>548348</v>
       </c>
       <c r="R98" t="n">
-        <v>7015192</v>
+        <v>7014988</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10364,32 +10359,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137874</v>
+        <v>129137788</v>
       </c>
       <c r="B99" t="n">
-        <v>97528</v>
+        <v>98651</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10399,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548348</v>
+        <v>548605</v>
       </c>
       <c r="R99" t="n">
-        <v>7014988</v>
+        <v>7014687</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10435,6 +10430,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10461,32 +10461,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137788</v>
+        <v>129137903</v>
       </c>
       <c r="B100" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10496,10 +10496,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548605</v>
+        <v>548633</v>
       </c>
       <c r="R100" t="n">
-        <v>7014687</v>
+        <v>7015045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10532,11 +10532,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10563,10 +10558,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137903</v>
+        <v>129137848</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10574,21 +10569,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10598,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548633</v>
+        <v>548598</v>
       </c>
       <c r="R101" t="n">
-        <v>7015045</v>
+        <v>7015227</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10634,6 +10629,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10660,32 +10660,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137848</v>
+        <v>129137912</v>
       </c>
       <c r="B102" t="n">
-        <v>57723</v>
+        <v>96770</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10695,10 +10695,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548598</v>
+        <v>548604</v>
       </c>
       <c r="R102" t="n">
-        <v>7015227</v>
+        <v>7015234</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10731,11 +10731,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10762,32 +10757,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137912</v>
+        <v>129137863</v>
       </c>
       <c r="B103" t="n">
-        <v>96770</v>
+        <v>80140</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2869</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10797,10 +10792,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548604</v>
+        <v>548702</v>
       </c>
       <c r="R103" t="n">
-        <v>7015234</v>
+        <v>7014752</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10859,10 +10854,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137863</v>
+        <v>129137840</v>
       </c>
       <c r="B104" t="n">
-        <v>80140</v>
+        <v>91520</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10870,21 +10865,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10894,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548702</v>
+        <v>548660</v>
       </c>
       <c r="R104" t="n">
-        <v>7014752</v>
+        <v>7014820</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10956,10 +10951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137840</v>
+        <v>129137753</v>
       </c>
       <c r="B105" t="n">
-        <v>91520</v>
+        <v>91805</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10967,21 +10962,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10991,10 +10986,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548660</v>
+        <v>548681</v>
       </c>
       <c r="R105" t="n">
-        <v>7014820</v>
+        <v>7015193</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11053,32 +11048,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137753</v>
+        <v>129137758</v>
       </c>
       <c r="B106" t="n">
-        <v>91805</v>
+        <v>97522</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11088,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548681</v>
+        <v>548629</v>
       </c>
       <c r="R106" t="n">
-        <v>7015193</v>
+        <v>7014777</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11150,32 +11145,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137758</v>
+        <v>129137883</v>
       </c>
       <c r="B107" t="n">
-        <v>97522</v>
+        <v>80139</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11185,10 +11180,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548629</v>
+        <v>548499</v>
       </c>
       <c r="R107" t="n">
-        <v>7014777</v>
+        <v>7015176</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11247,32 +11242,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137883</v>
+        <v>129137873</v>
       </c>
       <c r="B108" t="n">
-        <v>80139</v>
+        <v>97528</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11282,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548499</v>
+        <v>548291</v>
       </c>
       <c r="R108" t="n">
-        <v>7015176</v>
+        <v>7015110</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11344,32 +11339,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137873</v>
+        <v>129137847</v>
       </c>
       <c r="B109" t="n">
-        <v>97528</v>
+        <v>57723</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11379,10 +11374,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548291</v>
+        <v>548490</v>
       </c>
       <c r="R109" t="n">
-        <v>7015110</v>
+        <v>7014739</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11415,6 +11410,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11441,7 +11441,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137847</v>
+        <v>129137844</v>
       </c>
       <c r="B110" t="n">
         <v>57723</v>
@@ -11476,10 +11476,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548490</v>
+        <v>548672</v>
       </c>
       <c r="R110" t="n">
-        <v>7014739</v>
+        <v>7014893</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11543,32 +11543,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137844</v>
+        <v>129137768</v>
       </c>
       <c r="B111" t="n">
-        <v>57723</v>
+        <v>80167</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11578,10 +11578,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548672</v>
+        <v>548723</v>
       </c>
       <c r="R111" t="n">
-        <v>7014893</v>
+        <v>7014940</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11614,11 +11614,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11645,10 +11640,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137768</v>
+        <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>80167</v>
+        <v>97522</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11656,21 +11651,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11680,10 +11675,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548723</v>
+        <v>548366</v>
       </c>
       <c r="R112" t="n">
-        <v>7014940</v>
+        <v>7015047</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11739,103 +11734,6 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>129137761</v>
-      </c>
-      <c r="B113" t="n">
-        <v>97522</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Bäckedalen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q113" t="n">
-        <v>548366</v>
-      </c>
-      <c r="R113" t="n">
-        <v>7015047</v>
-      </c>
-      <c r="S113" t="n">
-        <v>10</v>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AD113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT113" t="inlineStr"/>
-      <c r="AW113" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1246,32 +1246,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137870</v>
+        <v>129137817</v>
       </c>
       <c r="B7" t="n">
-        <v>97528</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548358</v>
+        <v>548367</v>
       </c>
       <c r="R7" t="n">
-        <v>7014777</v>
+        <v>7014944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137817</v>
+        <v>129137797</v>
       </c>
       <c r="B8" t="n">
         <v>79034</v>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548367</v>
+        <v>548657</v>
       </c>
       <c r="R8" t="n">
-        <v>7014944</v>
+        <v>7014768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137740</v>
+        <v>129137815</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548618</v>
+        <v>548398</v>
       </c>
       <c r="R9" t="n">
-        <v>7015211</v>
+        <v>7015004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137797</v>
+        <v>129137740</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548657</v>
+        <v>548618</v>
       </c>
       <c r="R10" t="n">
-        <v>7014768</v>
+        <v>7015211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137787</v>
+        <v>129137870</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>97533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548366</v>
+        <v>548358</v>
       </c>
       <c r="R11" t="n">
-        <v>7014942</v>
+        <v>7014777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137815</v>
+        <v>129137787</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548398</v>
+        <v>548366</v>
       </c>
       <c r="R12" t="n">
-        <v>7015004</v>
+        <v>7014942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R14" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137804</v>
+        <v>129137794</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548550</v>
+        <v>548459</v>
       </c>
       <c r="R15" t="n">
-        <v>7015142</v>
+        <v>7015186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2440,32 +2440,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137869</v>
+        <v>129137802</v>
       </c>
       <c r="B19" t="n">
-        <v>97528</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548335</v>
+        <v>548499</v>
       </c>
       <c r="R19" t="n">
-        <v>7014782</v>
+        <v>7014902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,32 +2537,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137802</v>
+        <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>97533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548499</v>
+        <v>548335</v>
       </c>
       <c r="R20" t="n">
-        <v>7014902</v>
+        <v>7014782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,32 +2731,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137750</v>
+        <v>129137771</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>80167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548514</v>
+        <v>548360</v>
       </c>
       <c r="R22" t="n">
-        <v>7015227</v>
+        <v>7014942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,11 +2802,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2833,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137771</v>
+        <v>129137819</v>
       </c>
       <c r="B23" t="n">
-        <v>80167</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548360</v>
+        <v>548318</v>
       </c>
       <c r="R23" t="n">
-        <v>7014942</v>
+        <v>7014904</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137744</v>
+        <v>129137862</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548511</v>
+        <v>548497</v>
       </c>
       <c r="R24" t="n">
-        <v>7015241</v>
+        <v>7015181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3001,11 +2996,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3032,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137819</v>
+        <v>129137744</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3043,21 +3033,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3067,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548318</v>
+        <v>548511</v>
       </c>
       <c r="R25" t="n">
-        <v>7014904</v>
+        <v>7015241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,6 +3093,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3129,32 +3124,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137862</v>
+        <v>129137750</v>
       </c>
       <c r="B26" t="n">
-        <v>80168</v>
+        <v>57883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3164,10 +3159,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548497</v>
+        <v>548514</v>
       </c>
       <c r="R26" t="n">
-        <v>7015181</v>
+        <v>7015227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,6 +3195,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3226,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129125929</v>
+        <v>129137876</v>
       </c>
       <c r="B27" t="n">
-        <v>97522</v>
+        <v>80167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548372</v>
+        <v>548475</v>
       </c>
       <c r="R27" t="n">
-        <v>7014829</v>
+        <v>7015265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B28" t="n">
-        <v>80167</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R28" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137749</v>
+        <v>129137806</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548618</v>
+        <v>548632</v>
       </c>
       <c r="R29" t="n">
-        <v>7015211</v>
+        <v>7015246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3491,11 +3491,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3522,10 +3517,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137810</v>
+        <v>129137749</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,21 +3528,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3557,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548538</v>
+        <v>548618</v>
       </c>
       <c r="R30" t="n">
-        <v>7015259</v>
+        <v>7015211</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3593,6 +3588,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3619,32 +3619,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137806</v>
+        <v>129125929</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>97527</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548632</v>
+        <v>548372</v>
       </c>
       <c r="R31" t="n">
-        <v>7015246</v>
+        <v>7014829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,49 +3716,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129126213</v>
+        <v>129137800</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548265</v>
+        <v>548708</v>
       </c>
       <c r="R32" t="n">
-        <v>7014876</v>
+        <v>7014937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,6 +3787,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137789</v>
+        <v>129137821</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3852,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548461</v>
+        <v>548369</v>
       </c>
       <c r="R33" t="n">
-        <v>7015210</v>
+        <v>7014853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3888,11 +3889,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,32 +3915,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137800</v>
+        <v>129137789</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3954,10 +3950,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548708</v>
+        <v>548461</v>
       </c>
       <c r="R34" t="n">
-        <v>7014937</v>
+        <v>7015210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3994,7 +3990,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,32 +4017,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4052,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R35" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,6 +4088,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4118,45 +4119,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137849</v>
+        <v>129126213</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548629</v>
+        <v>548265</v>
       </c>
       <c r="R36" t="n">
-        <v>7015247</v>
+        <v>7014876</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4189,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4220,32 +4220,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137896</v>
+        <v>129137849</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548260</v>
+        <v>548629</v>
       </c>
       <c r="R37" t="n">
-        <v>7014898</v>
+        <v>7015247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137895</v>
+        <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548277</v>
+        <v>548395</v>
       </c>
       <c r="R40" t="n">
-        <v>7015126</v>
+        <v>7015086</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4720,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137812</v>
+        <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548395</v>
+        <v>548277</v>
       </c>
       <c r="R42" t="n">
-        <v>7015086</v>
+        <v>7015126</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4786,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4914,10 +4914,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137843</v>
+        <v>129137814</v>
       </c>
       <c r="B44" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548488</v>
+        <v>548376</v>
       </c>
       <c r="R44" t="n">
-        <v>7015296</v>
+        <v>7015053</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137909</v>
+        <v>129137822</v>
       </c>
       <c r="B45" t="n">
-        <v>82897</v>
+        <v>57644</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548610</v>
+        <v>548346</v>
       </c>
       <c r="R45" t="n">
-        <v>7015229</v>
+        <v>7015026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137814</v>
+        <v>129137843</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548376</v>
+        <v>548488</v>
       </c>
       <c r="R46" t="n">
-        <v>7015053</v>
+        <v>7015296</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5205,32 +5205,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137783</v>
+        <v>129137909</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>82897</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548595</v>
+        <v>548610</v>
       </c>
       <c r="R47" t="n">
-        <v>7015162</v>
+        <v>7015229</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,11 +5276,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5307,10 +5302,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137891</v>
+        <v>129137783</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,10 +5337,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548627</v>
+        <v>548595</v>
       </c>
       <c r="R48" t="n">
-        <v>7015253</v>
+        <v>7015162</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5382,7 +5377,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5409,32 +5404,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137822</v>
+        <v>129137891</v>
       </c>
       <c r="B49" t="n">
-        <v>57644</v>
+        <v>98656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5444,10 +5439,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548346</v>
+        <v>548627</v>
       </c>
       <c r="R49" t="n">
-        <v>7015026</v>
+        <v>7015253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5480,6 +5475,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5509,7 +5509,7 @@
         <v>129137792</v>
       </c>
       <c r="B50" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>129137786</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>129137766</v>
       </c>
       <c r="B52" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137739</v>
+        <v>129126001</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548460</v>
+        <v>548299</v>
       </c>
       <c r="R55" t="n">
-        <v>7014976</v>
+        <v>7014876</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6077,11 +6077,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6108,10 +6103,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137860</v>
+        <v>129137882</v>
       </c>
       <c r="B56" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6119,21 +6114,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6143,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548481</v>
+        <v>548510</v>
       </c>
       <c r="R56" t="n">
-        <v>7015172</v>
+        <v>7015191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6179,11 +6174,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6210,10 +6200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137859</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6221,21 +6211,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6245,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548434</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7014792</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6285,7 +6275,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6414,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137882</v>
+        <v>129137746</v>
       </c>
       <c r="B59" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6425,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6449,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548510</v>
+        <v>548355</v>
       </c>
       <c r="R59" t="n">
-        <v>7015191</v>
+        <v>7014874</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6485,6 +6475,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6511,10 +6506,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137746</v>
+        <v>129137860</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,21 +6517,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548355</v>
+        <v>548481</v>
       </c>
       <c r="R60" t="n">
-        <v>7014874</v>
+        <v>7015172</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6586,7 +6581,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6613,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129126001</v>
+        <v>129137859</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6648,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548299</v>
+        <v>548434</v>
       </c>
       <c r="R61" t="n">
-        <v>7014876</v>
+        <v>7014792</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6684,6 +6679,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6710,10 +6710,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B62" t="n">
-        <v>92811</v>
+        <v>80167</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R62" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B63" t="n">
         <v>80167</v>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R63" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,7 +6907,7 @@
         <v>129137782</v>
       </c>
       <c r="B64" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137875</v>
+        <v>129137910</v>
       </c>
       <c r="B65" t="n">
-        <v>80167</v>
+        <v>92816</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7017,21 +7017,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548581</v>
+        <v>548510</v>
       </c>
       <c r="R65" t="n">
-        <v>7015017</v>
+        <v>7014986</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7103,10 +7103,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137857</v>
+        <v>129137811</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7114,21 +7114,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548502</v>
+        <v>548458</v>
       </c>
       <c r="R66" t="n">
-        <v>7015176</v>
+        <v>7015205</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,11 +7174,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7205,32 +7200,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137890</v>
+        <v>129137857</v>
       </c>
       <c r="B67" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7240,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548594</v>
+        <v>548502</v>
       </c>
       <c r="R67" t="n">
-        <v>7015211</v>
+        <v>7015176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7280,7 +7275,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7307,32 +7302,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137811</v>
+        <v>129137890</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7342,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548458</v>
+        <v>548594</v>
       </c>
       <c r="R68" t="n">
-        <v>7015205</v>
+        <v>7015211</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7378,6 +7373,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7404,10 +7404,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137858</v>
+        <v>129137791</v>
       </c>
       <c r="B69" t="n">
-        <v>56913</v>
+        <v>105719</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7415,21 +7415,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548400</v>
+        <v>548452</v>
       </c>
       <c r="R69" t="n">
-        <v>7015152</v>
+        <v>7014769</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7475,11 +7475,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7506,10 +7501,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137791</v>
+        <v>129137762</v>
       </c>
       <c r="B70" t="n">
-        <v>105714</v>
+        <v>97533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7517,21 +7512,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7541,10 +7536,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548452</v>
+        <v>548603</v>
       </c>
       <c r="R70" t="n">
-        <v>7014769</v>
+        <v>7014709</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7603,10 +7598,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137762</v>
+        <v>129137858</v>
       </c>
       <c r="B71" t="n">
-        <v>97528</v>
+        <v>56913</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7614,21 +7609,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7638,10 +7633,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548603</v>
+        <v>548400</v>
       </c>
       <c r="R71" t="n">
-        <v>7014709</v>
+        <v>7015152</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7674,6 +7669,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7700,32 +7700,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137780</v>
+        <v>129137773</v>
       </c>
       <c r="B72" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548594</v>
+        <v>548717</v>
       </c>
       <c r="R72" t="n">
-        <v>7015114</v>
+        <v>7014991</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,11 +7771,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7802,32 +7797,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137748</v>
+        <v>129137886</v>
       </c>
       <c r="B73" t="n">
-        <v>57883</v>
+        <v>80175</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7837,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548710</v>
+        <v>548498</v>
       </c>
       <c r="R73" t="n">
-        <v>7014904</v>
+        <v>7015173</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7873,11 +7868,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7904,10 +7894,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137773</v>
+        <v>129137902</v>
       </c>
       <c r="B74" t="n">
-        <v>80139</v>
+        <v>91541</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7915,21 +7905,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7939,10 +7929,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548717</v>
+        <v>548480</v>
       </c>
       <c r="R74" t="n">
-        <v>7014991</v>
+        <v>7015285</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8103,32 +8093,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137886</v>
+        <v>129137748</v>
       </c>
       <c r="B76" t="n">
-        <v>80175</v>
+        <v>57883</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8138,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548498</v>
+        <v>548710</v>
       </c>
       <c r="R76" t="n">
-        <v>7015173</v>
+        <v>7014904</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8174,6 +8164,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8200,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137902</v>
+        <v>129137780</v>
       </c>
       <c r="B77" t="n">
-        <v>91538</v>
+        <v>98656</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548480</v>
+        <v>548594</v>
       </c>
       <c r="R77" t="n">
-        <v>7015285</v>
+        <v>7015114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8271,6 +8266,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137759</v>
+        <v>129137813</v>
       </c>
       <c r="B78" t="n">
-        <v>97522</v>
+        <v>79034</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548487</v>
+        <v>548374</v>
       </c>
       <c r="R78" t="n">
-        <v>7014855</v>
+        <v>7015064</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,7 +8394,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137813</v>
+        <v>129137818</v>
       </c>
       <c r="B79" t="n">
         <v>79034</v>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548374</v>
+        <v>548329</v>
       </c>
       <c r="R79" t="n">
-        <v>7015064</v>
+        <v>7014932</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8494,7 +8494,7 @@
         <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8593,32 +8593,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137818</v>
+        <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>97527</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548329</v>
+        <v>548487</v>
       </c>
       <c r="R81" t="n">
-        <v>7014932</v>
+        <v>7014855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8792,10 +8792,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137900</v>
+        <v>129137871</v>
       </c>
       <c r="B83" t="n">
-        <v>105714</v>
+        <v>97533</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8803,21 +8803,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548451</v>
+        <v>548457</v>
       </c>
       <c r="R83" t="n">
-        <v>7014746</v>
+        <v>7014764</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8889,32 +8889,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137805</v>
+        <v>129137872</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>97533</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548613</v>
+        <v>548477</v>
       </c>
       <c r="R84" t="n">
-        <v>7015186</v>
+        <v>7015144</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8986,32 +8986,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137871</v>
+        <v>129137805</v>
       </c>
       <c r="B85" t="n">
-        <v>97528</v>
+        <v>79034</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548457</v>
+        <v>548613</v>
       </c>
       <c r="R85" t="n">
-        <v>7014764</v>
+        <v>7015186</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9083,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137872</v>
+        <v>129137796</v>
       </c>
       <c r="B86" t="n">
-        <v>97528</v>
+        <v>79034</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548477</v>
+        <v>548559</v>
       </c>
       <c r="R86" t="n">
-        <v>7015144</v>
+        <v>7014776</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,32 +9180,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137889</v>
+        <v>129137816</v>
       </c>
       <c r="B87" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548440</v>
+        <v>548400</v>
       </c>
       <c r="R87" t="n">
-        <v>7014752</v>
+        <v>7014970</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9251,11 +9251,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,32 +9277,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137796</v>
+        <v>129137900</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>105719</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9312,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548559</v>
+        <v>548451</v>
       </c>
       <c r="R88" t="n">
-        <v>7014776</v>
+        <v>7014746</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9379,32 +9374,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137816</v>
+        <v>129137889</v>
       </c>
       <c r="B89" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9409,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548400</v>
+        <v>548440</v>
       </c>
       <c r="R89" t="n">
-        <v>7014970</v>
+        <v>7014752</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9450,6 +9445,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9479,7 +9479,7 @@
         <v>129137781</v>
       </c>
       <c r="B90" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9578,32 +9578,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137901</v>
+        <v>129137878</v>
       </c>
       <c r="B91" t="n">
-        <v>105714</v>
+        <v>80139</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548281</v>
+        <v>548705</v>
       </c>
       <c r="R91" t="n">
-        <v>7015128</v>
+        <v>7014750</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137790</v>
+        <v>129137778</v>
       </c>
       <c r="B92" t="n">
-        <v>105714</v>
+        <v>57827</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9686,21 +9686,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>103031</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548558</v>
+        <v>548706</v>
       </c>
       <c r="R92" t="n">
-        <v>7014771</v>
+        <v>7014864</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9746,6 +9746,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9772,10 +9777,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137778</v>
+        <v>129137901</v>
       </c>
       <c r="B93" t="n">
-        <v>57827</v>
+        <v>105719</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9783,21 +9788,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103031</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9807,10 +9812,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548706</v>
+        <v>548281</v>
       </c>
       <c r="R93" t="n">
-        <v>7014864</v>
+        <v>7015128</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9843,11 +9848,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9874,10 +9874,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137764</v>
+        <v>129137790</v>
       </c>
       <c r="B94" t="n">
-        <v>97528</v>
+        <v>105719</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9885,21 +9885,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548590</v>
+        <v>548558</v>
       </c>
       <c r="R94" t="n">
-        <v>7015157</v>
+        <v>7014771</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9971,32 +9971,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137878</v>
+        <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>80139</v>
+        <v>97533</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548705</v>
+        <v>548590</v>
       </c>
       <c r="R95" t="n">
-        <v>7014750</v>
+        <v>7015157</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10262,10 +10262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137874</v>
+        <v>129137912</v>
       </c>
       <c r="B98" t="n">
-        <v>97528</v>
+        <v>96775</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10273,21 +10273,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548348</v>
+        <v>548604</v>
       </c>
       <c r="R98" t="n">
-        <v>7014988</v>
+        <v>7015234</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10359,32 +10359,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137788</v>
+        <v>129137863</v>
       </c>
       <c r="B99" t="n">
-        <v>98651</v>
+        <v>80140</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548605</v>
+        <v>548702</v>
       </c>
       <c r="R99" t="n">
-        <v>7014687</v>
+        <v>7014752</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10430,11 +10430,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10660,32 +10655,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137912</v>
+        <v>129137788</v>
       </c>
       <c r="B102" t="n">
-        <v>96770</v>
+        <v>98656</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10695,10 +10690,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548604</v>
+        <v>548605</v>
       </c>
       <c r="R102" t="n">
-        <v>7015234</v>
+        <v>7014687</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10731,6 +10726,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10757,32 +10757,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137863</v>
+        <v>129137874</v>
       </c>
       <c r="B103" t="n">
-        <v>80140</v>
+        <v>97533</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548702</v>
+        <v>548348</v>
       </c>
       <c r="R103" t="n">
-        <v>7014752</v>
+        <v>7014988</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137840</v>
+        <v>129137883</v>
       </c>
       <c r="B104" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10865,21 +10865,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548660</v>
+        <v>548499</v>
       </c>
       <c r="R104" t="n">
-        <v>7014820</v>
+        <v>7015176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10951,10 +10951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137753</v>
+        <v>129137840</v>
       </c>
       <c r="B105" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10962,21 +10962,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548681</v>
+        <v>548660</v>
       </c>
       <c r="R105" t="n">
-        <v>7015193</v>
+        <v>7014820</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11048,32 +11048,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137758</v>
+        <v>129137753</v>
       </c>
       <c r="B106" t="n">
-        <v>97522</v>
+        <v>91808</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548629</v>
+        <v>548681</v>
       </c>
       <c r="R106" t="n">
-        <v>7014777</v>
+        <v>7015193</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11145,32 +11145,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137883</v>
+        <v>129137758</v>
       </c>
       <c r="B107" t="n">
-        <v>80139</v>
+        <v>97527</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548499</v>
+        <v>548629</v>
       </c>
       <c r="R107" t="n">
-        <v>7015176</v>
+        <v>7014777</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11242,10 +11242,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137873</v>
+        <v>129137768</v>
       </c>
       <c r="B108" t="n">
-        <v>97528</v>
+        <v>80167</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11253,21 +11253,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548291</v>
+        <v>548723</v>
       </c>
       <c r="R108" t="n">
-        <v>7015110</v>
+        <v>7014940</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11543,10 +11543,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137768</v>
+        <v>129137761</v>
       </c>
       <c r="B111" t="n">
-        <v>80167</v>
+        <v>97527</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11554,21 +11554,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11578,10 +11578,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548723</v>
+        <v>548366</v>
       </c>
       <c r="R111" t="n">
-        <v>7014940</v>
+        <v>7015047</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11640,10 +11640,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137761</v>
+        <v>129137873</v>
       </c>
       <c r="B112" t="n">
-        <v>97522</v>
+        <v>97533</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11651,16 +11651,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548366</v>
+        <v>548291</v>
       </c>
       <c r="R112" t="n">
-        <v>7015047</v>
+        <v>7015110</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1246,32 +1246,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137817</v>
+        <v>129137870</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>97536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548367</v>
+        <v>548358</v>
       </c>
       <c r="R7" t="n">
-        <v>7014944</v>
+        <v>7014777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137797</v>
+        <v>129137817</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548657</v>
+        <v>548367</v>
       </c>
       <c r="R8" t="n">
-        <v>7014768</v>
+        <v>7014944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137815</v>
+        <v>129137797</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548398</v>
+        <v>548657</v>
       </c>
       <c r="R9" t="n">
-        <v>7015004</v>
+        <v>7014768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,11 +1511,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137740</v>
+        <v>129137815</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548618</v>
+        <v>548398</v>
       </c>
       <c r="R10" t="n">
-        <v>7015211</v>
+        <v>7015004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1612,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137870</v>
+        <v>129137740</v>
       </c>
       <c r="B11" t="n">
-        <v>97533</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548358</v>
+        <v>548618</v>
       </c>
       <c r="R11" t="n">
-        <v>7014777</v>
+        <v>7015211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1744,7 @@
         <v>129137787</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137795</v>
+        <v>129137794</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548538</v>
+        <v>548459</v>
       </c>
       <c r="R13" t="n">
-        <v>7014770</v>
+        <v>7015186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,11 +1914,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R14" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,6 +2011,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R15" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137820</v>
+        <v>129137802</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548328</v>
+        <v>548499</v>
       </c>
       <c r="R17" t="n">
-        <v>7014882</v>
+        <v>7014902</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,11 +2312,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,32 +2338,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137801</v>
+        <v>129137869</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>97536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548686</v>
+        <v>548335</v>
       </c>
       <c r="R18" t="n">
-        <v>7014817</v>
+        <v>7014782</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137802</v>
+        <v>129137820</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,10 +2470,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548499</v>
+        <v>548328</v>
       </c>
       <c r="R19" t="n">
-        <v>7014902</v>
+        <v>7014882</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,6 +2506,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,32 +2537,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137869</v>
+        <v>129137801</v>
       </c>
       <c r="B20" t="n">
-        <v>97533</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548335</v>
+        <v>548686</v>
       </c>
       <c r="R20" t="n">
-        <v>7014782</v>
+        <v>7014817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137906</v>
+        <v>129137771</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>80168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548693</v>
+        <v>548360</v>
       </c>
       <c r="R21" t="n">
-        <v>7014874</v>
+        <v>7014942</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137771</v>
+        <v>129137862</v>
       </c>
       <c r="B22" t="n">
-        <v>80167</v>
+        <v>80169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,21 +2742,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548360</v>
+        <v>548497</v>
       </c>
       <c r="R22" t="n">
-        <v>7014942</v>
+        <v>7015181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137819</v>
+        <v>129137906</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548318</v>
+        <v>548693</v>
       </c>
       <c r="R23" t="n">
-        <v>7014904</v>
+        <v>7014874</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B24" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R24" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137744</v>
+        <v>129137750</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548511</v>
+        <v>548514</v>
       </c>
       <c r="R25" t="n">
-        <v>7015241</v>
+        <v>7015227</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3124,10 +3124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137750</v>
+        <v>129137744</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548514</v>
+        <v>548511</v>
       </c>
       <c r="R26" t="n">
-        <v>7015227</v>
+        <v>7015241</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3226,32 +3226,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B27" t="n">
-        <v>80167</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R27" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137810</v>
+        <v>129137806</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548538</v>
+        <v>548632</v>
       </c>
       <c r="R28" t="n">
-        <v>7015259</v>
+        <v>7015246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137806</v>
+        <v>129137749</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548632</v>
+        <v>548618</v>
       </c>
       <c r="R29" t="n">
-        <v>7015246</v>
+        <v>7015211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3491,6 +3491,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3517,32 +3522,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137749</v>
+        <v>129125929</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>97530</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548618</v>
+        <v>548372</v>
       </c>
       <c r="R30" t="n">
-        <v>7015211</v>
+        <v>7014829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,11 +3593,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3619,10 +3619,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129125929</v>
+        <v>129137876</v>
       </c>
       <c r="B31" t="n">
-        <v>97527</v>
+        <v>80168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3630,21 +3630,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548372</v>
+        <v>548475</v>
       </c>
       <c r="R31" t="n">
-        <v>7014829</v>
+        <v>7015265</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,32 +3716,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137800</v>
+        <v>129137789</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548708</v>
+        <v>548461</v>
       </c>
       <c r="R32" t="n">
-        <v>7014937</v>
+        <v>7015210</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3818,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R33" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,6 +3889,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3915,10 +3920,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137789</v>
+        <v>129126213</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,17 +3948,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548461</v>
+        <v>548265</v>
       </c>
       <c r="R34" t="n">
-        <v>7015210</v>
+        <v>7014876</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,11 +3995,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,32 +4021,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137896</v>
+        <v>129137849</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4052,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548260</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7014898</v>
+        <v>7015247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,7 +4096,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,49 +4123,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129126213</v>
+        <v>129137800</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548265</v>
+        <v>548708</v>
       </c>
       <c r="R36" t="n">
-        <v>7014876</v>
+        <v>7014937</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4194,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4220,10 +4225,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137849</v>
+        <v>129137821</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4231,21 +4236,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548629</v>
+        <v>548369</v>
       </c>
       <c r="R37" t="n">
-        <v>7015247</v>
+        <v>7014853</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,11 +4296,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4325,7 +4325,7 @@
         <v>129137774</v>
       </c>
       <c r="B38" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>129137772</v>
       </c>
       <c r="B39" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137812</v>
+        <v>129137895</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548395</v>
+        <v>548277</v>
       </c>
       <c r="R40" t="n">
-        <v>7015086</v>
+        <v>7015126</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137846</v>
+        <v>129137812</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548317</v>
+        <v>548395</v>
       </c>
       <c r="R41" t="n">
-        <v>7014833</v>
+        <v>7015086</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137895</v>
+        <v>129137846</v>
       </c>
       <c r="B42" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548277</v>
+        <v>548317</v>
       </c>
       <c r="R42" t="n">
-        <v>7015126</v>
+        <v>7014833</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137803</v>
+        <v>129137822</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>57644</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548467</v>
+        <v>548346</v>
       </c>
       <c r="R43" t="n">
-        <v>7014995</v>
+        <v>7015026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137814</v>
+        <v>129137783</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548376</v>
+        <v>548595</v>
       </c>
       <c r="R44" t="n">
-        <v>7015053</v>
+        <v>7015162</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,6 +4985,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,32 +5016,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137822</v>
+        <v>129137891</v>
       </c>
       <c r="B45" t="n">
-        <v>57644</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5051,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548346</v>
+        <v>548627</v>
       </c>
       <c r="R45" t="n">
-        <v>7015026</v>
+        <v>7015253</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,6 +5087,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5108,32 +5118,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137843</v>
+        <v>129137792</v>
       </c>
       <c r="B46" t="n">
-        <v>91523</v>
+        <v>105722</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5153,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548488</v>
+        <v>548368</v>
       </c>
       <c r="R46" t="n">
-        <v>7015296</v>
+        <v>7014860</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5179,6 +5189,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5205,32 +5220,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137909</v>
+        <v>129137786</v>
       </c>
       <c r="B47" t="n">
-        <v>82897</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548610</v>
+        <v>548402</v>
       </c>
       <c r="R47" t="n">
-        <v>7015229</v>
+        <v>7015096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,6 +5291,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5302,32 +5322,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137783</v>
+        <v>129137843</v>
       </c>
       <c r="B48" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5337,10 +5357,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548595</v>
+        <v>548488</v>
       </c>
       <c r="R48" t="n">
-        <v>7015162</v>
+        <v>7015296</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5373,11 +5393,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5404,32 +5419,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137891</v>
+        <v>129137909</v>
       </c>
       <c r="B49" t="n">
-        <v>98656</v>
+        <v>82898</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5439,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548627</v>
+        <v>548610</v>
       </c>
       <c r="R49" t="n">
-        <v>7015253</v>
+        <v>7015229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5475,11 +5490,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5506,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137792</v>
+        <v>129137803</v>
       </c>
       <c r="B50" t="n">
-        <v>105719</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5541,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548368</v>
+        <v>548467</v>
       </c>
       <c r="R50" t="n">
-        <v>7014860</v>
+        <v>7014995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5577,11 +5587,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137786</v>
+        <v>129137814</v>
       </c>
       <c r="B51" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548402</v>
+        <v>548376</v>
       </c>
       <c r="R51" t="n">
-        <v>7015096</v>
+        <v>7015053</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,11 +5684,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5713,7 +5713,7 @@
         <v>129137766</v>
       </c>
       <c r="B52" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137905</v>
+        <v>129137860</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548618</v>
+        <v>548481</v>
       </c>
       <c r="R53" t="n">
-        <v>7015116</v>
+        <v>7015172</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,6 +5883,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5909,32 +5914,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137877</v>
+        <v>129137859</v>
       </c>
       <c r="B54" t="n">
-        <v>80167</v>
+        <v>57883</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5944,10 +5949,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548334</v>
+        <v>548434</v>
       </c>
       <c r="R54" t="n">
-        <v>7015001</v>
+        <v>7014792</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5980,6 +5985,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6006,32 +6016,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129126001</v>
+        <v>129137877</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>80168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6051,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548299</v>
+        <v>548334</v>
       </c>
       <c r="R55" t="n">
-        <v>7014876</v>
+        <v>7015001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6106,7 +6116,7 @@
         <v>129137882</v>
       </c>
       <c r="B56" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6200,10 +6210,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137739</v>
+        <v>129137905</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6221,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6245,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548460</v>
+        <v>548618</v>
       </c>
       <c r="R57" t="n">
-        <v>7014976</v>
+        <v>7015116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6271,11 +6281,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6302,10 +6307,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137845</v>
+        <v>129126001</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6313,21 +6318,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6337,10 +6342,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548531</v>
+        <v>548299</v>
       </c>
       <c r="R58" t="n">
-        <v>7014817</v>
+        <v>7014876</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6373,11 +6378,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6506,10 +6506,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137860</v>
+        <v>129137845</v>
       </c>
       <c r="B60" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548481</v>
+        <v>548531</v>
       </c>
       <c r="R60" t="n">
-        <v>7015172</v>
+        <v>7014817</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137859</v>
+        <v>129137739</v>
       </c>
       <c r="B61" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548434</v>
+        <v>548460</v>
       </c>
       <c r="R61" t="n">
-        <v>7014792</v>
+        <v>7014976</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6713,7 +6713,7 @@
         <v>129137769</v>
       </c>
       <c r="B62" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>129137875</v>
       </c>
       <c r="B63" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6904,32 +6904,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137782</v>
+        <v>129137910</v>
       </c>
       <c r="B64" t="n">
-        <v>98656</v>
+        <v>92819</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548485</v>
+        <v>548510</v>
       </c>
       <c r="R64" t="n">
-        <v>7014854</v>
+        <v>7014986</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6975,11 +6975,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7006,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137910</v>
+        <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>92816</v>
+        <v>98659</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7041,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548510</v>
+        <v>548485</v>
       </c>
       <c r="R65" t="n">
-        <v>7014986</v>
+        <v>7014854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7077,6 +7072,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7106,7 +7106,7 @@
         <v>129137811</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7200,32 +7200,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137857</v>
+        <v>129137858</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>56913</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548502</v>
+        <v>548400</v>
       </c>
       <c r="R67" t="n">
-        <v>7015176</v>
+        <v>7015152</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,32 +7302,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137890</v>
+        <v>129137857</v>
       </c>
       <c r="B68" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548594</v>
+        <v>548502</v>
       </c>
       <c r="R68" t="n">
-        <v>7015211</v>
+        <v>7015176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7404,10 +7404,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137791</v>
+        <v>129137762</v>
       </c>
       <c r="B69" t="n">
-        <v>105719</v>
+        <v>97536</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7415,21 +7415,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548452</v>
+        <v>548603</v>
       </c>
       <c r="R69" t="n">
-        <v>7014769</v>
+        <v>7014709</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7501,32 +7501,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137762</v>
+        <v>129137890</v>
       </c>
       <c r="B70" t="n">
-        <v>97533</v>
+        <v>98659</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548603</v>
+        <v>548594</v>
       </c>
       <c r="R70" t="n">
-        <v>7014709</v>
+        <v>7015211</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7572,6 +7572,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7598,10 +7603,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137858</v>
+        <v>129137791</v>
       </c>
       <c r="B71" t="n">
-        <v>56913</v>
+        <v>105722</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7609,21 +7614,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7633,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548400</v>
+        <v>548452</v>
       </c>
       <c r="R71" t="n">
-        <v>7015152</v>
+        <v>7014769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7669,11 +7674,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7700,32 +7700,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137773</v>
+        <v>129137780</v>
       </c>
       <c r="B72" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548717</v>
+        <v>548594</v>
       </c>
       <c r="R72" t="n">
-        <v>7014991</v>
+        <v>7015114</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,6 +7771,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7797,32 +7802,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137886</v>
+        <v>129137902</v>
       </c>
       <c r="B73" t="n">
-        <v>80175</v>
+        <v>91544</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7832,10 +7837,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548498</v>
+        <v>548480</v>
       </c>
       <c r="R73" t="n">
-        <v>7015173</v>
+        <v>7015285</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7894,10 +7899,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137902</v>
+        <v>129137773</v>
       </c>
       <c r="B74" t="n">
-        <v>91541</v>
+        <v>80140</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7905,21 +7910,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7929,10 +7934,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548480</v>
+        <v>548717</v>
       </c>
       <c r="R74" t="n">
-        <v>7015285</v>
+        <v>7014991</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7991,32 +7996,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137850</v>
+        <v>129137886</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>80176</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8026,10 +8031,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548629</v>
+        <v>548498</v>
       </c>
       <c r="R75" t="n">
-        <v>7015262</v>
+        <v>7015173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8062,11 +8067,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8093,10 +8093,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137748</v>
+        <v>129137850</v>
       </c>
       <c r="B76" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548710</v>
+        <v>548629</v>
       </c>
       <c r="R76" t="n">
-        <v>7014904</v>
+        <v>7015262</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137780</v>
+        <v>129137748</v>
       </c>
       <c r="B77" t="n">
-        <v>98656</v>
+        <v>57883</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548594</v>
+        <v>548710</v>
       </c>
       <c r="R77" t="n">
-        <v>7015114</v>
+        <v>7014904</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8300,7 +8300,7 @@
         <v>129137813</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>129137818</v>
       </c>
       <c r="B79" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8690,10 +8690,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137745</v>
+        <v>129137805</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8701,21 +8701,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548373</v>
+        <v>548613</v>
       </c>
       <c r="R82" t="n">
-        <v>7014966</v>
+        <v>7015186</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8761,11 +8761,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8792,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137871</v>
+        <v>129137796</v>
       </c>
       <c r="B83" t="n">
-        <v>97533</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8827,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548457</v>
+        <v>548559</v>
       </c>
       <c r="R83" t="n">
-        <v>7014764</v>
+        <v>7014776</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8889,32 +8884,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137872</v>
+        <v>129137816</v>
       </c>
       <c r="B84" t="n">
-        <v>97533</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8924,10 +8919,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548477</v>
+        <v>548400</v>
       </c>
       <c r="R84" t="n">
-        <v>7015144</v>
+        <v>7014970</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8986,10 +8981,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137805</v>
+        <v>129137745</v>
       </c>
       <c r="B85" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8997,21 +8992,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9021,10 +9016,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548613</v>
+        <v>548373</v>
       </c>
       <c r="R85" t="n">
-        <v>7015186</v>
+        <v>7014966</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9057,6 +9052,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9083,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137796</v>
+        <v>129137900</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>105722</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548559</v>
+        <v>548451</v>
       </c>
       <c r="R86" t="n">
-        <v>7014776</v>
+        <v>7014746</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,32 +9180,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137816</v>
+        <v>129137889</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548400</v>
+        <v>548440</v>
       </c>
       <c r="R87" t="n">
-        <v>7014970</v>
+        <v>7014752</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9251,6 +9251,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9277,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137900</v>
+        <v>129137781</v>
       </c>
       <c r="B88" t="n">
-        <v>105719</v>
+        <v>98659</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9312,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548451</v>
+        <v>548433</v>
       </c>
       <c r="R88" t="n">
-        <v>7014746</v>
+        <v>7014771</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9348,6 +9353,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9374,32 +9384,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137889</v>
+        <v>129137871</v>
       </c>
       <c r="B89" t="n">
-        <v>98656</v>
+        <v>97536</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9409,10 +9419,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548440</v>
+        <v>548457</v>
       </c>
       <c r="R89" t="n">
-        <v>7014752</v>
+        <v>7014764</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9445,11 +9455,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9476,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137781</v>
+        <v>129137872</v>
       </c>
       <c r="B90" t="n">
-        <v>98656</v>
+        <v>97536</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9511,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548433</v>
+        <v>548477</v>
       </c>
       <c r="R90" t="n">
-        <v>7014771</v>
+        <v>7015144</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9547,11 +9552,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9581,7 +9581,7 @@
         <v>129137878</v>
       </c>
       <c r="B91" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137901</v>
+        <v>129137764</v>
       </c>
       <c r="B93" t="n">
-        <v>105719</v>
+        <v>97536</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9788,21 +9788,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9812,10 +9812,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548281</v>
+        <v>548590</v>
       </c>
       <c r="R93" t="n">
-        <v>7015128</v>
+        <v>7015157</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137790</v>
+        <v>129137901</v>
       </c>
       <c r="B94" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548558</v>
+        <v>548281</v>
       </c>
       <c r="R94" t="n">
-        <v>7014771</v>
+        <v>7015128</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9971,10 +9971,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137764</v>
+        <v>129137790</v>
       </c>
       <c r="B95" t="n">
-        <v>97533</v>
+        <v>105722</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9982,21 +9982,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548590</v>
+        <v>548558</v>
       </c>
       <c r="R95" t="n">
-        <v>7015157</v>
+        <v>7014771</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10068,27 +10068,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B96" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10103,10 +10103,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R96" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10165,27 +10165,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137911</v>
+        <v>129137908</v>
       </c>
       <c r="B97" t="n">
-        <v>80174</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548512</v>
+        <v>548306</v>
       </c>
       <c r="R97" t="n">
-        <v>7015192</v>
+        <v>7015082</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10265,7 +10265,7 @@
         <v>129137912</v>
       </c>
       <c r="B98" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10359,10 +10359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137863</v>
+        <v>129137848</v>
       </c>
       <c r="B99" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548702</v>
+        <v>548598</v>
       </c>
       <c r="R99" t="n">
-        <v>7014752</v>
+        <v>7015227</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10430,6 +10430,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10456,10 +10461,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137903</v>
+        <v>129137863</v>
       </c>
       <c r="B100" t="n">
-        <v>79034</v>
+        <v>80141</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10467,21 +10472,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10491,10 +10496,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548633</v>
+        <v>548702</v>
       </c>
       <c r="R100" t="n">
-        <v>7015045</v>
+        <v>7014752</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10553,32 +10558,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137848</v>
+        <v>129137788</v>
       </c>
       <c r="B101" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10588,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548598</v>
+        <v>548605</v>
       </c>
       <c r="R101" t="n">
-        <v>7015227</v>
+        <v>7014687</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10628,7 +10633,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10655,32 +10660,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137788</v>
+        <v>129137874</v>
       </c>
       <c r="B102" t="n">
-        <v>98656</v>
+        <v>97536</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10690,10 +10695,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548605</v>
+        <v>548348</v>
       </c>
       <c r="R102" t="n">
-        <v>7014687</v>
+        <v>7014988</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10726,11 +10731,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10757,32 +10757,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137874</v>
+        <v>129137903</v>
       </c>
       <c r="B103" t="n">
-        <v>97533</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548348</v>
+        <v>548633</v>
       </c>
       <c r="R103" t="n">
-        <v>7014988</v>
+        <v>7015045</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137883</v>
+        <v>129137840</v>
       </c>
       <c r="B104" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10865,21 +10865,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548499</v>
+        <v>548660</v>
       </c>
       <c r="R104" t="n">
-        <v>7015176</v>
+        <v>7014820</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10951,10 +10951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137840</v>
+        <v>129137753</v>
       </c>
       <c r="B105" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10962,21 +10962,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548660</v>
+        <v>548681</v>
       </c>
       <c r="R105" t="n">
-        <v>7014820</v>
+        <v>7015193</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11048,10 +11048,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137753</v>
+        <v>129137883</v>
       </c>
       <c r="B106" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11059,21 +11059,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548681</v>
+        <v>548499</v>
       </c>
       <c r="R106" t="n">
-        <v>7015193</v>
+        <v>7015176</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
         <v>129137758</v>
       </c>
       <c r="B107" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137768</v>
+        <v>129137844</v>
       </c>
       <c r="B108" t="n">
-        <v>80167</v>
+        <v>57723</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548723</v>
+        <v>548672</v>
       </c>
       <c r="R108" t="n">
-        <v>7014940</v>
+        <v>7014893</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11313,6 +11313,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11441,32 +11446,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137844</v>
+        <v>129137873</v>
       </c>
       <c r="B110" t="n">
-        <v>57723</v>
+        <v>97536</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11476,10 +11481,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548672</v>
+        <v>548291</v>
       </c>
       <c r="R110" t="n">
-        <v>7014893</v>
+        <v>7015110</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11512,11 +11517,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11546,7 +11546,7 @@
         <v>129137761</v>
       </c>
       <c r="B111" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137873</v>
+        <v>129137768</v>
       </c>
       <c r="B112" t="n">
-        <v>97533</v>
+        <v>80168</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548291</v>
+        <v>548723</v>
       </c>
       <c r="R112" t="n">
-        <v>7015110</v>
+        <v>7014940</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137751</v>
+        <v>129137817</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548268</v>
+        <v>548367</v>
       </c>
       <c r="R6" t="n">
-        <v>7014891</v>
+        <v>7014944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,11 +1215,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,32 +1241,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137870</v>
+        <v>129137797</v>
       </c>
       <c r="B7" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548358</v>
+        <v>548657</v>
       </c>
       <c r="R7" t="n">
-        <v>7014777</v>
+        <v>7014768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137817</v>
+        <v>129137815</v>
       </c>
       <c r="B8" t="n">
         <v>79035</v>
@@ -1378,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548367</v>
+        <v>548398</v>
       </c>
       <c r="R8" t="n">
-        <v>7014944</v>
+        <v>7015004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,6 +1409,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137797</v>
+        <v>129137740</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548657</v>
+        <v>548618</v>
       </c>
       <c r="R9" t="n">
-        <v>7014768</v>
+        <v>7015211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,6 +1511,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137815</v>
+        <v>129137787</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548398</v>
+        <v>548366</v>
       </c>
       <c r="R10" t="n">
-        <v>7015004</v>
+        <v>7014942</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137740</v>
+        <v>129137751</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548618</v>
+        <v>548268</v>
       </c>
       <c r="R11" t="n">
-        <v>7015211</v>
+        <v>7014891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1719,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137787</v>
+        <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>97536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548366</v>
+        <v>548358</v>
       </c>
       <c r="R12" t="n">
-        <v>7014942</v>
+        <v>7014777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1817,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2241,7 +2241,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137802</v>
+        <v>129137820</v>
       </c>
       <c r="B17" t="n">
         <v>79035</v>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548499</v>
+        <v>548328</v>
       </c>
       <c r="R17" t="n">
-        <v>7014902</v>
+        <v>7014882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,6 +2312,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,32 +2343,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137869</v>
+        <v>129137801</v>
       </c>
       <c r="B18" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548335</v>
+        <v>548686</v>
       </c>
       <c r="R18" t="n">
-        <v>7014782</v>
+        <v>7014817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,7 +2440,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137820</v>
+        <v>129137802</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -2470,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548328</v>
+        <v>548499</v>
       </c>
       <c r="R19" t="n">
-        <v>7014882</v>
+        <v>7014902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,11 +2511,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,32 +2537,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137801</v>
+        <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548686</v>
+        <v>548335</v>
       </c>
       <c r="R20" t="n">
-        <v>7014817</v>
+        <v>7014782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137771</v>
+        <v>129137906</v>
       </c>
       <c r="B21" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548360</v>
+        <v>548693</v>
       </c>
       <c r="R21" t="n">
-        <v>7014942</v>
+        <v>7014874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,32 +2731,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B22" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R22" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137906</v>
+        <v>129137771</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>80168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548693</v>
+        <v>548360</v>
       </c>
       <c r="R23" t="n">
-        <v>7014874</v>
+        <v>7014942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137819</v>
+        <v>129137862</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548318</v>
+        <v>548497</v>
       </c>
       <c r="R24" t="n">
-        <v>7014904</v>
+        <v>7015181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137750</v>
+        <v>129137744</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548514</v>
+        <v>548511</v>
       </c>
       <c r="R25" t="n">
-        <v>7015227</v>
+        <v>7015241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3124,10 +3124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137744</v>
+        <v>129137750</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548511</v>
+        <v>548514</v>
       </c>
       <c r="R26" t="n">
-        <v>7015241</v>
+        <v>7015227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129125929</v>
+        <v>129137876</v>
       </c>
       <c r="B30" t="n">
-        <v>97530</v>
+        <v>80168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,21 +3533,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548372</v>
+        <v>548475</v>
       </c>
       <c r="R30" t="n">
-        <v>7014829</v>
+        <v>7015265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137876</v>
+        <v>129125929</v>
       </c>
       <c r="B31" t="n">
-        <v>80168</v>
+        <v>97530</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3630,21 +3630,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548475</v>
+        <v>548372</v>
       </c>
       <c r="R31" t="n">
-        <v>7015265</v>
+        <v>7014829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,32 +3716,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137789</v>
+        <v>129137800</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548461</v>
+        <v>548708</v>
       </c>
       <c r="R32" t="n">
-        <v>7015210</v>
+        <v>7014937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3818,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R33" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,11 +3889,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3920,7 +3915,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129126213</v>
+        <v>129137789</v>
       </c>
       <c r="B34" t="n">
         <v>98659</v>
@@ -3948,21 +3943,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548265</v>
+        <v>548461</v>
       </c>
       <c r="R34" t="n">
-        <v>7014876</v>
+        <v>7015210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,6 +3986,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4123,32 +4119,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137800</v>
+        <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4154,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548708</v>
+        <v>548260</v>
       </c>
       <c r="R36" t="n">
-        <v>7014937</v>
+        <v>7014898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4198,7 +4194,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4225,45 +4221,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137821</v>
+        <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548369</v>
+        <v>548265</v>
       </c>
       <c r="R37" t="n">
-        <v>7014853</v>
+        <v>7014876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4516,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137895</v>
+        <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548277</v>
+        <v>548395</v>
       </c>
       <c r="R40" t="n">
-        <v>7015126</v>
+        <v>7015086</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137812</v>
+        <v>129137846</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548395</v>
+        <v>548317</v>
       </c>
       <c r="R41" t="n">
-        <v>7015086</v>
+        <v>7014833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137846</v>
+        <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548317</v>
+        <v>548277</v>
       </c>
       <c r="R42" t="n">
-        <v>7014833</v>
+        <v>7015126</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137822</v>
+        <v>129137909</v>
       </c>
       <c r="B43" t="n">
-        <v>57644</v>
+        <v>82898</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100001</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548346</v>
+        <v>548610</v>
       </c>
       <c r="R43" t="n">
-        <v>7015026</v>
+        <v>7015229</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137783</v>
+        <v>129137803</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548595</v>
+        <v>548467</v>
       </c>
       <c r="R44" t="n">
-        <v>7015162</v>
+        <v>7014995</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,11 +4985,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5016,7 +5011,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137891</v>
+        <v>129137783</v>
       </c>
       <c r="B45" t="n">
         <v>98659</v>
@@ -5051,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548627</v>
+        <v>548595</v>
       </c>
       <c r="R45" t="n">
-        <v>7015253</v>
+        <v>7015162</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5091,7 +5086,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5118,32 +5113,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137792</v>
+        <v>129137891</v>
       </c>
       <c r="B46" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5153,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548368</v>
+        <v>548627</v>
       </c>
       <c r="R46" t="n">
-        <v>7014860</v>
+        <v>7015253</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5193,7 +5188,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5220,32 +5215,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137786</v>
+        <v>129137843</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5255,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548402</v>
+        <v>548488</v>
       </c>
       <c r="R47" t="n">
-        <v>7015096</v>
+        <v>7015296</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,11 +5286,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5322,10 +5312,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137843</v>
+        <v>129137814</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5333,21 +5323,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5357,10 +5347,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548488</v>
+        <v>548376</v>
       </c>
       <c r="R48" t="n">
-        <v>7015296</v>
+        <v>7015053</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5419,10 +5409,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137909</v>
+        <v>129137822</v>
       </c>
       <c r="B49" t="n">
-        <v>82898</v>
+        <v>57644</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5430,21 +5420,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>100001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5444,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548610</v>
+        <v>548346</v>
       </c>
       <c r="R49" t="n">
-        <v>7015229</v>
+        <v>7015026</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5516,32 +5506,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137803</v>
+        <v>129137766</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5541,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548467</v>
+        <v>548366</v>
       </c>
       <c r="R50" t="n">
-        <v>7014995</v>
+        <v>7014942</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,6 +5577,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,32 +5608,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137814</v>
+        <v>129137786</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548376</v>
+        <v>548402</v>
       </c>
       <c r="R51" t="n">
-        <v>7015053</v>
+        <v>7015096</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5684,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137766</v>
+        <v>129137792</v>
       </c>
       <c r="B52" t="n">
-        <v>97536</v>
+        <v>105722</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548366</v>
+        <v>548368</v>
       </c>
       <c r="R52" t="n">
-        <v>7014942</v>
+        <v>7014860</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>5 exemplar</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137860</v>
+        <v>129137877</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>80168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548481</v>
+        <v>548334</v>
       </c>
       <c r="R53" t="n">
-        <v>7015172</v>
+        <v>7015001</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,11 +5883,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5914,10 +5909,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137859</v>
+        <v>129137882</v>
       </c>
       <c r="B54" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5925,21 +5920,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5949,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548434</v>
+        <v>548510</v>
       </c>
       <c r="R54" t="n">
-        <v>7014792</v>
+        <v>7015191</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5985,11 +5980,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6016,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137877</v>
+        <v>129137746</v>
       </c>
       <c r="B55" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6051,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548334</v>
+        <v>548355</v>
       </c>
       <c r="R55" t="n">
-        <v>7015001</v>
+        <v>7014874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6087,6 +6077,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6113,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137882</v>
+        <v>129137845</v>
       </c>
       <c r="B56" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6124,21 +6119,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6148,10 +6143,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548510</v>
+        <v>548531</v>
       </c>
       <c r="R56" t="n">
-        <v>7015191</v>
+        <v>7014817</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6184,6 +6179,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6210,10 +6210,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137905</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6221,21 +6221,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548618</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7015116</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6281,6 +6281,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6307,10 +6312,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129126001</v>
+        <v>129137859</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6318,21 +6323,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6342,10 +6347,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548299</v>
+        <v>548434</v>
       </c>
       <c r="R58" t="n">
-        <v>7014876</v>
+        <v>7014792</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6378,6 +6383,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6404,10 +6414,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137746</v>
+        <v>129137860</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6425,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548355</v>
+        <v>548481</v>
       </c>
       <c r="R59" t="n">
-        <v>7014874</v>
+        <v>7015172</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6479,7 +6489,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6506,10 +6516,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137845</v>
+        <v>129137905</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6517,21 +6527,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6541,10 +6551,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548531</v>
+        <v>548618</v>
       </c>
       <c r="R60" t="n">
-        <v>7014817</v>
+        <v>7015116</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6577,11 +6587,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6608,10 +6613,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137739</v>
+        <v>129126001</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,21 +6624,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6648,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548460</v>
+        <v>548299</v>
       </c>
       <c r="R61" t="n">
-        <v>7014976</v>
+        <v>7014876</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6679,11 +6684,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6710,32 +6710,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137769</v>
+        <v>129137782</v>
       </c>
       <c r="B62" t="n">
-        <v>80168</v>
+        <v>98659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548487</v>
+        <v>548485</v>
       </c>
       <c r="R62" t="n">
-        <v>7015073</v>
+        <v>7014854</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6781,6 +6781,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6807,10 +6812,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137875</v>
+        <v>129137910</v>
       </c>
       <c r="B63" t="n">
-        <v>80168</v>
+        <v>92819</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6818,21 +6823,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6842,10 +6847,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548581</v>
+        <v>548510</v>
       </c>
       <c r="R63" t="n">
-        <v>7015017</v>
+        <v>7014986</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,10 +6909,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B64" t="n">
-        <v>92819</v>
+        <v>80168</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6915,21 +6920,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,10 +6944,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R64" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7001,32 +7006,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137782</v>
+        <v>129137875</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>80168</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7041,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548485</v>
+        <v>548581</v>
       </c>
       <c r="R65" t="n">
-        <v>7014854</v>
+        <v>7015017</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,11 +7077,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7501,32 +7501,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137890</v>
+        <v>129137791</v>
       </c>
       <c r="B70" t="n">
-        <v>98659</v>
+        <v>105722</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548594</v>
+        <v>548452</v>
       </c>
       <c r="R70" t="n">
-        <v>7015211</v>
+        <v>7014769</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7572,11 +7572,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7603,32 +7598,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137791</v>
+        <v>129137890</v>
       </c>
       <c r="B71" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7638,10 +7633,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548452</v>
+        <v>548594</v>
       </c>
       <c r="R71" t="n">
-        <v>7014769</v>
+        <v>7015211</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7674,6 +7669,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7700,32 +7700,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137780</v>
+        <v>129137773</v>
       </c>
       <c r="B72" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548594</v>
+        <v>548717</v>
       </c>
       <c r="R72" t="n">
-        <v>7015114</v>
+        <v>7014991</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,11 +7771,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7802,32 +7797,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137902</v>
+        <v>129137886</v>
       </c>
       <c r="B73" t="n">
-        <v>91544</v>
+        <v>80176</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7837,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548480</v>
+        <v>548498</v>
       </c>
       <c r="R73" t="n">
-        <v>7015285</v>
+        <v>7015173</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7899,10 +7894,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137773</v>
+        <v>129137850</v>
       </c>
       <c r="B74" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7910,21 +7905,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7934,10 +7929,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548717</v>
+        <v>548629</v>
       </c>
       <c r="R74" t="n">
-        <v>7014991</v>
+        <v>7015262</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7970,6 +7965,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,32 +7996,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137886</v>
+        <v>129137902</v>
       </c>
       <c r="B75" t="n">
-        <v>80176</v>
+        <v>91544</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548498</v>
+        <v>548480</v>
       </c>
       <c r="R75" t="n">
-        <v>7015173</v>
+        <v>7015285</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137850</v>
+        <v>129137748</v>
       </c>
       <c r="B76" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548629</v>
+        <v>548710</v>
       </c>
       <c r="R76" t="n">
-        <v>7015262</v>
+        <v>7014904</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137748</v>
+        <v>129137780</v>
       </c>
       <c r="B77" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548710</v>
+        <v>548594</v>
       </c>
       <c r="R77" t="n">
-        <v>7014904</v>
+        <v>7015114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137813</v>
+        <v>129137779</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548374</v>
+        <v>548620</v>
       </c>
       <c r="R78" t="n">
-        <v>7015064</v>
+        <v>7014685</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8368,6 +8368,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8394,7 +8399,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137818</v>
+        <v>129137813</v>
       </c>
       <c r="B79" t="n">
         <v>79035</v>
@@ -8429,10 +8434,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548329</v>
+        <v>548374</v>
       </c>
       <c r="R79" t="n">
-        <v>7014932</v>
+        <v>7015064</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8491,32 +8496,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8526,10 +8531,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R80" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8562,11 +8567,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8690,32 +8690,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137805</v>
+        <v>129137871</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548613</v>
+        <v>548457</v>
       </c>
       <c r="R82" t="n">
-        <v>7015186</v>
+        <v>7014764</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8787,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137796</v>
+        <v>129137872</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548559</v>
+        <v>548477</v>
       </c>
       <c r="R83" t="n">
-        <v>7014776</v>
+        <v>7015144</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8884,32 +8884,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137816</v>
+        <v>129137900</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>105722</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548400</v>
+        <v>548451</v>
       </c>
       <c r="R84" t="n">
-        <v>7014970</v>
+        <v>7014746</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8981,10 +8981,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137745</v>
+        <v>129137805</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548373</v>
+        <v>548613</v>
       </c>
       <c r="R85" t="n">
-        <v>7014966</v>
+        <v>7015186</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9052,11 +9052,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9083,32 +9078,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137900</v>
+        <v>129137796</v>
       </c>
       <c r="B86" t="n">
-        <v>105722</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9113,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548451</v>
+        <v>548559</v>
       </c>
       <c r="R86" t="n">
-        <v>7014746</v>
+        <v>7014776</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,32 +9175,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137889</v>
+        <v>129137816</v>
       </c>
       <c r="B87" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9215,10 +9210,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548440</v>
+        <v>548400</v>
       </c>
       <c r="R87" t="n">
-        <v>7014752</v>
+        <v>7014970</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9251,11 +9246,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,32 +9272,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137781</v>
+        <v>129137745</v>
       </c>
       <c r="B88" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9307,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548433</v>
+        <v>548373</v>
       </c>
       <c r="R88" t="n">
-        <v>7014771</v>
+        <v>7014966</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9357,7 +9347,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>11 stycken kan finnas mer I mossan</t>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9384,32 +9374,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137871</v>
+        <v>129137889</v>
       </c>
       <c r="B89" t="n">
-        <v>97536</v>
+        <v>98659</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9419,10 +9409,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548457</v>
+        <v>548440</v>
       </c>
       <c r="R89" t="n">
-        <v>7014764</v>
+        <v>7014752</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9455,6 +9445,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9476,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137872</v>
+        <v>129137781</v>
       </c>
       <c r="B90" t="n">
-        <v>97536</v>
+        <v>98659</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9511,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548477</v>
+        <v>548433</v>
       </c>
       <c r="R90" t="n">
-        <v>7015144</v>
+        <v>7014771</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9552,6 +9547,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9675,10 +9675,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137778</v>
+        <v>129137764</v>
       </c>
       <c r="B92" t="n">
-        <v>57827</v>
+        <v>97536</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9686,21 +9686,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548706</v>
+        <v>548590</v>
       </c>
       <c r="R92" t="n">
-        <v>7014864</v>
+        <v>7015157</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9746,11 +9746,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9777,10 +9772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137764</v>
+        <v>129137778</v>
       </c>
       <c r="B93" t="n">
-        <v>97536</v>
+        <v>57827</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9788,21 +9783,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9812,10 +9807,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548590</v>
+        <v>548706</v>
       </c>
       <c r="R93" t="n">
-        <v>7015157</v>
+        <v>7014864</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9848,6 +9843,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10359,10 +10359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137848</v>
+        <v>129137863</v>
       </c>
       <c r="B99" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548598</v>
+        <v>548702</v>
       </c>
       <c r="R99" t="n">
-        <v>7015227</v>
+        <v>7014752</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10430,11 +10430,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10461,10 +10456,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137863</v>
+        <v>129137903</v>
       </c>
       <c r="B100" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10472,21 +10467,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10496,10 +10491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548702</v>
+        <v>548633</v>
       </c>
       <c r="R100" t="n">
-        <v>7014752</v>
+        <v>7015045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10558,32 +10553,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137788</v>
+        <v>129137848</v>
       </c>
       <c r="B101" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10593,10 +10588,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548605</v>
+        <v>548598</v>
       </c>
       <c r="R101" t="n">
-        <v>7014687</v>
+        <v>7015227</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10633,7 +10628,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10757,32 +10752,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137903</v>
+        <v>129137788</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10792,10 +10787,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548633</v>
+        <v>548605</v>
       </c>
       <c r="R103" t="n">
-        <v>7015045</v>
+        <v>7014687</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10828,6 +10823,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10854,10 +10854,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137840</v>
+        <v>129137883</v>
       </c>
       <c r="B104" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10865,21 +10865,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548660</v>
+        <v>548499</v>
       </c>
       <c r="R104" t="n">
-        <v>7014820</v>
+        <v>7015176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11048,10 +11048,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137883</v>
+        <v>129137840</v>
       </c>
       <c r="B106" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11059,21 +11059,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548499</v>
+        <v>548660</v>
       </c>
       <c r="R106" t="n">
-        <v>7015176</v>
+        <v>7014820</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11446,10 +11446,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137873</v>
+        <v>129137768</v>
       </c>
       <c r="B110" t="n">
-        <v>97536</v>
+        <v>80168</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11457,21 +11457,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11481,10 +11481,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548291</v>
+        <v>548723</v>
       </c>
       <c r="R110" t="n">
-        <v>7015110</v>
+        <v>7014940</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11543,10 +11543,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137761</v>
+        <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>97530</v>
+        <v>97536</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11554,16 +11554,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11578,10 +11578,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548366</v>
+        <v>548291</v>
       </c>
       <c r="R111" t="n">
-        <v>7015047</v>
+        <v>7015110</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11640,10 +11640,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137768</v>
+        <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>80168</v>
+        <v>97530</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548723</v>
+        <v>548366</v>
       </c>
       <c r="R112" t="n">
-        <v>7014940</v>
+        <v>7015047</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,7 +1144,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137817</v>
+        <v>129137815</v>
       </c>
       <c r="B6" t="n">
         <v>79035</v>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548367</v>
+        <v>548398</v>
       </c>
       <c r="R6" t="n">
-        <v>7014944</v>
+        <v>7015004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,6 +1215,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137797</v>
+        <v>129137740</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548657</v>
+        <v>548618</v>
       </c>
       <c r="R7" t="n">
-        <v>7014768</v>
+        <v>7015211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,6 +1317,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137815</v>
+        <v>129137797</v>
       </c>
       <c r="B8" t="n">
         <v>79035</v>
@@ -1373,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548398</v>
+        <v>548657</v>
       </c>
       <c r="R8" t="n">
-        <v>7015004</v>
+        <v>7014768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,11 +1419,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137740</v>
+        <v>129137817</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548618</v>
+        <v>548367</v>
       </c>
       <c r="R9" t="n">
-        <v>7015211</v>
+        <v>7014944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,11 +1516,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137751</v>
+        <v>129137870</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>97536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548268</v>
+        <v>548358</v>
       </c>
       <c r="R11" t="n">
-        <v>7014891</v>
+        <v>7014777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137870</v>
+        <v>129137751</v>
       </c>
       <c r="B12" t="n">
-        <v>97536</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548358</v>
+        <v>548268</v>
       </c>
       <c r="R12" t="n">
-        <v>7014777</v>
+        <v>7014891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2634,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137906</v>
+        <v>129137744</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,21 +2645,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548693</v>
+        <v>548511</v>
       </c>
       <c r="R21" t="n">
-        <v>7014874</v>
+        <v>7015241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,6 +2705,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2731,7 +2736,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137819</v>
+        <v>129137906</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -2766,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548318</v>
+        <v>548693</v>
       </c>
       <c r="R22" t="n">
-        <v>7014904</v>
+        <v>7014874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,32 +2833,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137771</v>
+        <v>129137819</v>
       </c>
       <c r="B23" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548360</v>
+        <v>548318</v>
       </c>
       <c r="R23" t="n">
-        <v>7014942</v>
+        <v>7014904</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137862</v>
+        <v>129137771</v>
       </c>
       <c r="B24" t="n">
-        <v>80169</v>
+        <v>80168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2941,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548497</v>
+        <v>548360</v>
       </c>
       <c r="R24" t="n">
-        <v>7015181</v>
+        <v>7014942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,32 +3027,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137744</v>
+        <v>129137862</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3057,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548511</v>
+        <v>548497</v>
       </c>
       <c r="R25" t="n">
-        <v>7015241</v>
+        <v>7015181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,11 +3098,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4516,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137812</v>
+        <v>129137895</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548395</v>
+        <v>548277</v>
       </c>
       <c r="R40" t="n">
-        <v>7015086</v>
+        <v>7015126</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4715,32 +4720,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137895</v>
+        <v>129137812</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548277</v>
+        <v>548395</v>
       </c>
       <c r="R42" t="n">
-        <v>7015126</v>
+        <v>7015086</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4786,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137877</v>
+        <v>129137746</v>
       </c>
       <c r="B53" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548334</v>
+        <v>548355</v>
       </c>
       <c r="R53" t="n">
-        <v>7015001</v>
+        <v>7014874</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,6 +5883,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5909,10 +5914,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137882</v>
+        <v>129137845</v>
       </c>
       <c r="B54" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5920,21 +5925,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5944,10 +5949,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548510</v>
+        <v>548531</v>
       </c>
       <c r="R54" t="n">
-        <v>7015191</v>
+        <v>7014817</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5980,6 +5985,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6006,7 +6016,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137746</v>
+        <v>129137739</v>
       </c>
       <c r="B55" t="n">
         <v>57723</v>
@@ -6041,10 +6051,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548355</v>
+        <v>548460</v>
       </c>
       <c r="R55" t="n">
-        <v>7014874</v>
+        <v>7014976</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6081,7 +6091,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6108,10 +6118,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137845</v>
+        <v>129137859</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6119,21 +6129,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6143,10 +6153,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548531</v>
+        <v>548434</v>
       </c>
       <c r="R56" t="n">
-        <v>7014817</v>
+        <v>7014792</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6183,7 +6193,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6210,10 +6220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137739</v>
+        <v>129137860</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6221,21 +6231,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6245,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548460</v>
+        <v>548481</v>
       </c>
       <c r="R57" t="n">
-        <v>7014976</v>
+        <v>7015172</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6285,7 +6295,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6312,10 +6322,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137859</v>
+        <v>129137905</v>
       </c>
       <c r="B58" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6323,21 +6333,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6347,10 +6357,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548434</v>
+        <v>548618</v>
       </c>
       <c r="R58" t="n">
-        <v>7014792</v>
+        <v>7015116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6383,11 +6393,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6414,10 +6419,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137860</v>
+        <v>129126001</v>
       </c>
       <c r="B59" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6425,21 +6430,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6449,10 +6454,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548481</v>
+        <v>548299</v>
       </c>
       <c r="R59" t="n">
-        <v>7015172</v>
+        <v>7014876</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6485,11 +6490,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6516,32 +6516,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137905</v>
+        <v>129137877</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>80168</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548618</v>
+        <v>548334</v>
       </c>
       <c r="R60" t="n">
-        <v>7015116</v>
+        <v>7015001</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129126001</v>
+        <v>129137882</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,21 +6624,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548299</v>
+        <v>548510</v>
       </c>
       <c r="R61" t="n">
-        <v>7014876</v>
+        <v>7015191</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,32 +6710,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137782</v>
+        <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548485</v>
+        <v>548510</v>
       </c>
       <c r="R62" t="n">
-        <v>7014854</v>
+        <v>7014986</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6781,11 +6781,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6812,10 +6807,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B63" t="n">
-        <v>92819</v>
+        <v>80168</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6823,21 +6818,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6847,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R63" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6909,7 +6904,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B64" t="n">
         <v>80168</v>
@@ -6944,10 +6939,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R64" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7006,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137875</v>
+        <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>80168</v>
+        <v>98659</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7041,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548581</v>
+        <v>548485</v>
       </c>
       <c r="R65" t="n">
-        <v>7015017</v>
+        <v>7014854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7077,6 +7072,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7103,32 +7103,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137811</v>
+        <v>129137890</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548458</v>
+        <v>548594</v>
       </c>
       <c r="R66" t="n">
-        <v>7015205</v>
+        <v>7015211</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,6 +7174,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7205,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137858</v>
+        <v>129137762</v>
       </c>
       <c r="B67" t="n">
-        <v>56913</v>
+        <v>97536</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7216,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7240,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548400</v>
+        <v>548603</v>
       </c>
       <c r="R67" t="n">
-        <v>7015152</v>
+        <v>7014709</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,11 +7276,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,32 +7302,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137857</v>
+        <v>129137791</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>105722</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548502</v>
+        <v>548452</v>
       </c>
       <c r="R68" t="n">
-        <v>7015176</v>
+        <v>7014769</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,11 +7373,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7404,32 +7399,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137762</v>
+        <v>129137811</v>
       </c>
       <c r="B69" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7439,10 +7434,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548603</v>
+        <v>548458</v>
       </c>
       <c r="R69" t="n">
-        <v>7014709</v>
+        <v>7015205</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7501,10 +7496,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137791</v>
+        <v>129137858</v>
       </c>
       <c r="B70" t="n">
-        <v>105722</v>
+        <v>56913</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7512,21 +7507,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7536,10 +7531,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548452</v>
+        <v>548400</v>
       </c>
       <c r="R70" t="n">
-        <v>7014769</v>
+        <v>7015152</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7572,6 +7567,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7598,32 +7598,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137890</v>
+        <v>129137857</v>
       </c>
       <c r="B71" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548594</v>
+        <v>548502</v>
       </c>
       <c r="R71" t="n">
-        <v>7015211</v>
+        <v>7015176</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9578,32 +9578,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137878</v>
+        <v>129137764</v>
       </c>
       <c r="B91" t="n">
-        <v>80140</v>
+        <v>97536</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548705</v>
+        <v>548590</v>
       </c>
       <c r="R91" t="n">
-        <v>7014750</v>
+        <v>7015157</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137764</v>
+        <v>129137778</v>
       </c>
       <c r="B92" t="n">
-        <v>97536</v>
+        <v>57827</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9686,21 +9686,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548590</v>
+        <v>548706</v>
       </c>
       <c r="R92" t="n">
-        <v>7015157</v>
+        <v>7014864</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9746,6 +9746,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9772,10 +9777,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137778</v>
+        <v>129137901</v>
       </c>
       <c r="B93" t="n">
-        <v>57827</v>
+        <v>105722</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9783,21 +9788,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103031</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9807,10 +9812,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548706</v>
+        <v>548281</v>
       </c>
       <c r="R93" t="n">
-        <v>7014864</v>
+        <v>7015128</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9843,11 +9848,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9874,7 +9874,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137901</v>
+        <v>129137790</v>
       </c>
       <c r="B94" t="n">
         <v>105722</v>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548281</v>
+        <v>548558</v>
       </c>
       <c r="R94" t="n">
-        <v>7015128</v>
+        <v>7014771</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9971,32 +9971,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137790</v>
+        <v>129137878</v>
       </c>
       <c r="B95" t="n">
-        <v>105722</v>
+        <v>80140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548558</v>
+        <v>548705</v>
       </c>
       <c r="R95" t="n">
-        <v>7014771</v>
+        <v>7014750</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10262,10 +10262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137912</v>
+        <v>129137874</v>
       </c>
       <c r="B98" t="n">
-        <v>96778</v>
+        <v>97536</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10273,21 +10273,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548604</v>
+        <v>548348</v>
       </c>
       <c r="R98" t="n">
-        <v>7015234</v>
+        <v>7014988</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10359,32 +10359,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137863</v>
+        <v>129137788</v>
       </c>
       <c r="B99" t="n">
-        <v>80141</v>
+        <v>98659</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548702</v>
+        <v>548605</v>
       </c>
       <c r="R99" t="n">
-        <v>7014752</v>
+        <v>7014687</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10430,6 +10430,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10456,32 +10461,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137903</v>
+        <v>129137912</v>
       </c>
       <c r="B100" t="n">
-        <v>79035</v>
+        <v>96778</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10491,10 +10496,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548633</v>
+        <v>548604</v>
       </c>
       <c r="R100" t="n">
-        <v>7015045</v>
+        <v>7015234</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10553,10 +10558,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137848</v>
+        <v>129137863</v>
       </c>
       <c r="B101" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10564,21 +10569,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10588,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548598</v>
+        <v>548702</v>
       </c>
       <c r="R101" t="n">
-        <v>7015227</v>
+        <v>7014752</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10624,11 +10629,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10655,32 +10655,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137874</v>
+        <v>129137903</v>
       </c>
       <c r="B102" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548348</v>
+        <v>548633</v>
       </c>
       <c r="R102" t="n">
-        <v>7014988</v>
+        <v>7015045</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10752,32 +10752,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137788</v>
+        <v>129137848</v>
       </c>
       <c r="B103" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548605</v>
+        <v>548598</v>
       </c>
       <c r="R103" t="n">
-        <v>7014687</v>
+        <v>7015227</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10827,7 +10827,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137815</v>
+        <v>129137751</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548398</v>
+        <v>548268</v>
       </c>
       <c r="R6" t="n">
-        <v>7015004</v>
+        <v>7014891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137740</v>
+        <v>129137817</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548618</v>
+        <v>548367</v>
       </c>
       <c r="R7" t="n">
-        <v>7015211</v>
+        <v>7014944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,11 +1317,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137797</v>
+        <v>129137815</v>
       </c>
       <c r="B8" t="n">
         <v>79035</v>
@@ -1383,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548657</v>
+        <v>548398</v>
       </c>
       <c r="R8" t="n">
-        <v>7014768</v>
+        <v>7015004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,6 +1414,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,7 +1445,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137817</v>
+        <v>129137797</v>
       </c>
       <c r="B9" t="n">
         <v>79035</v>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548367</v>
+        <v>548657</v>
       </c>
       <c r="R9" t="n">
-        <v>7014944</v>
+        <v>7014768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137787</v>
+        <v>129137740</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548366</v>
+        <v>548618</v>
       </c>
       <c r="R10" t="n">
-        <v>7014942</v>
+        <v>7015211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137870</v>
+        <v>129137787</v>
       </c>
       <c r="B11" t="n">
-        <v>97536</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548358</v>
+        <v>548366</v>
       </c>
       <c r="R11" t="n">
-        <v>7014777</v>
+        <v>7014942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137751</v>
+        <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>97536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548268</v>
+        <v>548358</v>
       </c>
       <c r="R12" t="n">
-        <v>7014891</v>
+        <v>7014777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1817,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,7 +1940,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137795</v>
+        <v>129137804</v>
       </c>
       <c r="B14" t="n">
         <v>79035</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548538</v>
+        <v>548550</v>
       </c>
       <c r="R14" t="n">
-        <v>7014770</v>
+        <v>7015142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,11 +2011,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B15" t="n">
         <v>79035</v>
@@ -2077,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R15" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,6 +2108,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,32 +2241,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137820</v>
+        <v>129137869</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548328</v>
+        <v>548335</v>
       </c>
       <c r="R17" t="n">
-        <v>7014882</v>
+        <v>7014782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,11 +2312,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,7 +2338,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137801</v>
+        <v>129137820</v>
       </c>
       <c r="B18" t="n">
         <v>79035</v>
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548686</v>
+        <v>548328</v>
       </c>
       <c r="R18" t="n">
-        <v>7014817</v>
+        <v>7014882</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,6 +2409,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,7 +2440,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137802</v>
+        <v>129137801</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548499</v>
+        <v>548686</v>
       </c>
       <c r="R19" t="n">
-        <v>7014902</v>
+        <v>7014817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,32 +2537,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137869</v>
+        <v>129137802</v>
       </c>
       <c r="B20" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548335</v>
+        <v>548499</v>
       </c>
       <c r="R20" t="n">
-        <v>7014782</v>
+        <v>7014902</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137906</v>
+        <v>129137771</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>80168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548693</v>
+        <v>548360</v>
       </c>
       <c r="R22" t="n">
-        <v>7014874</v>
+        <v>7014942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137819</v>
+        <v>129137862</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548318</v>
+        <v>548497</v>
       </c>
       <c r="R23" t="n">
-        <v>7014904</v>
+        <v>7015181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137771</v>
+        <v>129137906</v>
       </c>
       <c r="B24" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548360</v>
+        <v>548693</v>
       </c>
       <c r="R24" t="n">
-        <v>7014942</v>
+        <v>7014874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B25" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R25" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,32 +3226,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137810</v>
+        <v>129137876</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>80168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548538</v>
+        <v>548475</v>
       </c>
       <c r="R27" t="n">
-        <v>7015259</v>
+        <v>7015265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137806</v>
+        <v>129137810</v>
       </c>
       <c r="B28" t="n">
         <v>79035</v>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548632</v>
+        <v>548538</v>
       </c>
       <c r="R28" t="n">
-        <v>7015246</v>
+        <v>7015259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137749</v>
+        <v>129137806</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548618</v>
+        <v>548632</v>
       </c>
       <c r="R29" t="n">
-        <v>7015211</v>
+        <v>7015246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3491,11 +3491,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3522,32 +3517,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137876</v>
+        <v>129137749</v>
       </c>
       <c r="B30" t="n">
-        <v>80168</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3557,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548475</v>
+        <v>548618</v>
       </c>
       <c r="R30" t="n">
-        <v>7015265</v>
+        <v>7015211</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3593,6 +3588,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3716,32 +3716,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137800</v>
+        <v>129137789</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548708</v>
+        <v>548461</v>
       </c>
       <c r="R32" t="n">
-        <v>7014937</v>
+        <v>7015210</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3818,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R33" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,6 +3889,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3915,7 +3920,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137789</v>
+        <v>129126213</v>
       </c>
       <c r="B34" t="n">
         <v>98659</v>
@@ -3943,17 +3948,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548461</v>
+        <v>548265</v>
       </c>
       <c r="R34" t="n">
-        <v>7015210</v>
+        <v>7014876</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,11 +3995,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137849</v>
+        <v>129137800</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4028,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4052,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548629</v>
+        <v>548708</v>
       </c>
       <c r="R35" t="n">
-        <v>7015247</v>
+        <v>7014937</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,7 +4096,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,32 +4123,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4154,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R36" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4221,49 +4220,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129126213</v>
+        <v>129137849</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548265</v>
+        <v>548629</v>
       </c>
       <c r="R37" t="n">
-        <v>7014876</v>
+        <v>7015247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,6 +4291,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137895</v>
+        <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548277</v>
+        <v>548395</v>
       </c>
       <c r="R40" t="n">
-        <v>7015126</v>
+        <v>7015086</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4720,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137812</v>
+        <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548395</v>
+        <v>548277</v>
       </c>
       <c r="R42" t="n">
-        <v>7015086</v>
+        <v>7015126</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4786,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,32 +4817,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137909</v>
+        <v>129137783</v>
       </c>
       <c r="B43" t="n">
-        <v>82898</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548610</v>
+        <v>548595</v>
       </c>
       <c r="R43" t="n">
-        <v>7015229</v>
+        <v>7015162</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4914,32 +4919,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137803</v>
+        <v>129137891</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4954,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548467</v>
+        <v>548627</v>
       </c>
       <c r="R44" t="n">
-        <v>7014995</v>
+        <v>7015253</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,6 +4990,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,32 +5021,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137783</v>
+        <v>129137792</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>105722</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548595</v>
+        <v>548368</v>
       </c>
       <c r="R45" t="n">
-        <v>7015162</v>
+        <v>7014860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5086,7 +5096,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5113,7 +5123,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137891</v>
+        <v>129137786</v>
       </c>
       <c r="B46" t="n">
         <v>98659</v>
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548627</v>
+        <v>548402</v>
       </c>
       <c r="R46" t="n">
-        <v>7015253</v>
+        <v>7015096</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5188,7 +5198,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5215,32 +5225,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137843</v>
+        <v>129137766</v>
       </c>
       <c r="B47" t="n">
-        <v>91526</v>
+        <v>97536</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5250,10 +5260,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548488</v>
+        <v>548366</v>
       </c>
       <c r="R47" t="n">
-        <v>7015296</v>
+        <v>7014942</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,6 +5296,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5312,10 +5327,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137814</v>
+        <v>129137843</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5323,21 +5338,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5347,10 +5362,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548376</v>
+        <v>548488</v>
       </c>
       <c r="R48" t="n">
-        <v>7015053</v>
+        <v>7015296</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5409,10 +5424,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137822</v>
+        <v>129137909</v>
       </c>
       <c r="B49" t="n">
-        <v>57644</v>
+        <v>82898</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5420,21 +5435,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100001</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5444,10 +5459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548346</v>
+        <v>548610</v>
       </c>
       <c r="R49" t="n">
-        <v>7015026</v>
+        <v>7015229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5506,32 +5521,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137766</v>
+        <v>129137803</v>
       </c>
       <c r="B50" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5541,10 +5556,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548366</v>
+        <v>548467</v>
       </c>
       <c r="R50" t="n">
-        <v>7014942</v>
+        <v>7014995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5577,11 +5592,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,32 +5618,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137786</v>
+        <v>129137814</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5653,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548402</v>
+        <v>548376</v>
       </c>
       <c r="R51" t="n">
-        <v>7015096</v>
+        <v>7015053</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,11 +5689,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,32 +5715,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137792</v>
+        <v>129137822</v>
       </c>
       <c r="B52" t="n">
-        <v>105722</v>
+        <v>57644</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>100001</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5750,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548368</v>
+        <v>548346</v>
       </c>
       <c r="R52" t="n">
-        <v>7014860</v>
+        <v>7015026</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,11 +5786,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137746</v>
+        <v>129137877</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548355</v>
+        <v>548334</v>
       </c>
       <c r="R53" t="n">
-        <v>7014874</v>
+        <v>7015001</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,11 +5883,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5914,10 +5909,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137845</v>
+        <v>129137882</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5925,21 +5920,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5949,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548531</v>
+        <v>548510</v>
       </c>
       <c r="R54" t="n">
-        <v>7014817</v>
+        <v>7015191</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5985,11 +5980,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6016,10 +6006,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137739</v>
+        <v>129137905</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6027,21 +6017,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6051,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548460</v>
+        <v>548618</v>
       </c>
       <c r="R55" t="n">
-        <v>7014976</v>
+        <v>7015116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6087,11 +6077,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6118,10 +6103,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137859</v>
+        <v>129126001</v>
       </c>
       <c r="B56" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6129,21 +6114,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6153,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548434</v>
+        <v>548299</v>
       </c>
       <c r="R56" t="n">
-        <v>7014792</v>
+        <v>7014876</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6189,11 +6174,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6220,10 +6200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137860</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6231,21 +6211,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548481</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7015172</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6295,7 +6275,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6322,10 +6302,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137905</v>
+        <v>129137845</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6333,21 +6313,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6357,10 +6337,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548618</v>
+        <v>548531</v>
       </c>
       <c r="R58" t="n">
-        <v>7015116</v>
+        <v>7014817</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6393,6 +6373,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6419,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129126001</v>
+        <v>129137746</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6430,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6454,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548299</v>
+        <v>548355</v>
       </c>
       <c r="R59" t="n">
-        <v>7014876</v>
+        <v>7014874</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6490,6 +6475,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6516,32 +6506,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137877</v>
+        <v>129137859</v>
       </c>
       <c r="B60" t="n">
-        <v>80168</v>
+        <v>57883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6551,10 +6541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548334</v>
+        <v>548434</v>
       </c>
       <c r="R60" t="n">
-        <v>7015001</v>
+        <v>7014792</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6587,6 +6577,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6613,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137882</v>
+        <v>129137860</v>
       </c>
       <c r="B61" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6648,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548510</v>
+        <v>548481</v>
       </c>
       <c r="R61" t="n">
-        <v>7015191</v>
+        <v>7015172</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6684,6 +6679,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7103,32 +7103,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137890</v>
+        <v>129137857</v>
       </c>
       <c r="B66" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548594</v>
+        <v>548502</v>
       </c>
       <c r="R66" t="n">
-        <v>7015211</v>
+        <v>7015176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7302,32 +7302,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137791</v>
+        <v>129137890</v>
       </c>
       <c r="B68" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548452</v>
+        <v>548594</v>
       </c>
       <c r="R68" t="n">
-        <v>7014769</v>
+        <v>7015211</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,6 +7373,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7399,32 +7404,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137811</v>
+        <v>129137791</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>105722</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7434,10 +7439,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548458</v>
+        <v>548452</v>
       </c>
       <c r="R69" t="n">
-        <v>7015205</v>
+        <v>7014769</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7496,32 +7501,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137858</v>
+        <v>129137811</v>
       </c>
       <c r="B70" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7531,10 +7536,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548400</v>
+        <v>548458</v>
       </c>
       <c r="R70" t="n">
-        <v>7015152</v>
+        <v>7015205</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7567,11 +7572,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7598,32 +7598,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137857</v>
+        <v>129137858</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>56913</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548502</v>
+        <v>548400</v>
       </c>
       <c r="R71" t="n">
-        <v>7015176</v>
+        <v>7015152</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7700,10 +7700,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137773</v>
+        <v>129137748</v>
       </c>
       <c r="B72" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7711,21 +7711,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548717</v>
+        <v>548710</v>
       </c>
       <c r="R72" t="n">
-        <v>7014991</v>
+        <v>7014904</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,6 +7771,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7797,32 +7802,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137886</v>
+        <v>129137780</v>
       </c>
       <c r="B73" t="n">
-        <v>80176</v>
+        <v>98659</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7832,10 +7837,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548498</v>
+        <v>548594</v>
       </c>
       <c r="R73" t="n">
-        <v>7015173</v>
+        <v>7015114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7868,6 +7873,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7894,10 +7904,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137850</v>
+        <v>129137902</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7905,21 +7915,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7929,10 +7939,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548629</v>
+        <v>548480</v>
       </c>
       <c r="R74" t="n">
-        <v>7015262</v>
+        <v>7015285</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7965,11 +7975,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,32 +8001,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137902</v>
+        <v>129137886</v>
       </c>
       <c r="B75" t="n">
-        <v>91544</v>
+        <v>80176</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8031,10 +8036,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548480</v>
+        <v>548498</v>
       </c>
       <c r="R75" t="n">
-        <v>7015285</v>
+        <v>7015173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8093,10 +8098,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137748</v>
+        <v>129137773</v>
       </c>
       <c r="B76" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,21 +8109,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8128,10 +8133,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548710</v>
+        <v>548717</v>
       </c>
       <c r="R76" t="n">
-        <v>7014904</v>
+        <v>7014991</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8164,11 +8169,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137780</v>
+        <v>129137850</v>
       </c>
       <c r="B77" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548594</v>
+        <v>548629</v>
       </c>
       <c r="R77" t="n">
-        <v>7015114</v>
+        <v>7015262</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137779</v>
+        <v>129137813</v>
       </c>
       <c r="B78" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548620</v>
+        <v>548374</v>
       </c>
       <c r="R78" t="n">
-        <v>7014685</v>
+        <v>7015064</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8368,11 +8368,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8399,7 +8394,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137813</v>
+        <v>129137818</v>
       </c>
       <c r="B79" t="n">
         <v>79035</v>
@@ -8434,10 +8429,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548374</v>
+        <v>548329</v>
       </c>
       <c r="R79" t="n">
-        <v>7015064</v>
+        <v>7014932</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8496,32 +8491,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137818</v>
+        <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8531,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548329</v>
+        <v>548620</v>
       </c>
       <c r="R80" t="n">
-        <v>7014932</v>
+        <v>7014685</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8567,6 +8562,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8690,32 +8690,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137871</v>
+        <v>129137796</v>
       </c>
       <c r="B82" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548457</v>
+        <v>548559</v>
       </c>
       <c r="R82" t="n">
-        <v>7014764</v>
+        <v>7014776</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8787,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137872</v>
+        <v>129137816</v>
       </c>
       <c r="B83" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548477</v>
+        <v>548400</v>
       </c>
       <c r="R83" t="n">
-        <v>7015144</v>
+        <v>7014970</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8884,32 +8884,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137900</v>
+        <v>129137805</v>
       </c>
       <c r="B84" t="n">
-        <v>105722</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548451</v>
+        <v>548613</v>
       </c>
       <c r="R84" t="n">
-        <v>7014746</v>
+        <v>7015186</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8981,10 +8981,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137805</v>
+        <v>129137745</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548613</v>
+        <v>548373</v>
       </c>
       <c r="R85" t="n">
-        <v>7015186</v>
+        <v>7014966</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9052,6 +9052,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9078,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137796</v>
+        <v>129137900</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>105722</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9113,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548559</v>
+        <v>548451</v>
       </c>
       <c r="R86" t="n">
-        <v>7014776</v>
+        <v>7014746</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9175,32 +9180,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137816</v>
+        <v>129137889</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9210,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548400</v>
+        <v>548440</v>
       </c>
       <c r="R87" t="n">
-        <v>7014970</v>
+        <v>7014752</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9246,6 +9251,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9272,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137745</v>
+        <v>129137781</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9307,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548373</v>
+        <v>548433</v>
       </c>
       <c r="R88" t="n">
-        <v>7014966</v>
+        <v>7014771</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9357,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9374,32 +9384,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137889</v>
+        <v>129137871</v>
       </c>
       <c r="B89" t="n">
-        <v>98659</v>
+        <v>97536</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9409,10 +9419,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548440</v>
+        <v>548457</v>
       </c>
       <c r="R89" t="n">
-        <v>7014752</v>
+        <v>7014764</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9445,11 +9455,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9476,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137781</v>
+        <v>129137872</v>
       </c>
       <c r="B90" t="n">
-        <v>98659</v>
+        <v>97536</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9511,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548433</v>
+        <v>548477</v>
       </c>
       <c r="R90" t="n">
-        <v>7014771</v>
+        <v>7015144</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9547,11 +9552,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9578,32 +9578,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137764</v>
+        <v>129137878</v>
       </c>
       <c r="B91" t="n">
-        <v>97536</v>
+        <v>80140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548590</v>
+        <v>548705</v>
       </c>
       <c r="R91" t="n">
-        <v>7015157</v>
+        <v>7014750</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137778</v>
+        <v>129137764</v>
       </c>
       <c r="B92" t="n">
-        <v>57827</v>
+        <v>97536</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9686,21 +9686,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548706</v>
+        <v>548590</v>
       </c>
       <c r="R92" t="n">
-        <v>7014864</v>
+        <v>7015157</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9746,11 +9746,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9777,10 +9772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137901</v>
+        <v>129137778</v>
       </c>
       <c r="B93" t="n">
-        <v>105722</v>
+        <v>57827</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9788,21 +9783,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>103031</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9812,10 +9807,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548281</v>
+        <v>548706</v>
       </c>
       <c r="R93" t="n">
-        <v>7015128</v>
+        <v>7014864</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9848,6 +9843,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9874,7 +9874,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137790</v>
+        <v>129137901</v>
       </c>
       <c r="B94" t="n">
         <v>105722</v>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548558</v>
+        <v>548281</v>
       </c>
       <c r="R94" t="n">
-        <v>7014771</v>
+        <v>7015128</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9971,32 +9971,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137878</v>
+        <v>129137790</v>
       </c>
       <c r="B95" t="n">
-        <v>80140</v>
+        <v>105722</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548705</v>
+        <v>548558</v>
       </c>
       <c r="R95" t="n">
-        <v>7014750</v>
+        <v>7014771</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10262,32 +10262,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137874</v>
+        <v>129137903</v>
       </c>
       <c r="B98" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548348</v>
+        <v>548633</v>
       </c>
       <c r="R98" t="n">
-        <v>7014988</v>
+        <v>7015045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10359,32 +10359,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137788</v>
+        <v>129137848</v>
       </c>
       <c r="B99" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548605</v>
+        <v>548598</v>
       </c>
       <c r="R99" t="n">
-        <v>7014687</v>
+        <v>7015227</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10461,32 +10461,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137912</v>
+        <v>129137863</v>
       </c>
       <c r="B100" t="n">
-        <v>96778</v>
+        <v>80141</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2869</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10496,10 +10496,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548604</v>
+        <v>548702</v>
       </c>
       <c r="R100" t="n">
-        <v>7015234</v>
+        <v>7014752</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10558,32 +10558,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137863</v>
+        <v>129137912</v>
       </c>
       <c r="B101" t="n">
-        <v>80141</v>
+        <v>96778</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>2869</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548702</v>
+        <v>548604</v>
       </c>
       <c r="R101" t="n">
-        <v>7014752</v>
+        <v>7015234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10655,32 +10655,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137903</v>
+        <v>129137788</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548633</v>
+        <v>548605</v>
       </c>
       <c r="R102" t="n">
-        <v>7015045</v>
+        <v>7014687</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10726,6 +10726,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10752,32 +10757,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137848</v>
+        <v>129137874</v>
       </c>
       <c r="B103" t="n">
-        <v>57723</v>
+        <v>97536</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10787,10 +10792,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548598</v>
+        <v>548348</v>
       </c>
       <c r="R103" t="n">
-        <v>7015227</v>
+        <v>7014988</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10823,11 +10828,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10854,10 +10854,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137883</v>
+        <v>129137753</v>
       </c>
       <c r="B104" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10865,21 +10865,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548499</v>
+        <v>548681</v>
       </c>
       <c r="R104" t="n">
-        <v>7015176</v>
+        <v>7015193</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10951,10 +10951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137753</v>
+        <v>129137840</v>
       </c>
       <c r="B105" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10962,21 +10962,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548681</v>
+        <v>548660</v>
       </c>
       <c r="R105" t="n">
-        <v>7015193</v>
+        <v>7014820</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11048,10 +11048,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137840</v>
+        <v>129137883</v>
       </c>
       <c r="B106" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11059,21 +11059,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548660</v>
+        <v>548499</v>
       </c>
       <c r="R106" t="n">
-        <v>7014820</v>
+        <v>7015176</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11242,7 +11242,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137844</v>
+        <v>129137847</v>
       </c>
       <c r="B108" t="n">
         <v>57723</v>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548672</v>
+        <v>548490</v>
       </c>
       <c r="R108" t="n">
-        <v>7014893</v>
+        <v>7014739</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11344,7 +11344,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137847</v>
+        <v>129137844</v>
       </c>
       <c r="B109" t="n">
         <v>57723</v>
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548490</v>
+        <v>548672</v>
       </c>
       <c r="R109" t="n">
-        <v>7014739</v>
+        <v>7014893</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137751</v>
+        <v>129137740</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548268</v>
+        <v>548618</v>
       </c>
       <c r="R6" t="n">
-        <v>7014891</v>
+        <v>7015211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137817</v>
+        <v>129137751</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548367</v>
+        <v>548268</v>
       </c>
       <c r="R7" t="n">
-        <v>7014944</v>
+        <v>7014891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,6 +1317,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,32 +1348,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137815</v>
+        <v>129137787</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548398</v>
+        <v>548366</v>
       </c>
       <c r="R8" t="n">
-        <v>7015004</v>
+        <v>7014942</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1423,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137797</v>
+        <v>129137870</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>97546</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548657</v>
+        <v>548358</v>
       </c>
       <c r="R9" t="n">
-        <v>7014768</v>
+        <v>7014777</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137740</v>
+        <v>129137817</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1558,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548618</v>
+        <v>548367</v>
       </c>
       <c r="R10" t="n">
-        <v>7015211</v>
+        <v>7014944</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137787</v>
+        <v>129137797</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548366</v>
+        <v>548657</v>
       </c>
       <c r="R11" t="n">
-        <v>7014942</v>
+        <v>7014768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137870</v>
+        <v>129137815</v>
       </c>
       <c r="B12" t="n">
-        <v>97536</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548358</v>
+        <v>548398</v>
       </c>
       <c r="R12" t="n">
-        <v>7014777</v>
+        <v>7015004</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B13" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R13" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137804</v>
+        <v>129137794</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,21 +1951,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548550</v>
+        <v>548459</v>
       </c>
       <c r="R14" t="n">
-        <v>7015142</v>
+        <v>7015186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2040,7 @@
         <v>129137795</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>129137738</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,32 +2241,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137869</v>
+        <v>129137820</v>
       </c>
       <c r="B17" t="n">
-        <v>97536</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548335</v>
+        <v>548328</v>
       </c>
       <c r="R17" t="n">
-        <v>7014782</v>
+        <v>7014882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,6 +2312,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137820</v>
+        <v>129137801</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548328</v>
+        <v>548686</v>
       </c>
       <c r="R18" t="n">
-        <v>7014882</v>
+        <v>7014817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,11 +2414,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,10 +2440,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137801</v>
+        <v>129137802</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548686</v>
+        <v>548499</v>
       </c>
       <c r="R19" t="n">
-        <v>7014817</v>
+        <v>7014902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,32 +2537,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137802</v>
+        <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>97546</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548499</v>
+        <v>548335</v>
       </c>
       <c r="R20" t="n">
-        <v>7014902</v>
+        <v>7014782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137744</v>
+        <v>129137771</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>80172</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548511</v>
+        <v>548360</v>
       </c>
       <c r="R21" t="n">
-        <v>7015241</v>
+        <v>7014942</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,11 +2705,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2736,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137771</v>
+        <v>129137862</v>
       </c>
       <c r="B22" t="n">
-        <v>80168</v>
+        <v>80173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,21 +2742,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548360</v>
+        <v>548497</v>
       </c>
       <c r="R22" t="n">
-        <v>7014942</v>
+        <v>7015181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137862</v>
+        <v>129137906</v>
       </c>
       <c r="B23" t="n">
-        <v>80169</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548497</v>
+        <v>548693</v>
       </c>
       <c r="R23" t="n">
-        <v>7015181</v>
+        <v>7014874</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137906</v>
+        <v>129137819</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548693</v>
+        <v>548318</v>
       </c>
       <c r="R24" t="n">
-        <v>7014874</v>
+        <v>7014904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3027,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137819</v>
+        <v>129137744</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,21 +3033,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548318</v>
+        <v>548511</v>
       </c>
       <c r="R25" t="n">
-        <v>7014904</v>
+        <v>7015241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,6 +3093,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3127,7 +3127,7 @@
         <v>129137750</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3226,32 +3226,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B27" t="n">
-        <v>80168</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R27" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137810</v>
+        <v>129137806</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548538</v>
+        <v>548632</v>
       </c>
       <c r="R28" t="n">
-        <v>7015259</v>
+        <v>7015246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,32 +3420,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137806</v>
+        <v>129137876</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>80172</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548632</v>
+        <v>548475</v>
       </c>
       <c r="R29" t="n">
-        <v>7015246</v>
+        <v>7015265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,32 +3517,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137749</v>
+        <v>129125929</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>97540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548618</v>
+        <v>548372</v>
       </c>
       <c r="R30" t="n">
-        <v>7015211</v>
+        <v>7014829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,11 +3588,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3619,32 +3614,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129125929</v>
+        <v>129137749</v>
       </c>
       <c r="B31" t="n">
-        <v>97530</v>
+        <v>57885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3649,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548372</v>
+        <v>548618</v>
       </c>
       <c r="R31" t="n">
-        <v>7014829</v>
+        <v>7015211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,6 +3685,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3716,32 +3716,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137789</v>
+        <v>129137800</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548461</v>
+        <v>548708</v>
       </c>
       <c r="R32" t="n">
-        <v>7015210</v>
+        <v>7014937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3818,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R33" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,11 +3889,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3920,49 +3915,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129126213</v>
+        <v>129137849</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548265</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7014876</v>
+        <v>7015247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,6 +3986,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,32 +4017,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137800</v>
+        <v>129137789</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4052,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548708</v>
+        <v>548461</v>
       </c>
       <c r="R35" t="n">
-        <v>7014937</v>
+        <v>7015210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4096,7 +4092,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,32 +4119,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4154,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R36" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4190,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4220,45 +4221,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137849</v>
+        <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548629</v>
+        <v>548265</v>
       </c>
       <c r="R37" t="n">
-        <v>7015247</v>
+        <v>7014876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,11 +4296,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4325,7 +4325,7 @@
         <v>129137774</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>129137772</v>
       </c>
       <c r="B39" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137812</v>
+        <v>129137895</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548395</v>
+        <v>548277</v>
       </c>
       <c r="R40" t="n">
-        <v>7015086</v>
+        <v>7015126</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137846</v>
+        <v>129137812</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548317</v>
+        <v>548395</v>
       </c>
       <c r="R41" t="n">
-        <v>7014833</v>
+        <v>7015086</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137895</v>
+        <v>129137846</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548277</v>
+        <v>548317</v>
       </c>
       <c r="R42" t="n">
-        <v>7015126</v>
+        <v>7014833</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,32 +4817,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137783</v>
+        <v>129137843</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548595</v>
+        <v>548488</v>
       </c>
       <c r="R43" t="n">
-        <v>7015162</v>
+        <v>7015296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,11 +4888,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4919,32 +4914,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137891</v>
+        <v>129137909</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>82902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4954,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548627</v>
+        <v>548610</v>
       </c>
       <c r="R44" t="n">
-        <v>7015253</v>
+        <v>7015229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4990,11 +4985,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5021,32 +5011,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137792</v>
+        <v>129137822</v>
       </c>
       <c r="B45" t="n">
-        <v>105722</v>
+        <v>57646</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>100001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5056,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548368</v>
+        <v>548346</v>
       </c>
       <c r="R45" t="n">
-        <v>7014860</v>
+        <v>7015026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5092,11 +5082,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5126,7 +5111,7 @@
         <v>129137786</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5225,32 +5210,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137766</v>
+        <v>129137891</v>
       </c>
       <c r="B47" t="n">
-        <v>97536</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5260,10 +5245,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548366</v>
+        <v>548627</v>
       </c>
       <c r="R47" t="n">
-        <v>7014942</v>
+        <v>7015253</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5300,7 +5285,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 exemplar</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5327,32 +5312,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137843</v>
+        <v>129137783</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5362,10 +5347,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548488</v>
+        <v>548595</v>
       </c>
       <c r="R48" t="n">
-        <v>7015296</v>
+        <v>7015162</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5398,6 +5383,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5424,10 +5414,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137909</v>
+        <v>129137803</v>
       </c>
       <c r="B49" t="n">
-        <v>82898</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5435,21 +5425,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5459,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548610</v>
+        <v>548467</v>
       </c>
       <c r="R49" t="n">
-        <v>7015229</v>
+        <v>7014995</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5521,10 +5511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137803</v>
+        <v>129137814</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5556,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548467</v>
+        <v>548376</v>
       </c>
       <c r="R50" t="n">
-        <v>7014995</v>
+        <v>7015053</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5618,32 +5608,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137814</v>
+        <v>129137792</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>105732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5653,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548376</v>
+        <v>548368</v>
       </c>
       <c r="R51" t="n">
-        <v>7015053</v>
+        <v>7014860</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5689,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5715,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137822</v>
+        <v>129137766</v>
       </c>
       <c r="B52" t="n">
-        <v>57644</v>
+        <v>97546</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100001</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5750,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548346</v>
+        <v>548366</v>
       </c>
       <c r="R52" t="n">
-        <v>7015026</v>
+        <v>7014942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5786,6 +5781,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137877</v>
+        <v>129137905</v>
       </c>
       <c r="B53" t="n">
-        <v>80168</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548334</v>
+        <v>548618</v>
       </c>
       <c r="R53" t="n">
-        <v>7015001</v>
+        <v>7015116</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137882</v>
+        <v>129126001</v>
       </c>
       <c r="B54" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5920,21 +5920,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548510</v>
+        <v>548299</v>
       </c>
       <c r="R54" t="n">
-        <v>7015191</v>
+        <v>7014876</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6006,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137905</v>
+        <v>129137877</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>80172</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548618</v>
+        <v>548334</v>
       </c>
       <c r="R55" t="n">
-        <v>7015116</v>
+        <v>7015001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129126001</v>
+        <v>129137882</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548299</v>
+        <v>548510</v>
       </c>
       <c r="R56" t="n">
-        <v>7014876</v>
+        <v>7015191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6203,7 +6203,7 @@
         <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>129137845</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>129137746</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137859</v>
+        <v>129137860</v>
       </c>
       <c r="B60" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548434</v>
+        <v>548481</v>
       </c>
       <c r="R60" t="n">
-        <v>7014792</v>
+        <v>7015172</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137860</v>
+        <v>129137859</v>
       </c>
       <c r="B61" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548481</v>
+        <v>548434</v>
       </c>
       <c r="R61" t="n">
-        <v>7015172</v>
+        <v>7014792</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6710,10 +6710,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B62" t="n">
-        <v>92819</v>
+        <v>80172</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R62" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B63" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R63" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,10 +6904,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137875</v>
+        <v>129137910</v>
       </c>
       <c r="B64" t="n">
-        <v>80168</v>
+        <v>92826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6915,21 +6915,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548581</v>
+        <v>548510</v>
       </c>
       <c r="R64" t="n">
-        <v>7015017</v>
+        <v>7014986</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
         <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7103,32 +7103,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137857</v>
+        <v>129137858</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>56915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548502</v>
+        <v>548400</v>
       </c>
       <c r="R66" t="n">
-        <v>7015176</v>
+        <v>7015152</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7205,32 +7205,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137762</v>
+        <v>129137890</v>
       </c>
       <c r="B67" t="n">
-        <v>97536</v>
+        <v>98669</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548603</v>
+        <v>548594</v>
       </c>
       <c r="R67" t="n">
-        <v>7014709</v>
+        <v>7015211</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7276,6 +7276,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,32 +7307,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137890</v>
+        <v>129137791</v>
       </c>
       <c r="B68" t="n">
-        <v>98659</v>
+        <v>105732</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7342,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548594</v>
+        <v>548452</v>
       </c>
       <c r="R68" t="n">
-        <v>7015211</v>
+        <v>7014769</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,11 +7378,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7404,10 +7404,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137791</v>
+        <v>129137762</v>
       </c>
       <c r="B69" t="n">
-        <v>105722</v>
+        <v>97546</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7415,21 +7415,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548452</v>
+        <v>548603</v>
       </c>
       <c r="R69" t="n">
-        <v>7014769</v>
+        <v>7014709</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7504,7 +7504,7 @@
         <v>129137811</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7598,32 +7598,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137858</v>
+        <v>129137857</v>
       </c>
       <c r="B71" t="n">
-        <v>56913</v>
+        <v>57725</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548400</v>
+        <v>548502</v>
       </c>
       <c r="R71" t="n">
-        <v>7015152</v>
+        <v>7015176</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>1 ex, förbiflygande</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7700,10 +7700,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137748</v>
+        <v>129137773</v>
       </c>
       <c r="B72" t="n">
-        <v>57883</v>
+        <v>80144</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7711,21 +7711,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548710</v>
+        <v>548717</v>
       </c>
       <c r="R72" t="n">
-        <v>7014904</v>
+        <v>7014991</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,11 +7771,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7802,32 +7797,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137780</v>
+        <v>129137886</v>
       </c>
       <c r="B73" t="n">
-        <v>98659</v>
+        <v>80180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7837,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548594</v>
+        <v>548498</v>
       </c>
       <c r="R73" t="n">
-        <v>7015114</v>
+        <v>7015173</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7873,11 +7868,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7907,7 +7897,7 @@
         <v>129137902</v>
       </c>
       <c r="B74" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8001,32 +7991,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137886</v>
+        <v>129137850</v>
       </c>
       <c r="B75" t="n">
-        <v>80176</v>
+        <v>57725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8036,10 +8026,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548498</v>
+        <v>548629</v>
       </c>
       <c r="R75" t="n">
-        <v>7015173</v>
+        <v>7015262</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8072,6 +8062,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8098,10 +8093,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137773</v>
+        <v>129137748</v>
       </c>
       <c r="B76" t="n">
-        <v>80140</v>
+        <v>57885</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8109,21 +8104,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8133,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548717</v>
+        <v>548710</v>
       </c>
       <c r="R76" t="n">
-        <v>7014991</v>
+        <v>7014904</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8169,6 +8164,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137850</v>
+        <v>129137780</v>
       </c>
       <c r="B77" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548629</v>
+        <v>548594</v>
       </c>
       <c r="R77" t="n">
-        <v>7015262</v>
+        <v>7015114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,10 +8297,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137813</v>
+        <v>129137818</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548374</v>
+        <v>548329</v>
       </c>
       <c r="R78" t="n">
-        <v>7015064</v>
+        <v>7014932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,32 +8394,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137818</v>
+        <v>129137779</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548329</v>
+        <v>548620</v>
       </c>
       <c r="R79" t="n">
-        <v>7014932</v>
+        <v>7014685</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8465,6 +8465,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8491,32 +8496,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137779</v>
+        <v>129137759</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>97540</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8526,10 +8531,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548620</v>
+        <v>548487</v>
       </c>
       <c r="R80" t="n">
-        <v>7014685</v>
+        <v>7014855</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8562,11 +8567,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8593,32 +8593,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137759</v>
+        <v>129137813</v>
       </c>
       <c r="B81" t="n">
-        <v>97530</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548487</v>
+        <v>548374</v>
       </c>
       <c r="R81" t="n">
-        <v>7014855</v>
+        <v>7015064</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8693,7 +8693,7 @@
         <v>129137796</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137816</v>
+        <v>129137805</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548400</v>
+        <v>548613</v>
       </c>
       <c r="R83" t="n">
-        <v>7014970</v>
+        <v>7015186</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8884,10 +8884,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137805</v>
+        <v>129137816</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548613</v>
+        <v>548400</v>
       </c>
       <c r="R84" t="n">
-        <v>7015186</v>
+        <v>7014970</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8984,7 +8984,7 @@
         <v>129137745</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9083,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137900</v>
+        <v>129137781</v>
       </c>
       <c r="B86" t="n">
-        <v>105722</v>
+        <v>98669</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548451</v>
+        <v>548433</v>
       </c>
       <c r="R86" t="n">
-        <v>7014746</v>
+        <v>7014771</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9154,6 +9154,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9183,7 +9188,7 @@
         <v>129137889</v>
       </c>
       <c r="B87" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,32 +9287,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137781</v>
+        <v>129137900</v>
       </c>
       <c r="B88" t="n">
-        <v>98659</v>
+        <v>105732</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9322,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548433</v>
+        <v>548451</v>
       </c>
       <c r="R88" t="n">
-        <v>7014771</v>
+        <v>7014746</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,11 +9358,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9387,7 +9387,7 @@
         <v>129137871</v>
       </c>
       <c r="B89" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>129137872</v>
       </c>
       <c r="B90" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>129137878</v>
       </c>
       <c r="B91" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137764</v>
+        <v>129137901</v>
       </c>
       <c r="B92" t="n">
-        <v>97536</v>
+        <v>105732</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9686,21 +9686,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548590</v>
+        <v>548281</v>
       </c>
       <c r="R92" t="n">
-        <v>7015157</v>
+        <v>7015128</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137778</v>
+        <v>129137790</v>
       </c>
       <c r="B93" t="n">
-        <v>57827</v>
+        <v>105732</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9783,21 +9783,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103031</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548706</v>
+        <v>548558</v>
       </c>
       <c r="R93" t="n">
-        <v>7014864</v>
+        <v>7014771</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9843,11 +9843,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9874,10 +9869,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137901</v>
+        <v>129137764</v>
       </c>
       <c r="B94" t="n">
-        <v>105722</v>
+        <v>97546</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9885,21 +9880,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9909,10 +9904,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548281</v>
+        <v>548590</v>
       </c>
       <c r="R94" t="n">
-        <v>7015128</v>
+        <v>7015157</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9971,10 +9966,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137790</v>
+        <v>129137778</v>
       </c>
       <c r="B95" t="n">
-        <v>105722</v>
+        <v>57829</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9982,21 +9977,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221144</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10006,10 +10001,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548558</v>
+        <v>548706</v>
       </c>
       <c r="R95" t="n">
-        <v>7014771</v>
+        <v>7014864</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10042,6 +10037,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10068,27 +10068,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137911</v>
+        <v>129137908</v>
       </c>
       <c r="B96" t="n">
-        <v>80175</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10103,10 +10103,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548512</v>
+        <v>548306</v>
       </c>
       <c r="R96" t="n">
-        <v>7015192</v>
+        <v>7015082</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10165,27 +10165,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>80179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R97" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10262,32 +10262,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137903</v>
+        <v>129137912</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>96788</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548633</v>
+        <v>548604</v>
       </c>
       <c r="R98" t="n">
-        <v>7015045</v>
+        <v>7015234</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10359,10 +10359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137848</v>
+        <v>129137863</v>
       </c>
       <c r="B99" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548598</v>
+        <v>548702</v>
       </c>
       <c r="R99" t="n">
-        <v>7015227</v>
+        <v>7014752</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10430,11 +10430,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10461,10 +10456,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137863</v>
+        <v>129137903</v>
       </c>
       <c r="B100" t="n">
-        <v>80141</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10472,21 +10467,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10496,10 +10491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548702</v>
+        <v>548633</v>
       </c>
       <c r="R100" t="n">
-        <v>7014752</v>
+        <v>7015045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10558,32 +10553,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137912</v>
+        <v>129137848</v>
       </c>
       <c r="B101" t="n">
-        <v>96778</v>
+        <v>57725</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10593,10 +10588,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548604</v>
+        <v>548598</v>
       </c>
       <c r="R101" t="n">
-        <v>7015234</v>
+        <v>7015227</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10629,6 +10624,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10658,7 +10658,7 @@
         <v>129137788</v>
       </c>
       <c r="B102" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>129137874</v>
       </c>
       <c r="B103" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>129137753</v>
       </c>
       <c r="B104" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>129137840</v>
       </c>
       <c r="B105" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>129137883</v>
       </c>
       <c r="B106" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>129137758</v>
       </c>
       <c r="B107" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137847</v>
+        <v>129137768</v>
       </c>
       <c r="B108" t="n">
-        <v>57723</v>
+        <v>80172</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548490</v>
+        <v>548723</v>
       </c>
       <c r="R108" t="n">
-        <v>7014739</v>
+        <v>7014940</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11313,11 +11313,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11344,10 +11339,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137844</v>
+        <v>129137847</v>
       </c>
       <c r="B109" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11379,10 +11374,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548672</v>
+        <v>548490</v>
       </c>
       <c r="R109" t="n">
-        <v>7014893</v>
+        <v>7014739</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11419,7 +11414,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11446,32 +11441,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137768</v>
+        <v>129137844</v>
       </c>
       <c r="B110" t="n">
-        <v>80168</v>
+        <v>57725</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11481,10 +11476,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548723</v>
+        <v>548672</v>
       </c>
       <c r="R110" t="n">
-        <v>7014940</v>
+        <v>7014893</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11517,6 +11512,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11546,7 +11546,7 @@
         <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -2634,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137771</v>
+        <v>129137906</v>
       </c>
       <c r="B21" t="n">
-        <v>80172</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548360</v>
+        <v>548693</v>
       </c>
       <c r="R21" t="n">
-        <v>7014942</v>
+        <v>7014874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,32 +2731,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B22" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R22" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137906</v>
+        <v>129137771</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>80172</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548693</v>
+        <v>548360</v>
       </c>
       <c r="R23" t="n">
-        <v>7014874</v>
+        <v>7014942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137819</v>
+        <v>129137862</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548318</v>
+        <v>548497</v>
       </c>
       <c r="R24" t="n">
-        <v>7014904</v>
+        <v>7015181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3915,32 +3915,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137849</v>
+        <v>129137789</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548461</v>
       </c>
       <c r="R34" t="n">
-        <v>7015247</v>
+        <v>7015210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,7 +4017,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137789</v>
+        <v>129137896</v>
       </c>
       <c r="B35" t="n">
         <v>98669</v>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548461</v>
+        <v>548260</v>
       </c>
       <c r="R35" t="n">
-        <v>7015210</v>
+        <v>7014898</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,7 +4119,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137896</v>
+        <v>129126213</v>
       </c>
       <c r="B36" t="n">
         <v>98669</v>
@@ -4147,17 +4147,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548260</v>
+        <v>548265</v>
       </c>
       <c r="R36" t="n">
-        <v>7014898</v>
+        <v>7014876</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4221,49 +4220,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129126213</v>
+        <v>129137849</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548265</v>
+        <v>548629</v>
       </c>
       <c r="R37" t="n">
-        <v>7014876</v>
+        <v>7015247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,6 +4291,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137843</v>
+        <v>129137822</v>
       </c>
       <c r="B43" t="n">
-        <v>91533</v>
+        <v>57646</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548488</v>
+        <v>548346</v>
       </c>
       <c r="R43" t="n">
-        <v>7015296</v>
+        <v>7015026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137909</v>
+        <v>129137786</v>
       </c>
       <c r="B44" t="n">
-        <v>82902</v>
+        <v>98669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548610</v>
+        <v>548402</v>
       </c>
       <c r="R44" t="n">
-        <v>7015229</v>
+        <v>7015096</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,6 +4985,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,32 +5016,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137822</v>
+        <v>129137891</v>
       </c>
       <c r="B45" t="n">
-        <v>57646</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5051,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548346</v>
+        <v>548627</v>
       </c>
       <c r="R45" t="n">
-        <v>7015026</v>
+        <v>7015253</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,6 +5087,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5108,7 +5118,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137786</v>
+        <v>129137783</v>
       </c>
       <c r="B46" t="n">
         <v>98669</v>
@@ -5143,10 +5153,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548402</v>
+        <v>548595</v>
       </c>
       <c r="R46" t="n">
-        <v>7015096</v>
+        <v>7015162</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5183,7 +5193,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15 stycken kan finnas mer I mossan</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5210,32 +5220,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137891</v>
+        <v>129137792</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>105732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5245,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548627</v>
+        <v>548368</v>
       </c>
       <c r="R47" t="n">
-        <v>7015253</v>
+        <v>7014860</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5285,7 +5295,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5312,32 +5322,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137783</v>
+        <v>129137766</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>97546</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5347,10 +5357,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548595</v>
+        <v>548366</v>
       </c>
       <c r="R48" t="n">
-        <v>7015162</v>
+        <v>7014942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5387,7 +5397,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5414,10 +5424,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137803</v>
+        <v>129137843</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>91533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5425,21 +5435,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548467</v>
+        <v>548488</v>
       </c>
       <c r="R49" t="n">
-        <v>7014995</v>
+        <v>7015296</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,10 +5521,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137814</v>
+        <v>129137909</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>82902</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5522,21 +5532,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5556,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548376</v>
+        <v>548610</v>
       </c>
       <c r="R50" t="n">
-        <v>7015053</v>
+        <v>7015229</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5608,32 +5618,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137792</v>
+        <v>129137803</v>
       </c>
       <c r="B51" t="n">
-        <v>105732</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5653,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548368</v>
+        <v>548467</v>
       </c>
       <c r="R51" t="n">
-        <v>7014860</v>
+        <v>7014995</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,11 +5689,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,32 +5715,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137766</v>
+        <v>129137814</v>
       </c>
       <c r="B52" t="n">
-        <v>97546</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5750,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548366</v>
+        <v>548376</v>
       </c>
       <c r="R52" t="n">
-        <v>7014942</v>
+        <v>7015053</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,11 +5786,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6710,10 +6710,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137769</v>
+        <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>80172</v>
+        <v>92826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548487</v>
+        <v>548510</v>
       </c>
       <c r="R62" t="n">
-        <v>7015073</v>
+        <v>7014986</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137875</v>
+        <v>129137769</v>
       </c>
       <c r="B63" t="n">
         <v>80172</v>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548581</v>
+        <v>548487</v>
       </c>
       <c r="R63" t="n">
-        <v>7015017</v>
+        <v>7015073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,10 +6904,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137910</v>
+        <v>129137875</v>
       </c>
       <c r="B64" t="n">
-        <v>92826</v>
+        <v>80172</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6915,21 +6915,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548510</v>
+        <v>548581</v>
       </c>
       <c r="R64" t="n">
-        <v>7014986</v>
+        <v>7015017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137773</v>
+        <v>129137748</v>
       </c>
       <c r="B72" t="n">
-        <v>80144</v>
+        <v>57885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7711,21 +7711,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548717</v>
+        <v>548710</v>
       </c>
       <c r="R72" t="n">
-        <v>7014991</v>
+        <v>7014904</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,6 +7771,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7797,32 +7802,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137886</v>
+        <v>129137773</v>
       </c>
       <c r="B73" t="n">
-        <v>80180</v>
+        <v>80144</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7832,10 +7837,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548498</v>
+        <v>548717</v>
       </c>
       <c r="R73" t="n">
-        <v>7015173</v>
+        <v>7014991</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7894,32 +7899,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137902</v>
+        <v>129137886</v>
       </c>
       <c r="B74" t="n">
-        <v>91551</v>
+        <v>80180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7929,10 +7934,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548480</v>
+        <v>548498</v>
       </c>
       <c r="R74" t="n">
-        <v>7015285</v>
+        <v>7015173</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7991,10 +7996,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137850</v>
+        <v>129137902</v>
       </c>
       <c r="B75" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8002,21 +8007,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8026,10 +8031,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548629</v>
+        <v>548480</v>
       </c>
       <c r="R75" t="n">
-        <v>7015262</v>
+        <v>7015285</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8062,11 +8067,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8093,10 +8093,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137748</v>
+        <v>129137850</v>
       </c>
       <c r="B76" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548710</v>
+        <v>548629</v>
       </c>
       <c r="R76" t="n">
-        <v>7014904</v>
+        <v>7015262</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8297,7 +8297,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137818</v>
+        <v>129137813</v>
       </c>
       <c r="B78" t="n">
         <v>79039</v>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548329</v>
+        <v>548374</v>
       </c>
       <c r="R78" t="n">
-        <v>7014932</v>
+        <v>7015064</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,32 +8394,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B79" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R79" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8465,11 +8465,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8496,32 +8491,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137759</v>
+        <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>97540</v>
+        <v>98669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8531,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548487</v>
+        <v>548620</v>
       </c>
       <c r="R80" t="n">
-        <v>7014855</v>
+        <v>7014685</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8567,6 +8562,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8593,32 +8593,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137813</v>
+        <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>97540</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548374</v>
+        <v>548487</v>
       </c>
       <c r="R81" t="n">
-        <v>7015064</v>
+        <v>7014855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137740</v>
+        <v>129137751</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548618</v>
+        <v>548268</v>
       </c>
       <c r="R6" t="n">
-        <v>7015211</v>
+        <v>7014891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137751</v>
+        <v>129137817</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548268</v>
+        <v>548367</v>
       </c>
       <c r="R7" t="n">
-        <v>7014891</v>
+        <v>7014944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,11 +1317,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,32 +1343,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137787</v>
+        <v>129137797</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548366</v>
+        <v>548657</v>
       </c>
       <c r="R8" t="n">
-        <v>7014942</v>
+        <v>7014768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,11 +1414,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,32 +1440,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137870</v>
+        <v>129137815</v>
       </c>
       <c r="B9" t="n">
-        <v>97546</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548358</v>
+        <v>548398</v>
       </c>
       <c r="R9" t="n">
-        <v>7014777</v>
+        <v>7015004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,6 +1511,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137817</v>
+        <v>129137740</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1582,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548367</v>
+        <v>548618</v>
       </c>
       <c r="R10" t="n">
-        <v>7014944</v>
+        <v>7015211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137797</v>
+        <v>129137787</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548657</v>
+        <v>548366</v>
       </c>
       <c r="R11" t="n">
-        <v>7014768</v>
+        <v>7014942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137815</v>
+        <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>97553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548398</v>
+        <v>548358</v>
       </c>
       <c r="R12" t="n">
-        <v>7015004</v>
+        <v>7014777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1817,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137804</v>
+        <v>129137794</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548550</v>
+        <v>548459</v>
       </c>
       <c r="R13" t="n">
-        <v>7015142</v>
+        <v>7015186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137794</v>
+        <v>129137795</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,21 +1951,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548459</v>
+        <v>548538</v>
       </c>
       <c r="R14" t="n">
-        <v>7015186</v>
+        <v>7014770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,6 +2011,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,7 +2042,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137795</v>
+        <v>129137804</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -2072,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548538</v>
+        <v>548550</v>
       </c>
       <c r="R15" t="n">
-        <v>7014770</v>
+        <v>7015142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,11 +2113,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2540,7 +2540,7 @@
         <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137771</v>
+        <v>129137744</v>
       </c>
       <c r="B23" t="n">
-        <v>80172</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548360</v>
+        <v>548511</v>
       </c>
       <c r="R23" t="n">
-        <v>7014942</v>
+        <v>7015241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,6 +2899,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2925,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137862</v>
+        <v>129137771</v>
       </c>
       <c r="B24" t="n">
-        <v>80173</v>
+        <v>80172</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2941,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548497</v>
+        <v>548360</v>
       </c>
       <c r="R24" t="n">
-        <v>7015181</v>
+        <v>7014942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,32 +3027,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137744</v>
+        <v>129137862</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>80173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3057,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548511</v>
+        <v>548497</v>
       </c>
       <c r="R25" t="n">
-        <v>7015241</v>
+        <v>7015181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,11 +3098,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,32 +3226,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137810</v>
+        <v>129125929</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>97547</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548538</v>
+        <v>548372</v>
       </c>
       <c r="R27" t="n">
-        <v>7015259</v>
+        <v>7014829</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137806</v>
+        <v>129137810</v>
       </c>
       <c r="B28" t="n">
         <v>79039</v>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548632</v>
+        <v>548538</v>
       </c>
       <c r="R28" t="n">
-        <v>7015246</v>
+        <v>7015259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,32 +3420,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137876</v>
+        <v>129137806</v>
       </c>
       <c r="B29" t="n">
-        <v>80172</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548475</v>
+        <v>548632</v>
       </c>
       <c r="R29" t="n">
-        <v>7015265</v>
+        <v>7015246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,10 +3517,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129125929</v>
+        <v>129137876</v>
       </c>
       <c r="B30" t="n">
-        <v>97540</v>
+        <v>80172</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,21 +3528,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548372</v>
+        <v>548475</v>
       </c>
       <c r="R30" t="n">
-        <v>7014829</v>
+        <v>7015265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3915,32 +3915,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137789</v>
+        <v>129137849</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548461</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015210</v>
+        <v>7015247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137896</v>
+        <v>129137789</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548260</v>
+        <v>548461</v>
       </c>
       <c r="R35" t="n">
-        <v>7014898</v>
+        <v>7015210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,10 +4119,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129126213</v>
+        <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4147,21 +4147,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548265</v>
+        <v>548260</v>
       </c>
       <c r="R36" t="n">
-        <v>7014876</v>
+        <v>7014898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4190,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4220,45 +4221,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137849</v>
+        <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548629</v>
+        <v>548265</v>
       </c>
       <c r="R37" t="n">
-        <v>7015247</v>
+        <v>7014876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,11 +4296,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137895</v>
+        <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548277</v>
+        <v>548395</v>
       </c>
       <c r="R40" t="n">
-        <v>7015126</v>
+        <v>7015086</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137812</v>
+        <v>129137846</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548395</v>
+        <v>548317</v>
       </c>
       <c r="R41" t="n">
-        <v>7015086</v>
+        <v>7014833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137846</v>
+        <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548317</v>
+        <v>548277</v>
       </c>
       <c r="R42" t="n">
-        <v>7014833</v>
+        <v>7015126</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137822</v>
+        <v>129137803</v>
       </c>
       <c r="B43" t="n">
-        <v>57646</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548346</v>
+        <v>548467</v>
       </c>
       <c r="R43" t="n">
-        <v>7015026</v>
+        <v>7014995</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137786</v>
+        <v>129137814</v>
       </c>
       <c r="B44" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548402</v>
+        <v>548376</v>
       </c>
       <c r="R44" t="n">
-        <v>7015096</v>
+        <v>7015053</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,11 +4985,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5016,32 +5011,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5051,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R45" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5087,11 +5082,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5118,32 +5108,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137783</v>
+        <v>129137909</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>82871</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5153,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548595</v>
+        <v>548610</v>
       </c>
       <c r="R46" t="n">
-        <v>7015162</v>
+        <v>7015229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,11 +5179,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5220,32 +5205,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137792</v>
+        <v>129137822</v>
       </c>
       <c r="B47" t="n">
-        <v>105732</v>
+        <v>57646</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>100001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5255,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548368</v>
+        <v>548346</v>
       </c>
       <c r="R47" t="n">
-        <v>7014860</v>
+        <v>7015026</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,11 +5276,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5322,32 +5302,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137766</v>
+        <v>129137783</v>
       </c>
       <c r="B48" t="n">
-        <v>97546</v>
+        <v>98676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5357,10 +5337,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548366</v>
+        <v>548595</v>
       </c>
       <c r="R48" t="n">
-        <v>7014942</v>
+        <v>7015162</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5397,7 +5377,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>5 exemplar</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5424,32 +5404,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B49" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5459,10 +5439,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R49" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5495,6 +5475,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5521,32 +5506,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137909</v>
+        <v>129137786</v>
       </c>
       <c r="B50" t="n">
-        <v>82902</v>
+        <v>98676</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5556,10 +5541,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548610</v>
+        <v>548402</v>
       </c>
       <c r="R50" t="n">
-        <v>7015229</v>
+        <v>7015096</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5592,6 +5577,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5618,32 +5608,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137803</v>
+        <v>129137792</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>105739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5653,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548467</v>
+        <v>548368</v>
       </c>
       <c r="R51" t="n">
-        <v>7014995</v>
+        <v>7014860</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5689,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5715,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137814</v>
+        <v>129137766</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>97553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5750,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548376</v>
+        <v>548366</v>
       </c>
       <c r="R52" t="n">
-        <v>7015053</v>
+        <v>7014942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5786,6 +5781,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137905</v>
+        <v>129137877</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>80172</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548618</v>
+        <v>548334</v>
       </c>
       <c r="R53" t="n">
-        <v>7015116</v>
+        <v>7015001</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137877</v>
+        <v>129137882</v>
       </c>
       <c r="B55" t="n">
-        <v>80172</v>
+        <v>80144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548334</v>
+        <v>548510</v>
       </c>
       <c r="R55" t="n">
-        <v>7015001</v>
+        <v>7015191</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137882</v>
+        <v>129137860</v>
       </c>
       <c r="B56" t="n">
-        <v>80144</v>
+        <v>57885</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548510</v>
+        <v>548481</v>
       </c>
       <c r="R56" t="n">
-        <v>7015191</v>
+        <v>7015172</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6174,6 +6174,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6200,10 +6205,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137739</v>
+        <v>129137859</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6216,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6240,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548460</v>
+        <v>548434</v>
       </c>
       <c r="R57" t="n">
-        <v>7014976</v>
+        <v>7014792</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6302,7 +6307,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137845</v>
+        <v>129137739</v>
       </c>
       <c r="B58" t="n">
         <v>57725</v>
@@ -6337,10 +6342,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548531</v>
+        <v>548460</v>
       </c>
       <c r="R58" t="n">
-        <v>7014817</v>
+        <v>7014976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6377,7 +6382,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6404,10 +6409,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137746</v>
+        <v>129137905</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6420,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6444,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548355</v>
+        <v>548618</v>
       </c>
       <c r="R59" t="n">
-        <v>7014874</v>
+        <v>7015116</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6475,11 +6480,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6506,10 +6506,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137860</v>
+        <v>129137845</v>
       </c>
       <c r="B60" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548481</v>
+        <v>548531</v>
       </c>
       <c r="R60" t="n">
-        <v>7015172</v>
+        <v>7014817</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137859</v>
+        <v>129137746</v>
       </c>
       <c r="B61" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548434</v>
+        <v>548355</v>
       </c>
       <c r="R61" t="n">
-        <v>7014792</v>
+        <v>7014874</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6710,10 +6710,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B62" t="n">
-        <v>92826</v>
+        <v>80172</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R62" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B63" t="n">
         <v>80172</v>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R63" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,32 +6904,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137875</v>
+        <v>129137782</v>
       </c>
       <c r="B64" t="n">
-        <v>80172</v>
+        <v>98676</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548581</v>
+        <v>548485</v>
       </c>
       <c r="R64" t="n">
-        <v>7015017</v>
+        <v>7014854</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6975,6 +6975,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7001,32 +7006,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137782</v>
+        <v>129137910</v>
       </c>
       <c r="B65" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7041,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548485</v>
+        <v>548510</v>
       </c>
       <c r="R65" t="n">
-        <v>7014854</v>
+        <v>7014986</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,11 +7077,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7103,32 +7103,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137858</v>
+        <v>129137811</v>
       </c>
       <c r="B66" t="n">
-        <v>56915</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548400</v>
+        <v>548458</v>
       </c>
       <c r="R66" t="n">
-        <v>7015152</v>
+        <v>7015205</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,11 +7174,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7205,32 +7200,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137890</v>
+        <v>129137857</v>
       </c>
       <c r="B67" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7240,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548594</v>
+        <v>548502</v>
       </c>
       <c r="R67" t="n">
-        <v>7015211</v>
+        <v>7015176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7280,7 +7275,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7307,10 +7302,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137791</v>
+        <v>129137858</v>
       </c>
       <c r="B68" t="n">
-        <v>105732</v>
+        <v>56915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7318,21 +7313,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7342,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548452</v>
+        <v>548400</v>
       </c>
       <c r="R68" t="n">
-        <v>7014769</v>
+        <v>7015152</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7378,6 +7373,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7404,32 +7404,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137762</v>
+        <v>129137890</v>
       </c>
       <c r="B69" t="n">
-        <v>97546</v>
+        <v>98676</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548603</v>
+        <v>548594</v>
       </c>
       <c r="R69" t="n">
-        <v>7014709</v>
+        <v>7015211</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7475,6 +7475,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7501,32 +7506,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137811</v>
+        <v>129137791</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>105739</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7536,10 +7541,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548458</v>
+        <v>548452</v>
       </c>
       <c r="R70" t="n">
-        <v>7015205</v>
+        <v>7014769</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7598,32 +7603,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137857</v>
+        <v>129137762</v>
       </c>
       <c r="B71" t="n">
-        <v>57725</v>
+        <v>97553</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7633,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548502</v>
+        <v>548603</v>
       </c>
       <c r="R71" t="n">
-        <v>7015176</v>
+        <v>7014709</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7669,11 +7674,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7700,32 +7700,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137748</v>
+        <v>129137780</v>
       </c>
       <c r="B72" t="n">
-        <v>57885</v>
+        <v>98676</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548710</v>
+        <v>548594</v>
       </c>
       <c r="R72" t="n">
-        <v>7014904</v>
+        <v>7015114</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7802,10 +7802,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137773</v>
+        <v>129137850</v>
       </c>
       <c r="B73" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7813,21 +7813,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548717</v>
+        <v>548629</v>
       </c>
       <c r="R73" t="n">
-        <v>7014991</v>
+        <v>7015262</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7873,6 +7873,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7899,32 +7904,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137886</v>
+        <v>129137902</v>
       </c>
       <c r="B74" t="n">
-        <v>80180</v>
+        <v>91558</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7934,10 +7939,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548498</v>
+        <v>548480</v>
       </c>
       <c r="R74" t="n">
-        <v>7015173</v>
+        <v>7015285</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7996,10 +8001,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137902</v>
+        <v>129137773</v>
       </c>
       <c r="B75" t="n">
-        <v>91551</v>
+        <v>80144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8007,21 +8012,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8031,10 +8036,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548480</v>
+        <v>548717</v>
       </c>
       <c r="R75" t="n">
-        <v>7015285</v>
+        <v>7014991</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8093,32 +8098,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137850</v>
+        <v>129137886</v>
       </c>
       <c r="B76" t="n">
-        <v>57725</v>
+        <v>80180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8128,10 +8133,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548629</v>
+        <v>548498</v>
       </c>
       <c r="R76" t="n">
-        <v>7015262</v>
+        <v>7015173</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8164,11 +8169,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137780</v>
+        <v>129137748</v>
       </c>
       <c r="B77" t="n">
-        <v>98669</v>
+        <v>57885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548594</v>
+        <v>548710</v>
       </c>
       <c r="R77" t="n">
-        <v>7015114</v>
+        <v>7014904</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137813</v>
+        <v>129137779</v>
       </c>
       <c r="B78" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548374</v>
+        <v>548620</v>
       </c>
       <c r="R78" t="n">
-        <v>7015064</v>
+        <v>7014685</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8368,6 +8368,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8394,32 +8399,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137818</v>
+        <v>129137759</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>97547</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8429,10 +8434,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548329</v>
+        <v>548487</v>
       </c>
       <c r="R79" t="n">
-        <v>7014932</v>
+        <v>7014855</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8491,32 +8496,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137779</v>
+        <v>129137813</v>
       </c>
       <c r="B80" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8526,10 +8531,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548620</v>
+        <v>548374</v>
       </c>
       <c r="R80" t="n">
-        <v>7014685</v>
+        <v>7015064</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8562,11 +8567,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8593,32 +8593,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137759</v>
+        <v>129137818</v>
       </c>
       <c r="B81" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548487</v>
+        <v>548329</v>
       </c>
       <c r="R81" t="n">
-        <v>7014855</v>
+        <v>7014932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8690,10 +8690,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137796</v>
+        <v>129137745</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8701,21 +8701,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548559</v>
+        <v>548373</v>
       </c>
       <c r="R82" t="n">
-        <v>7014776</v>
+        <v>7014966</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8761,6 +8761,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8884,7 +8889,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137816</v>
+        <v>129137796</v>
       </c>
       <c r="B84" t="n">
         <v>79039</v>
@@ -8919,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548400</v>
+        <v>548559</v>
       </c>
       <c r="R84" t="n">
-        <v>7014970</v>
+        <v>7014776</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8981,10 +8986,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137745</v>
+        <v>129137816</v>
       </c>
       <c r="B85" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8992,21 +8997,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9016,10 +9021,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548373</v>
+        <v>548400</v>
       </c>
       <c r="R85" t="n">
-        <v>7014966</v>
+        <v>7014970</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9052,11 +9057,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9083,10 +9083,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137781</v>
+        <v>129137889</v>
       </c>
       <c r="B86" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548433</v>
+        <v>548440</v>
       </c>
       <c r="R86" t="n">
-        <v>7014771</v>
+        <v>7014752</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>11 stycken kan finnas mer I mossan</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9185,32 +9185,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137889</v>
+        <v>129137900</v>
       </c>
       <c r="B87" t="n">
-        <v>98669</v>
+        <v>105739</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9220,10 +9220,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548440</v>
+        <v>548451</v>
       </c>
       <c r="R87" t="n">
-        <v>7014752</v>
+        <v>7014746</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9256,11 +9256,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9287,10 +9282,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137900</v>
+        <v>129137871</v>
       </c>
       <c r="B88" t="n">
-        <v>105732</v>
+        <v>97553</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9298,21 +9293,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9322,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548451</v>
+        <v>548457</v>
       </c>
       <c r="R88" t="n">
-        <v>7014746</v>
+        <v>7014764</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9384,10 +9379,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137871</v>
+        <v>129137872</v>
       </c>
       <c r="B89" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9419,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548457</v>
+        <v>548477</v>
       </c>
       <c r="R89" t="n">
-        <v>7014764</v>
+        <v>7015144</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9481,32 +9476,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137872</v>
+        <v>129137781</v>
       </c>
       <c r="B90" t="n">
-        <v>97546</v>
+        <v>98676</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9511,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548477</v>
+        <v>548433</v>
       </c>
       <c r="R90" t="n">
-        <v>7015144</v>
+        <v>7014771</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9552,6 +9547,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9578,32 +9578,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137878</v>
+        <v>129137778</v>
       </c>
       <c r="B91" t="n">
-        <v>80144</v>
+        <v>57829</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548705</v>
+        <v>548706</v>
       </c>
       <c r="R91" t="n">
-        <v>7014750</v>
+        <v>7014864</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9649,6 +9649,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9675,32 +9680,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137901</v>
+        <v>129137878</v>
       </c>
       <c r="B92" t="n">
-        <v>105732</v>
+        <v>80144</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9715,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548281</v>
+        <v>548705</v>
       </c>
       <c r="R92" t="n">
-        <v>7015128</v>
+        <v>7014750</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9772,10 +9777,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137790</v>
+        <v>129137901</v>
       </c>
       <c r="B93" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9807,10 +9812,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548558</v>
+        <v>548281</v>
       </c>
       <c r="R93" t="n">
-        <v>7014771</v>
+        <v>7015128</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9869,10 +9874,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137764</v>
+        <v>129137790</v>
       </c>
       <c r="B94" t="n">
-        <v>97546</v>
+        <v>105739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9880,21 +9885,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9904,10 +9909,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548590</v>
+        <v>548558</v>
       </c>
       <c r="R94" t="n">
-        <v>7015157</v>
+        <v>7014771</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9966,10 +9971,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137778</v>
+        <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>57829</v>
+        <v>97553</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9977,21 +9982,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10001,10 +10006,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548706</v>
+        <v>548590</v>
       </c>
       <c r="R95" t="n">
-        <v>7014864</v>
+        <v>7015157</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10037,11 +10042,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10265,7 +10265,7 @@
         <v>129137912</v>
       </c>
       <c r="B98" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10359,32 +10359,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137863</v>
+        <v>129137874</v>
       </c>
       <c r="B99" t="n">
-        <v>80145</v>
+        <v>97553</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548702</v>
+        <v>548348</v>
       </c>
       <c r="R99" t="n">
-        <v>7014752</v>
+        <v>7014988</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10456,32 +10456,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137903</v>
+        <v>129137788</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548633</v>
+        <v>548605</v>
       </c>
       <c r="R100" t="n">
-        <v>7015045</v>
+        <v>7014687</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10527,6 +10527,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10553,10 +10558,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137848</v>
+        <v>129137903</v>
       </c>
       <c r="B101" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10564,21 +10569,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10588,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548598</v>
+        <v>548633</v>
       </c>
       <c r="R101" t="n">
-        <v>7015227</v>
+        <v>7015045</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10624,11 +10629,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10655,32 +10655,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137788</v>
+        <v>129137863</v>
       </c>
       <c r="B102" t="n">
-        <v>98669</v>
+        <v>80145</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548605</v>
+        <v>548702</v>
       </c>
       <c r="R102" t="n">
-        <v>7014687</v>
+        <v>7014752</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10726,11 +10726,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10757,32 +10752,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137874</v>
+        <v>129137848</v>
       </c>
       <c r="B103" t="n">
-        <v>97546</v>
+        <v>57725</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10792,10 +10787,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548348</v>
+        <v>548598</v>
       </c>
       <c r="R103" t="n">
-        <v>7014988</v>
+        <v>7015227</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10828,6 +10823,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10857,7 +10857,7 @@
         <v>129137753</v>
       </c>
       <c r="B104" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>129137840</v>
       </c>
       <c r="B105" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11048,32 +11048,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137883</v>
+        <v>129137758</v>
       </c>
       <c r="B106" t="n">
-        <v>80144</v>
+        <v>97547</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548499</v>
+        <v>548629</v>
       </c>
       <c r="R106" t="n">
-        <v>7015176</v>
+        <v>7014777</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11145,32 +11145,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137758</v>
+        <v>129137883</v>
       </c>
       <c r="B107" t="n">
-        <v>97540</v>
+        <v>80144</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548629</v>
+        <v>548499</v>
       </c>
       <c r="R107" t="n">
-        <v>7014777</v>
+        <v>7015176</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11242,10 +11242,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137768</v>
+        <v>129137873</v>
       </c>
       <c r="B108" t="n">
-        <v>80172</v>
+        <v>97553</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11253,21 +11253,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548723</v>
+        <v>548291</v>
       </c>
       <c r="R108" t="n">
-        <v>7014940</v>
+        <v>7015110</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11339,32 +11339,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137847</v>
+        <v>129137761</v>
       </c>
       <c r="B109" t="n">
-        <v>57725</v>
+        <v>97547</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11374,10 +11374,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548490</v>
+        <v>548366</v>
       </c>
       <c r="R109" t="n">
-        <v>7014739</v>
+        <v>7015047</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11410,11 +11410,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11441,32 +11436,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137844</v>
+        <v>129137768</v>
       </c>
       <c r="B110" t="n">
-        <v>57725</v>
+        <v>80172</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11476,10 +11471,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548672</v>
+        <v>548723</v>
       </c>
       <c r="R110" t="n">
-        <v>7014893</v>
+        <v>7014940</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11512,11 +11507,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11543,32 +11533,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137873</v>
+        <v>129137847</v>
       </c>
       <c r="B111" t="n">
-        <v>97546</v>
+        <v>57725</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11578,10 +11568,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548291</v>
+        <v>548490</v>
       </c>
       <c r="R111" t="n">
-        <v>7015110</v>
+        <v>7014739</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11614,6 +11604,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11640,32 +11635,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137761</v>
+        <v>129137844</v>
       </c>
       <c r="B112" t="n">
-        <v>97540</v>
+        <v>57725</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11675,10 +11670,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548366</v>
+        <v>548672</v>
       </c>
       <c r="R112" t="n">
-        <v>7015047</v>
+        <v>7014893</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11711,6 +11706,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137751</v>
+        <v>129137740</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548268</v>
+        <v>548618</v>
       </c>
       <c r="R6" t="n">
-        <v>7014891</v>
+        <v>7015211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1249,7 @@
         <v>129137817</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129137797</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129137815</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137740</v>
+        <v>129137751</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548618</v>
+        <v>548268</v>
       </c>
       <c r="R10" t="n">
-        <v>7015211</v>
+        <v>7014891</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137787</v>
+        <v>129137870</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>97555</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548366</v>
+        <v>548358</v>
       </c>
       <c r="R11" t="n">
-        <v>7014942</v>
+        <v>7014777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137870</v>
+        <v>129137787</v>
       </c>
       <c r="B12" t="n">
-        <v>97553</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548358</v>
+        <v>548366</v>
       </c>
       <c r="R12" t="n">
-        <v>7014777</v>
+        <v>7014942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,7 +1846,7 @@
         <v>129137794</v>
       </c>
       <c r="B13" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137795</v>
+        <v>129137738</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,21 +1951,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548538</v>
+        <v>548567</v>
       </c>
       <c r="R14" t="n">
-        <v>7014770</v>
+        <v>7014763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R15" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,6 +2113,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137738</v>
+        <v>129137804</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2174,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548567</v>
+        <v>548550</v>
       </c>
       <c r="R16" t="n">
-        <v>7014763</v>
+        <v>7015142</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,11 +2215,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137820</v>
+        <v>129137801</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548328</v>
+        <v>548686</v>
       </c>
       <c r="R17" t="n">
-        <v>7014882</v>
+        <v>7014817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,11 +2312,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,10 +2338,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137801</v>
+        <v>129137802</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548686</v>
+        <v>548499</v>
       </c>
       <c r="R18" t="n">
-        <v>7014817</v>
+        <v>7014902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137802</v>
+        <v>129137820</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,10 +2470,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548499</v>
+        <v>548328</v>
       </c>
       <c r="R19" t="n">
-        <v>7014902</v>
+        <v>7014882</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,6 +2506,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2540,7 +2540,7 @@
         <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137906</v>
+        <v>129137819</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548693</v>
+        <v>548318</v>
       </c>
       <c r="R21" t="n">
-        <v>7014874</v>
+        <v>7014904</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,32 +2731,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137819</v>
+        <v>129137771</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>80174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548318</v>
+        <v>548360</v>
       </c>
       <c r="R22" t="n">
-        <v>7014904</v>
+        <v>7014942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137744</v>
+        <v>129137862</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548511</v>
+        <v>548497</v>
       </c>
       <c r="R23" t="n">
-        <v>7015241</v>
+        <v>7015181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,11 +2899,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2930,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137771</v>
+        <v>129137744</v>
       </c>
       <c r="B24" t="n">
-        <v>80172</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548360</v>
+        <v>548511</v>
       </c>
       <c r="R24" t="n">
-        <v>7014942</v>
+        <v>7015241</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3001,6 +2996,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137862</v>
+        <v>129137750</v>
       </c>
       <c r="B25" t="n">
-        <v>80173</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548497</v>
+        <v>548514</v>
       </c>
       <c r="R25" t="n">
-        <v>7015181</v>
+        <v>7015227</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,6 +3098,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3124,10 +3129,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137750</v>
+        <v>129137906</v>
       </c>
       <c r="B26" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,21 +3140,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3159,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548514</v>
+        <v>548693</v>
       </c>
       <c r="R26" t="n">
-        <v>7015227</v>
+        <v>7014874</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,11 +3200,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3226,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129125929</v>
+        <v>129137876</v>
       </c>
       <c r="B27" t="n">
-        <v>97547</v>
+        <v>80174</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548372</v>
+        <v>548475</v>
       </c>
       <c r="R27" t="n">
-        <v>7014829</v>
+        <v>7015265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137810</v>
+        <v>129125929</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>97549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548538</v>
+        <v>548372</v>
       </c>
       <c r="R28" t="n">
-        <v>7015259</v>
+        <v>7014829</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137806</v>
+        <v>129137810</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548632</v>
+        <v>548538</v>
       </c>
       <c r="R29" t="n">
-        <v>7015246</v>
+        <v>7015259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,32 +3517,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137876</v>
+        <v>129137806</v>
       </c>
       <c r="B30" t="n">
-        <v>80172</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548475</v>
+        <v>548632</v>
       </c>
       <c r="R30" t="n">
-        <v>7015265</v>
+        <v>7015246</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3617,7 +3617,7 @@
         <v>129137749</v>
       </c>
       <c r="B31" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>129137800</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3818,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137821</v>
+        <v>129137789</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548369</v>
+        <v>548461</v>
       </c>
       <c r="R33" t="n">
-        <v>7014853</v>
+        <v>7015210</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,6 +3889,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3915,32 +3920,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137849</v>
+        <v>129137896</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3950,10 +3955,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548260</v>
       </c>
       <c r="R34" t="n">
-        <v>7015247</v>
+        <v>7014898</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,7 +3995,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,10 +4022,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137789</v>
+        <v>129126213</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4045,17 +4050,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548461</v>
+        <v>548265</v>
       </c>
       <c r="R35" t="n">
-        <v>7015210</v>
+        <v>7014876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4088,11 +4097,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,32 +4123,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4154,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R36" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4221,49 +4220,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129126213</v>
+        <v>129137849</v>
       </c>
       <c r="B37" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548265</v>
+        <v>548629</v>
       </c>
       <c r="R37" t="n">
-        <v>7014876</v>
+        <v>7015247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,6 +4291,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4325,7 +4325,7 @@
         <v>129137774</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>129137772</v>
       </c>
       <c r="B39" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>129137846</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137803</v>
+        <v>129137822</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>57648</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548467</v>
+        <v>548346</v>
       </c>
       <c r="R43" t="n">
-        <v>7014995</v>
+        <v>7015026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137814</v>
+        <v>129137783</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548376</v>
+        <v>548595</v>
       </c>
       <c r="R44" t="n">
-        <v>7015053</v>
+        <v>7015162</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,6 +4985,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,32 +5016,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5051,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R45" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,6 +5087,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5108,32 +5118,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137909</v>
+        <v>129137792</v>
       </c>
       <c r="B46" t="n">
-        <v>82871</v>
+        <v>105741</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5153,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548610</v>
+        <v>548368</v>
       </c>
       <c r="R46" t="n">
-        <v>7015229</v>
+        <v>7014860</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5179,6 +5189,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5205,32 +5220,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137822</v>
+        <v>129137786</v>
       </c>
       <c r="B47" t="n">
-        <v>57646</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548346</v>
+        <v>548402</v>
       </c>
       <c r="R47" t="n">
-        <v>7015026</v>
+        <v>7015096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,6 +5291,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5302,32 +5322,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137783</v>
+        <v>129137843</v>
       </c>
       <c r="B48" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5337,10 +5357,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548595</v>
+        <v>548488</v>
       </c>
       <c r="R48" t="n">
-        <v>7015162</v>
+        <v>7015296</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5373,11 +5393,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5404,32 +5419,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137891</v>
+        <v>129137909</v>
       </c>
       <c r="B49" t="n">
-        <v>98676</v>
+        <v>82873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5439,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548627</v>
+        <v>548610</v>
       </c>
       <c r="R49" t="n">
-        <v>7015253</v>
+        <v>7015229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5475,11 +5490,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5506,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137786</v>
+        <v>129137803</v>
       </c>
       <c r="B50" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5541,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548402</v>
+        <v>548467</v>
       </c>
       <c r="R50" t="n">
-        <v>7015096</v>
+        <v>7014995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5577,11 +5587,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137792</v>
+        <v>129137814</v>
       </c>
       <c r="B51" t="n">
-        <v>105739</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548368</v>
+        <v>548376</v>
       </c>
       <c r="R51" t="n">
-        <v>7014860</v>
+        <v>7015053</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,11 +5684,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5713,7 +5713,7 @@
         <v>129137766</v>
       </c>
       <c r="B52" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5812,32 +5812,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137877</v>
+        <v>129126001</v>
       </c>
       <c r="B53" t="n">
-        <v>80172</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548334</v>
+        <v>548299</v>
       </c>
       <c r="R53" t="n">
-        <v>7015001</v>
+        <v>7014876</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5909,32 +5909,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129126001</v>
+        <v>129137877</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>80174</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548299</v>
+        <v>548334</v>
       </c>
       <c r="R54" t="n">
-        <v>7014876</v>
+        <v>7015001</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6009,7 +6009,7 @@
         <v>129137882</v>
       </c>
       <c r="B55" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137860</v>
+        <v>129137905</v>
       </c>
       <c r="B56" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548481</v>
+        <v>548618</v>
       </c>
       <c r="R56" t="n">
-        <v>7015172</v>
+        <v>7015116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6174,11 +6174,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6205,10 +6200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137859</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>57885</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6216,21 +6211,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6240,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548434</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7014792</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6307,10 +6302,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137739</v>
+        <v>129137845</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6342,10 +6337,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548460</v>
+        <v>548531</v>
       </c>
       <c r="R58" t="n">
-        <v>7014976</v>
+        <v>7014817</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6382,7 +6377,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6409,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137905</v>
+        <v>129137746</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6420,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6444,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548618</v>
+        <v>548355</v>
       </c>
       <c r="R59" t="n">
-        <v>7015116</v>
+        <v>7014874</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6480,6 +6475,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6506,10 +6506,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137845</v>
+        <v>129137860</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548531</v>
+        <v>548481</v>
       </c>
       <c r="R60" t="n">
-        <v>7014817</v>
+        <v>7015172</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137746</v>
+        <v>129137859</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548355</v>
+        <v>548434</v>
       </c>
       <c r="R61" t="n">
-        <v>7014874</v>
+        <v>7014792</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6710,10 +6710,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137769</v>
+        <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>80172</v>
+        <v>92835</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548487</v>
+        <v>548510</v>
       </c>
       <c r="R62" t="n">
-        <v>7015073</v>
+        <v>7014986</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137875</v>
+        <v>129137769</v>
       </c>
       <c r="B63" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548581</v>
+        <v>548487</v>
       </c>
       <c r="R63" t="n">
-        <v>7015017</v>
+        <v>7015073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,32 +6904,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137782</v>
+        <v>129137875</v>
       </c>
       <c r="B64" t="n">
-        <v>98676</v>
+        <v>80174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548485</v>
+        <v>548581</v>
       </c>
       <c r="R64" t="n">
-        <v>7014854</v>
+        <v>7015017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6975,11 +6975,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7006,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137910</v>
+        <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7041,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548510</v>
+        <v>548485</v>
       </c>
       <c r="R65" t="n">
-        <v>7014986</v>
+        <v>7014854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7077,6 +7072,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7103,32 +7103,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137811</v>
+        <v>129137890</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548458</v>
+        <v>548594</v>
       </c>
       <c r="R66" t="n">
-        <v>7015205</v>
+        <v>7015211</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,6 +7174,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7203,7 +7208,7 @@
         <v>129137857</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7305,7 +7310,7 @@
         <v>129137858</v>
       </c>
       <c r="B68" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7404,32 +7409,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137890</v>
+        <v>129137811</v>
       </c>
       <c r="B69" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7439,10 +7444,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548594</v>
+        <v>548458</v>
       </c>
       <c r="R69" t="n">
-        <v>7015211</v>
+        <v>7015205</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7475,11 +7480,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7509,7 +7509,7 @@
         <v>129137791</v>
       </c>
       <c r="B70" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>129137762</v>
       </c>
       <c r="B71" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7700,32 +7700,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137780</v>
+        <v>129137902</v>
       </c>
       <c r="B72" t="n">
-        <v>98676</v>
+        <v>91560</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548594</v>
+        <v>548480</v>
       </c>
       <c r="R72" t="n">
-        <v>7015114</v>
+        <v>7015285</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7771,11 +7771,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7802,10 +7797,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137850</v>
+        <v>129137748</v>
       </c>
       <c r="B73" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7813,21 +7808,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7837,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548629</v>
+        <v>548710</v>
       </c>
       <c r="R73" t="n">
-        <v>7015262</v>
+        <v>7014904</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7877,7 +7872,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7904,10 +7899,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137902</v>
+        <v>129137773</v>
       </c>
       <c r="B74" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7915,21 +7910,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7939,10 +7934,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548480</v>
+        <v>548717</v>
       </c>
       <c r="R74" t="n">
-        <v>7015285</v>
+        <v>7014991</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8001,32 +7996,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137773</v>
+        <v>129137886</v>
       </c>
       <c r="B75" t="n">
-        <v>80144</v>
+        <v>80182</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8036,10 +8031,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548717</v>
+        <v>548498</v>
       </c>
       <c r="R75" t="n">
-        <v>7014991</v>
+        <v>7015173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8098,32 +8093,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137886</v>
+        <v>129137850</v>
       </c>
       <c r="B76" t="n">
-        <v>80180</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8133,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548498</v>
+        <v>548629</v>
       </c>
       <c r="R76" t="n">
-        <v>7015173</v>
+        <v>7015262</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8169,6 +8164,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137748</v>
+        <v>129137780</v>
       </c>
       <c r="B77" t="n">
-        <v>57885</v>
+        <v>98678</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548710</v>
+        <v>548594</v>
       </c>
       <c r="R77" t="n">
-        <v>7014904</v>
+        <v>7015114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B78" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R78" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8368,11 +8368,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8399,32 +8394,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137759</v>
+        <v>129137779</v>
       </c>
       <c r="B79" t="n">
-        <v>97547</v>
+        <v>98678</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8434,10 +8429,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548487</v>
+        <v>548620</v>
       </c>
       <c r="R79" t="n">
-        <v>7014855</v>
+        <v>7014685</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8470,6 +8465,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8499,7 +8499,7 @@
         <v>129137813</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8593,32 +8593,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137818</v>
+        <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>97549</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548329</v>
+        <v>548487</v>
       </c>
       <c r="R81" t="n">
-        <v>7014932</v>
+        <v>7014855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8693,7 +8693,7 @@
         <v>129137745</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>129137805</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>129137796</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>129137816</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9083,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137889</v>
+        <v>129137900</v>
       </c>
       <c r="B86" t="n">
-        <v>98676</v>
+        <v>105741</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548440</v>
+        <v>548451</v>
       </c>
       <c r="R86" t="n">
-        <v>7014752</v>
+        <v>7014746</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9154,11 +9154,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9185,10 +9180,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137900</v>
+        <v>129137871</v>
       </c>
       <c r="B87" t="n">
-        <v>105739</v>
+        <v>97555</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9196,21 +9191,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9220,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548451</v>
+        <v>548457</v>
       </c>
       <c r="R87" t="n">
-        <v>7014746</v>
+        <v>7014764</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9282,10 +9277,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137871</v>
+        <v>129137872</v>
       </c>
       <c r="B88" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9317,10 +9312,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548457</v>
+        <v>548477</v>
       </c>
       <c r="R88" t="n">
-        <v>7014764</v>
+        <v>7015144</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9379,32 +9374,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137872</v>
+        <v>129137889</v>
       </c>
       <c r="B89" t="n">
-        <v>97553</v>
+        <v>98678</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9409,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548477</v>
+        <v>548440</v>
       </c>
       <c r="R89" t="n">
-        <v>7015144</v>
+        <v>7014752</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9450,6 +9445,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9479,7 +9479,7 @@
         <v>129137781</v>
       </c>
       <c r="B90" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9578,10 +9578,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137778</v>
+        <v>129137901</v>
       </c>
       <c r="B91" t="n">
-        <v>57829</v>
+        <v>105741</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9589,21 +9589,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103031</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548706</v>
+        <v>548281</v>
       </c>
       <c r="R91" t="n">
-        <v>7014864</v>
+        <v>7015128</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9649,11 +9649,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9680,32 +9675,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137878</v>
+        <v>129137790</v>
       </c>
       <c r="B92" t="n">
-        <v>80144</v>
+        <v>105741</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9715,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548705</v>
+        <v>548558</v>
       </c>
       <c r="R92" t="n">
-        <v>7014750</v>
+        <v>7014771</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9777,10 +9772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137901</v>
+        <v>129137764</v>
       </c>
       <c r="B93" t="n">
-        <v>105739</v>
+        <v>97555</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9788,21 +9783,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9812,10 +9807,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548281</v>
+        <v>548590</v>
       </c>
       <c r="R93" t="n">
-        <v>7015128</v>
+        <v>7015157</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9874,32 +9869,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137790</v>
+        <v>129137878</v>
       </c>
       <c r="B94" t="n">
-        <v>105739</v>
+        <v>80146</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9909,10 +9904,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548558</v>
+        <v>548705</v>
       </c>
       <c r="R94" t="n">
-        <v>7014771</v>
+        <v>7014750</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9971,10 +9966,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137764</v>
+        <v>129137778</v>
       </c>
       <c r="B95" t="n">
-        <v>97553</v>
+        <v>57831</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9982,21 +9977,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10006,10 +10001,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548590</v>
+        <v>548706</v>
       </c>
       <c r="R95" t="n">
-        <v>7015157</v>
+        <v>7014864</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10042,6 +10037,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10071,7 +10071,7 @@
         <v>129137908</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>129137911</v>
       </c>
       <c r="B97" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10262,32 +10262,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137912</v>
+        <v>129137903</v>
       </c>
       <c r="B98" t="n">
-        <v>96795</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548604</v>
+        <v>548633</v>
       </c>
       <c r="R98" t="n">
-        <v>7015234</v>
+        <v>7015045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10359,32 +10359,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137874</v>
+        <v>129137848</v>
       </c>
       <c r="B99" t="n">
-        <v>97553</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548348</v>
+        <v>548598</v>
       </c>
       <c r="R99" t="n">
-        <v>7014988</v>
+        <v>7015227</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10430,6 +10430,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10456,32 +10461,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137788</v>
+        <v>129137912</v>
       </c>
       <c r="B100" t="n">
-        <v>98676</v>
+        <v>96797</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10491,10 +10496,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548605</v>
+        <v>548604</v>
       </c>
       <c r="R100" t="n">
-        <v>7014687</v>
+        <v>7015234</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10527,11 +10532,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10558,10 +10558,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137903</v>
+        <v>129137863</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10569,21 +10569,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548633</v>
+        <v>548702</v>
       </c>
       <c r="R101" t="n">
-        <v>7015045</v>
+        <v>7014752</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10655,32 +10655,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137863</v>
+        <v>129137874</v>
       </c>
       <c r="B102" t="n">
-        <v>80145</v>
+        <v>97555</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548702</v>
+        <v>548348</v>
       </c>
       <c r="R102" t="n">
-        <v>7014752</v>
+        <v>7014988</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10752,32 +10752,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137848</v>
+        <v>129137788</v>
       </c>
       <c r="B103" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548598</v>
+        <v>548605</v>
       </c>
       <c r="R103" t="n">
-        <v>7015227</v>
+        <v>7014687</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10827,7 +10827,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10854,32 +10854,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137753</v>
+        <v>129137758</v>
       </c>
       <c r="B104" t="n">
-        <v>91825</v>
+        <v>97549</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548681</v>
+        <v>548629</v>
       </c>
       <c r="R104" t="n">
-        <v>7015193</v>
+        <v>7014777</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10954,7 +10954,7 @@
         <v>129137840</v>
       </c>
       <c r="B105" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11048,32 +11048,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137758</v>
+        <v>129137753</v>
       </c>
       <c r="B106" t="n">
-        <v>97547</v>
+        <v>91827</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548629</v>
+        <v>548681</v>
       </c>
       <c r="R106" t="n">
-        <v>7014777</v>
+        <v>7015193</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
         <v>129137883</v>
       </c>
       <c r="B107" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137873</v>
+        <v>129137847</v>
       </c>
       <c r="B108" t="n">
-        <v>97553</v>
+        <v>57727</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548291</v>
+        <v>548490</v>
       </c>
       <c r="R108" t="n">
-        <v>7015110</v>
+        <v>7014739</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11313,6 +11313,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11339,32 +11344,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137761</v>
+        <v>129137844</v>
       </c>
       <c r="B109" t="n">
-        <v>97547</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11374,10 +11379,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548366</v>
+        <v>548672</v>
       </c>
       <c r="R109" t="n">
-        <v>7015047</v>
+        <v>7014893</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11410,6 +11415,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11439,7 +11449,7 @@
         <v>129137768</v>
       </c>
       <c r="B110" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11533,32 +11543,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137847</v>
+        <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>57725</v>
+        <v>97555</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11568,10 +11578,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548490</v>
+        <v>548291</v>
       </c>
       <c r="R111" t="n">
-        <v>7014739</v>
+        <v>7015110</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11604,11 +11614,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11635,32 +11640,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137844</v>
+        <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>57725</v>
+        <v>97549</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11670,10 +11675,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548672</v>
+        <v>548366</v>
       </c>
       <c r="R112" t="n">
-        <v>7014893</v>
+        <v>7015047</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11706,11 +11711,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137740</v>
+        <v>129137817</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548618</v>
+        <v>548367</v>
       </c>
       <c r="R6" t="n">
-        <v>7015211</v>
+        <v>7014944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,11 +1215,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137817</v>
+        <v>129137751</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548367</v>
+        <v>548268</v>
       </c>
       <c r="R7" t="n">
-        <v>7014944</v>
+        <v>7014891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,6 +1312,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137751</v>
+        <v>129137740</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548268</v>
+        <v>548618</v>
       </c>
       <c r="R10" t="n">
-        <v>7014891</v>
+        <v>7015211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137870</v>
+        <v>129137787</v>
       </c>
       <c r="B11" t="n">
-        <v>97555</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548358</v>
+        <v>548366</v>
       </c>
       <c r="R11" t="n">
-        <v>7014777</v>
+        <v>7014942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137787</v>
+        <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>97555</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548366</v>
+        <v>548358</v>
       </c>
       <c r="R12" t="n">
-        <v>7014942</v>
+        <v>7014777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1817,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137794</v>
+        <v>129137795</v>
       </c>
       <c r="B13" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548459</v>
+        <v>548538</v>
       </c>
       <c r="R13" t="n">
-        <v>7015186</v>
+        <v>7014770</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,6 +1914,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137738</v>
+        <v>129137804</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,21 +1956,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548567</v>
+        <v>548550</v>
       </c>
       <c r="R14" t="n">
-        <v>7014763</v>
+        <v>7015142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,11 +2016,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137795</v>
+        <v>129137738</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548538</v>
+        <v>548567</v>
       </c>
       <c r="R15" t="n">
-        <v>7014770</v>
+        <v>7014763</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137804</v>
+        <v>129137794</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548550</v>
+        <v>548459</v>
       </c>
       <c r="R16" t="n">
-        <v>7015142</v>
+        <v>7015186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137801</v>
+        <v>129137820</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548686</v>
+        <v>548328</v>
       </c>
       <c r="R17" t="n">
-        <v>7014817</v>
+        <v>7014882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,6 +2312,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,7 +2343,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137802</v>
+        <v>129137801</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548499</v>
+        <v>548686</v>
       </c>
       <c r="R18" t="n">
-        <v>7014902</v>
+        <v>7014817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,7 +2440,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137820</v>
+        <v>129137802</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2470,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548328</v>
+        <v>548499</v>
       </c>
       <c r="R19" t="n">
-        <v>7014882</v>
+        <v>7014902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,11 +2511,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137819</v>
+        <v>129137906</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548318</v>
+        <v>548693</v>
       </c>
       <c r="R21" t="n">
-        <v>7014904</v>
+        <v>7014874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,32 +2731,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137771</v>
+        <v>129137819</v>
       </c>
       <c r="B22" t="n">
-        <v>80174</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548360</v>
+        <v>548318</v>
       </c>
       <c r="R22" t="n">
-        <v>7014942</v>
+        <v>7014904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137862</v>
+        <v>129137771</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>80174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548497</v>
+        <v>548360</v>
       </c>
       <c r="R23" t="n">
-        <v>7015181</v>
+        <v>7014942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137744</v>
+        <v>129137862</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548511</v>
+        <v>548497</v>
       </c>
       <c r="R24" t="n">
-        <v>7015241</v>
+        <v>7015181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,11 +2996,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,10 +3124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137906</v>
+        <v>129137744</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,21 +3135,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3164,10 +3159,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548693</v>
+        <v>548511</v>
       </c>
       <c r="R26" t="n">
-        <v>7014874</v>
+        <v>7015241</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,6 +3195,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3226,32 +3226,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B27" t="n">
-        <v>80174</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R27" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129125929</v>
+        <v>129137806</v>
       </c>
       <c r="B28" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548372</v>
+        <v>548632</v>
       </c>
       <c r="R28" t="n">
-        <v>7014829</v>
+        <v>7015246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,32 +3420,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137810</v>
+        <v>129137876</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>80174</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548538</v>
+        <v>548475</v>
       </c>
       <c r="R29" t="n">
-        <v>7015259</v>
+        <v>7015265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,10 +3517,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137806</v>
+        <v>129137749</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,21 +3528,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548632</v>
+        <v>548618</v>
       </c>
       <c r="R30" t="n">
-        <v>7015246</v>
+        <v>7015211</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,6 +3588,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3614,32 +3619,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137749</v>
+        <v>129125929</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>97549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3649,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548618</v>
+        <v>548372</v>
       </c>
       <c r="R31" t="n">
-        <v>7015211</v>
+        <v>7014829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3685,11 +3690,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3716,10 +3716,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137800</v>
+        <v>129137849</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,21 +3727,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548708</v>
+        <v>548629</v>
       </c>
       <c r="R32" t="n">
-        <v>7014937</v>
+        <v>7015247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3818,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137789</v>
+        <v>129137800</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548461</v>
+        <v>548708</v>
       </c>
       <c r="R33" t="n">
-        <v>7015210</v>
+        <v>7014937</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3920,32 +3920,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R34" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3991,11 +3991,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4022,7 +4017,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129126213</v>
+        <v>129137789</v>
       </c>
       <c r="B35" t="n">
         <v>98678</v>
@@ -4050,21 +4045,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548265</v>
+        <v>548461</v>
       </c>
       <c r="R35" t="n">
-        <v>7014876</v>
+        <v>7015210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,6 +4088,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,32 +4119,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4154,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R36" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4190,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4220,45 +4221,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137849</v>
+        <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548629</v>
+        <v>548265</v>
       </c>
       <c r="R37" t="n">
-        <v>7015247</v>
+        <v>7014876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,11 +4296,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137812</v>
+        <v>129137846</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548395</v>
+        <v>548317</v>
       </c>
       <c r="R40" t="n">
-        <v>7015086</v>
+        <v>7014833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137846</v>
+        <v>129137812</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548317</v>
+        <v>548395</v>
       </c>
       <c r="R41" t="n">
-        <v>7014833</v>
+        <v>7015086</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137822</v>
+        <v>129137843</v>
       </c>
       <c r="B43" t="n">
-        <v>57648</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100001</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548346</v>
+        <v>548488</v>
       </c>
       <c r="R43" t="n">
-        <v>7015026</v>
+        <v>7015296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137783</v>
+        <v>129137909</v>
       </c>
       <c r="B44" t="n">
-        <v>98678</v>
+        <v>82873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548595</v>
+        <v>548610</v>
       </c>
       <c r="R44" t="n">
-        <v>7015162</v>
+        <v>7015229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,11 +4985,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5016,32 +5011,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137891</v>
+        <v>129137803</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5051,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548627</v>
+        <v>548467</v>
       </c>
       <c r="R45" t="n">
-        <v>7015253</v>
+        <v>7014995</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5087,11 +5082,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5118,32 +5108,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137792</v>
+        <v>129137814</v>
       </c>
       <c r="B46" t="n">
-        <v>105741</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5153,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548368</v>
+        <v>548376</v>
       </c>
       <c r="R46" t="n">
-        <v>7014860</v>
+        <v>7015053</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,11 +5179,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5220,32 +5205,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137786</v>
+        <v>129137822</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>57648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5255,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548402</v>
+        <v>548346</v>
       </c>
       <c r="R47" t="n">
-        <v>7015096</v>
+        <v>7015026</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,11 +5276,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5322,32 +5302,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137843</v>
+        <v>129137783</v>
       </c>
       <c r="B48" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5357,10 +5337,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548488</v>
+        <v>548595</v>
       </c>
       <c r="R48" t="n">
-        <v>7015296</v>
+        <v>7015162</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5393,6 +5373,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5419,32 +5404,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137909</v>
+        <v>129137891</v>
       </c>
       <c r="B49" t="n">
-        <v>82873</v>
+        <v>98678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5439,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548610</v>
+        <v>548627</v>
       </c>
       <c r="R49" t="n">
-        <v>7015229</v>
+        <v>7015253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5490,6 +5475,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5516,32 +5506,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137803</v>
+        <v>129137792</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>105741</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5541,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548467</v>
+        <v>548368</v>
       </c>
       <c r="R50" t="n">
-        <v>7014995</v>
+        <v>7014860</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,6 +5577,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,32 +5608,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137814</v>
+        <v>129137786</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548376</v>
+        <v>548402</v>
       </c>
       <c r="R51" t="n">
-        <v>7015053</v>
+        <v>7015096</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5684,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5812,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129126001</v>
+        <v>129137739</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548299</v>
+        <v>548460</v>
       </c>
       <c r="R53" t="n">
-        <v>7014876</v>
+        <v>7014976</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,6 +5883,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5909,32 +5914,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137877</v>
+        <v>129137845</v>
       </c>
       <c r="B54" t="n">
-        <v>80174</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5944,10 +5949,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548334</v>
+        <v>548531</v>
       </c>
       <c r="R54" t="n">
-        <v>7015001</v>
+        <v>7014817</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5980,6 +5985,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6006,10 +6016,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137882</v>
+        <v>129137746</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6017,21 +6027,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6051,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548510</v>
+        <v>548355</v>
       </c>
       <c r="R55" t="n">
-        <v>7015191</v>
+        <v>7014874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6077,6 +6087,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6103,7 +6118,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137905</v>
+        <v>129126001</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6138,10 +6153,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548618</v>
+        <v>548299</v>
       </c>
       <c r="R56" t="n">
-        <v>7015116</v>
+        <v>7014876</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6200,10 +6215,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137739</v>
+        <v>129137905</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6226,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6250,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548460</v>
+        <v>548618</v>
       </c>
       <c r="R57" t="n">
-        <v>7014976</v>
+        <v>7015116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6271,11 +6286,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6302,32 +6312,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137845</v>
+        <v>129137877</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6337,10 +6347,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548531</v>
+        <v>548334</v>
       </c>
       <c r="R58" t="n">
-        <v>7014817</v>
+        <v>7015001</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6373,11 +6383,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6404,10 +6409,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137746</v>
+        <v>129137882</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6420,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6444,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548355</v>
+        <v>548510</v>
       </c>
       <c r="R59" t="n">
-        <v>7014874</v>
+        <v>7015191</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6475,11 +6480,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7103,32 +7103,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137890</v>
+        <v>129137811</v>
       </c>
       <c r="B66" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548594</v>
+        <v>548458</v>
       </c>
       <c r="R66" t="n">
-        <v>7015211</v>
+        <v>7015205</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,11 +7174,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7409,32 +7404,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137811</v>
+        <v>129137762</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>97555</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7444,10 +7439,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548458</v>
+        <v>548603</v>
       </c>
       <c r="R69" t="n">
-        <v>7015205</v>
+        <v>7014709</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7506,32 +7501,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137791</v>
+        <v>129137890</v>
       </c>
       <c r="B70" t="n">
-        <v>105741</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7541,10 +7536,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548452</v>
+        <v>548594</v>
       </c>
       <c r="R70" t="n">
-        <v>7014769</v>
+        <v>7015211</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7577,6 +7572,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7603,10 +7603,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137762</v>
+        <v>129137791</v>
       </c>
       <c r="B71" t="n">
-        <v>97555</v>
+        <v>105741</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548603</v>
+        <v>548452</v>
       </c>
       <c r="R71" t="n">
-        <v>7014709</v>
+        <v>7014769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137902</v>
+        <v>129137773</v>
       </c>
       <c r="B72" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7711,21 +7711,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548480</v>
+        <v>548717</v>
       </c>
       <c r="R72" t="n">
-        <v>7015285</v>
+        <v>7014991</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7797,32 +7797,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137748</v>
+        <v>129137886</v>
       </c>
       <c r="B73" t="n">
-        <v>57887</v>
+        <v>80182</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548710</v>
+        <v>548498</v>
       </c>
       <c r="R73" t="n">
-        <v>7014904</v>
+        <v>7015173</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7868,11 +7868,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7899,10 +7894,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137773</v>
+        <v>129137902</v>
       </c>
       <c r="B74" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7910,21 +7905,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7934,10 +7929,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548717</v>
+        <v>548480</v>
       </c>
       <c r="R74" t="n">
-        <v>7014991</v>
+        <v>7015285</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7996,32 +7991,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137886</v>
+        <v>129137850</v>
       </c>
       <c r="B75" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8031,10 +8026,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548498</v>
+        <v>548629</v>
       </c>
       <c r="R75" t="n">
-        <v>7015173</v>
+        <v>7015262</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8067,6 +8062,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8093,10 +8093,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137850</v>
+        <v>129137748</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548629</v>
+        <v>548710</v>
       </c>
       <c r="R76" t="n">
-        <v>7015262</v>
+        <v>7014904</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137818</v>
+        <v>129137779</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548329</v>
+        <v>548620</v>
       </c>
       <c r="R78" t="n">
-        <v>7014932</v>
+        <v>7014685</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8368,6 +8368,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8394,32 +8399,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137779</v>
+        <v>129137759</v>
       </c>
       <c r="B79" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8429,10 +8434,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548620</v>
+        <v>548487</v>
       </c>
       <c r="R79" t="n">
-        <v>7014685</v>
+        <v>7014855</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8465,11 +8470,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8593,32 +8593,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137759</v>
+        <v>129137818</v>
       </c>
       <c r="B81" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548487</v>
+        <v>548329</v>
       </c>
       <c r="R81" t="n">
-        <v>7014855</v>
+        <v>7014932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8690,10 +8690,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137745</v>
+        <v>129137805</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8701,21 +8701,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548373</v>
+        <v>548613</v>
       </c>
       <c r="R82" t="n">
-        <v>7014966</v>
+        <v>7015186</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8761,11 +8761,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8792,7 +8787,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137805</v>
+        <v>129137816</v>
       </c>
       <c r="B83" t="n">
         <v>79041</v>
@@ -8827,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548613</v>
+        <v>548400</v>
       </c>
       <c r="R83" t="n">
-        <v>7015186</v>
+        <v>7014970</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8986,32 +8981,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137816</v>
+        <v>129137900</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>105741</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9021,10 +9016,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548400</v>
+        <v>548451</v>
       </c>
       <c r="R85" t="n">
-        <v>7014970</v>
+        <v>7014746</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9083,32 +9078,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137900</v>
+        <v>129137889</v>
       </c>
       <c r="B86" t="n">
-        <v>105741</v>
+        <v>98678</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9113,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548451</v>
+        <v>548440</v>
       </c>
       <c r="R86" t="n">
-        <v>7014746</v>
+        <v>7014752</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9154,6 +9149,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9180,32 +9180,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137871</v>
+        <v>129137781</v>
       </c>
       <c r="B87" t="n">
-        <v>97555</v>
+        <v>98678</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548457</v>
+        <v>548433</v>
       </c>
       <c r="R87" t="n">
-        <v>7014764</v>
+        <v>7014771</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9251,6 +9251,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9277,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137872</v>
+        <v>129137745</v>
       </c>
       <c r="B88" t="n">
-        <v>97555</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9312,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548477</v>
+        <v>548373</v>
       </c>
       <c r="R88" t="n">
-        <v>7015144</v>
+        <v>7014966</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9348,6 +9353,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9374,32 +9384,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137889</v>
+        <v>129137871</v>
       </c>
       <c r="B89" t="n">
-        <v>98678</v>
+        <v>97555</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9409,10 +9419,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548440</v>
+        <v>548457</v>
       </c>
       <c r="R89" t="n">
-        <v>7014752</v>
+        <v>7014764</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9445,11 +9455,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9476,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137781</v>
+        <v>129137872</v>
       </c>
       <c r="B90" t="n">
-        <v>98678</v>
+        <v>97555</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9511,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548433</v>
+        <v>548477</v>
       </c>
       <c r="R90" t="n">
-        <v>7014771</v>
+        <v>7015144</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9547,11 +9552,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10262,10 +10262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137903</v>
+        <v>129137863</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10273,21 +10273,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548633</v>
+        <v>548702</v>
       </c>
       <c r="R98" t="n">
-        <v>7015045</v>
+        <v>7014752</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10359,10 +10359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137848</v>
+        <v>129137903</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548598</v>
+        <v>548633</v>
       </c>
       <c r="R99" t="n">
-        <v>7015227</v>
+        <v>7015045</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10430,11 +10430,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10461,32 +10456,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137912</v>
+        <v>129137848</v>
       </c>
       <c r="B100" t="n">
-        <v>96797</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10496,10 +10491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548604</v>
+        <v>548598</v>
       </c>
       <c r="R100" t="n">
-        <v>7015234</v>
+        <v>7015227</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10532,6 +10527,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10558,32 +10558,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137863</v>
+        <v>129137912</v>
       </c>
       <c r="B101" t="n">
-        <v>80147</v>
+        <v>96797</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>2869</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548702</v>
+        <v>548604</v>
       </c>
       <c r="R101" t="n">
-        <v>7014752</v>
+        <v>7015234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10655,32 +10655,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137874</v>
+        <v>129137788</v>
       </c>
       <c r="B102" t="n">
-        <v>97555</v>
+        <v>98678</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548348</v>
+        <v>548605</v>
       </c>
       <c r="R102" t="n">
-        <v>7014988</v>
+        <v>7014687</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10726,6 +10726,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10752,32 +10757,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137788</v>
+        <v>129137874</v>
       </c>
       <c r="B103" t="n">
-        <v>98678</v>
+        <v>97555</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10787,10 +10792,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548605</v>
+        <v>548348</v>
       </c>
       <c r="R103" t="n">
-        <v>7014687</v>
+        <v>7014988</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10823,11 +10828,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10854,32 +10854,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137758</v>
+        <v>129137753</v>
       </c>
       <c r="B104" t="n">
-        <v>97549</v>
+        <v>91827</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548629</v>
+        <v>548681</v>
       </c>
       <c r="R104" t="n">
-        <v>7014777</v>
+        <v>7015193</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10951,10 +10951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137840</v>
+        <v>129137883</v>
       </c>
       <c r="B105" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10962,21 +10962,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548660</v>
+        <v>548499</v>
       </c>
       <c r="R105" t="n">
-        <v>7014820</v>
+        <v>7015176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11048,32 +11048,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137753</v>
+        <v>129137758</v>
       </c>
       <c r="B106" t="n">
-        <v>91827</v>
+        <v>97549</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548681</v>
+        <v>548629</v>
       </c>
       <c r="R106" t="n">
-        <v>7015193</v>
+        <v>7014777</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11145,10 +11145,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137883</v>
+        <v>129137840</v>
       </c>
       <c r="B107" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11156,21 +11156,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548499</v>
+        <v>548660</v>
       </c>
       <c r="R107" t="n">
-        <v>7015176</v>
+        <v>7014820</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,7 +1144,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137817</v>
+        <v>129137797</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548367</v>
+        <v>548657</v>
       </c>
       <c r="R6" t="n">
-        <v>7014944</v>
+        <v>7014768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137751</v>
+        <v>129137815</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548268</v>
+        <v>548398</v>
       </c>
       <c r="R7" t="n">
-        <v>7014891</v>
+        <v>7015004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137797</v>
+        <v>129137817</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548657</v>
+        <v>548367</v>
       </c>
       <c r="R8" t="n">
-        <v>7014768</v>
+        <v>7014944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137815</v>
+        <v>129137740</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548398</v>
+        <v>548618</v>
       </c>
       <c r="R9" t="n">
-        <v>7015004</v>
+        <v>7015211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137740</v>
+        <v>129137751</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548618</v>
+        <v>548268</v>
       </c>
       <c r="R10" t="n">
-        <v>7015211</v>
+        <v>7014891</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3226,32 +3226,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137810</v>
+        <v>129125929</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>97549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548538</v>
+        <v>548372</v>
       </c>
       <c r="R27" t="n">
-        <v>7015259</v>
+        <v>7014829</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137806</v>
+        <v>129137810</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548632</v>
+        <v>548538</v>
       </c>
       <c r="R28" t="n">
-        <v>7015246</v>
+        <v>7015259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,32 +3420,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137876</v>
+        <v>129137806</v>
       </c>
       <c r="B29" t="n">
-        <v>80174</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548475</v>
+        <v>548632</v>
       </c>
       <c r="R29" t="n">
-        <v>7015265</v>
+        <v>7015246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,32 +3517,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137749</v>
+        <v>129137876</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>80174</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548618</v>
+        <v>548475</v>
       </c>
       <c r="R30" t="n">
-        <v>7015211</v>
+        <v>7015265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,11 +3588,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3619,32 +3614,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129125929</v>
+        <v>129137749</v>
       </c>
       <c r="B31" t="n">
-        <v>97549</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3649,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548372</v>
+        <v>548618</v>
       </c>
       <c r="R31" t="n">
-        <v>7014829</v>
+        <v>7015211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,6 +3685,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3818,32 +3818,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137800</v>
+        <v>129137789</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548708</v>
+        <v>548461</v>
       </c>
       <c r="R33" t="n">
-        <v>7014937</v>
+        <v>7015210</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3920,32 +3920,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R34" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3991,6 +3991,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,7 +4022,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137789</v>
+        <v>129126213</v>
       </c>
       <c r="B35" t="n">
         <v>98678</v>
@@ -4045,17 +4050,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548461</v>
+        <v>548265</v>
       </c>
       <c r="R35" t="n">
-        <v>7015210</v>
+        <v>7014876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4088,11 +4097,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,32 +4123,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137896</v>
+        <v>129137800</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4154,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548260</v>
+        <v>548708</v>
       </c>
       <c r="R36" t="n">
-        <v>7014898</v>
+        <v>7014937</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,7 +4198,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4221,49 +4225,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129126213</v>
+        <v>129137821</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548265</v>
+        <v>548369</v>
       </c>
       <c r="R37" t="n">
-        <v>7014876</v>
+        <v>7014853</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137846</v>
+        <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548317</v>
+        <v>548395</v>
       </c>
       <c r="R40" t="n">
-        <v>7014833</v>
+        <v>7015086</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137812</v>
+        <v>129137846</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548395</v>
+        <v>548317</v>
       </c>
       <c r="R41" t="n">
-        <v>7015086</v>
+        <v>7014833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -7700,10 +7700,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137773</v>
+        <v>129137902</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7711,21 +7711,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548717</v>
+        <v>548480</v>
       </c>
       <c r="R72" t="n">
-        <v>7014991</v>
+        <v>7015285</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7797,32 +7797,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137886</v>
+        <v>129137850</v>
       </c>
       <c r="B73" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548498</v>
+        <v>548629</v>
       </c>
       <c r="R73" t="n">
-        <v>7015173</v>
+        <v>7015262</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7868,6 +7868,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7894,10 +7899,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137902</v>
+        <v>129137748</v>
       </c>
       <c r="B74" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7905,21 +7910,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7929,10 +7934,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548480</v>
+        <v>548710</v>
       </c>
       <c r="R74" t="n">
-        <v>7015285</v>
+        <v>7014904</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7965,6 +7970,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7991,32 +8001,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137850</v>
+        <v>129137780</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8026,10 +8036,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548629</v>
+        <v>548594</v>
       </c>
       <c r="R75" t="n">
-        <v>7015262</v>
+        <v>7015114</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8066,7 +8076,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8093,10 +8103,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137748</v>
+        <v>129137773</v>
       </c>
       <c r="B76" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,21 +8114,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8128,10 +8138,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548710</v>
+        <v>548717</v>
       </c>
       <c r="R76" t="n">
-        <v>7014904</v>
+        <v>7014991</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8164,11 +8174,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8200,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137780</v>
+        <v>129137886</v>
       </c>
       <c r="B77" t="n">
-        <v>98678</v>
+        <v>80182</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548594</v>
+        <v>548498</v>
       </c>
       <c r="R77" t="n">
-        <v>7015114</v>
+        <v>7015173</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8266,11 +8271,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B78" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R78" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8368,11 +8368,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8496,32 +8491,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137813</v>
+        <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8531,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548374</v>
+        <v>548620</v>
       </c>
       <c r="R80" t="n">
-        <v>7015064</v>
+        <v>7014685</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8567,6 +8562,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8593,7 +8593,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137818</v>
+        <v>129137813</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548329</v>
+        <v>548374</v>
       </c>
       <c r="R81" t="n">
-        <v>7014932</v>
+        <v>7015064</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9578,32 +9578,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137901</v>
+        <v>129137878</v>
       </c>
       <c r="B91" t="n">
-        <v>105741</v>
+        <v>80146</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548281</v>
+        <v>548705</v>
       </c>
       <c r="R91" t="n">
-        <v>7015128</v>
+        <v>7014750</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137790</v>
+        <v>129137778</v>
       </c>
       <c r="B92" t="n">
-        <v>105741</v>
+        <v>57831</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9686,21 +9686,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>103031</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548558</v>
+        <v>548706</v>
       </c>
       <c r="R92" t="n">
-        <v>7014771</v>
+        <v>7014864</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9746,6 +9746,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9772,10 +9777,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137764</v>
+        <v>129137901</v>
       </c>
       <c r="B93" t="n">
-        <v>97555</v>
+        <v>105741</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9783,21 +9788,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9807,10 +9812,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548590</v>
+        <v>548281</v>
       </c>
       <c r="R93" t="n">
-        <v>7015157</v>
+        <v>7015128</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9869,32 +9874,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137878</v>
+        <v>129137790</v>
       </c>
       <c r="B94" t="n">
-        <v>80146</v>
+        <v>105741</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9904,10 +9909,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548705</v>
+        <v>548558</v>
       </c>
       <c r="R94" t="n">
-        <v>7014750</v>
+        <v>7014771</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9966,10 +9971,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137778</v>
+        <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>57831</v>
+        <v>97555</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9977,21 +9982,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10001,10 +10006,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548706</v>
+        <v>548590</v>
       </c>
       <c r="R95" t="n">
-        <v>7014864</v>
+        <v>7015157</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10037,11 +10042,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10359,32 +10359,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137903</v>
+        <v>129137912</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>96797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548633</v>
+        <v>548604</v>
       </c>
       <c r="R99" t="n">
-        <v>7015045</v>
+        <v>7015234</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10456,10 +10456,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137848</v>
+        <v>129137903</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10467,21 +10467,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548598</v>
+        <v>548633</v>
       </c>
       <c r="R100" t="n">
-        <v>7015227</v>
+        <v>7015045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10527,11 +10527,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10558,32 +10553,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137912</v>
+        <v>129137848</v>
       </c>
       <c r="B101" t="n">
-        <v>96797</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10593,10 +10588,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548604</v>
+        <v>548598</v>
       </c>
       <c r="R101" t="n">
-        <v>7015234</v>
+        <v>7015227</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10629,6 +10624,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11242,32 +11242,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137847</v>
+        <v>129137768</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>80174</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548490</v>
+        <v>548723</v>
       </c>
       <c r="R108" t="n">
-        <v>7014739</v>
+        <v>7014940</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11313,11 +11313,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11344,7 +11339,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137844</v>
+        <v>129137847</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11379,10 +11374,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548672</v>
+        <v>548490</v>
       </c>
       <c r="R109" t="n">
-        <v>7014893</v>
+        <v>7014739</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11419,7 +11414,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11446,32 +11441,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137768</v>
+        <v>129137844</v>
       </c>
       <c r="B110" t="n">
-        <v>80174</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11481,10 +11476,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548723</v>
+        <v>548672</v>
       </c>
       <c r="R110" t="n">
-        <v>7014940</v>
+        <v>7014893</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11517,6 +11512,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137797</v>
+        <v>129137751</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548657</v>
+        <v>548268</v>
       </c>
       <c r="R6" t="n">
-        <v>7014768</v>
+        <v>7014891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,6 +1215,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,32 +1246,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137815</v>
+        <v>129137787</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548398</v>
+        <v>548366</v>
       </c>
       <c r="R7" t="n">
-        <v>7015004</v>
+        <v>7014942</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1321,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,32 +1348,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137817</v>
+        <v>129137870</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548367</v>
+        <v>548358</v>
       </c>
       <c r="R8" t="n">
-        <v>7014944</v>
+        <v>7014777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137740</v>
+        <v>129137817</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548618</v>
+        <v>548367</v>
       </c>
       <c r="R9" t="n">
-        <v>7015211</v>
+        <v>7014944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,11 +1516,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137751</v>
+        <v>129137797</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548268</v>
+        <v>548657</v>
       </c>
       <c r="R10" t="n">
-        <v>7014891</v>
+        <v>7014768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,11 +1613,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137787</v>
+        <v>129137815</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548366</v>
+        <v>548398</v>
       </c>
       <c r="R11" t="n">
-        <v>7014942</v>
+        <v>7015004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1714,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137870</v>
+        <v>129137740</v>
       </c>
       <c r="B12" t="n">
-        <v>97555</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548358</v>
+        <v>548618</v>
       </c>
       <c r="R12" t="n">
-        <v>7014777</v>
+        <v>7015211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137795</v>
+        <v>129137794</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548538</v>
+        <v>548459</v>
       </c>
       <c r="R13" t="n">
-        <v>7014770</v>
+        <v>7015186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,11 +1914,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,7 +1940,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1980,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R14" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,6 +2011,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137738</v>
+        <v>129137804</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548567</v>
+        <v>548550</v>
       </c>
       <c r="R15" t="n">
-        <v>7014763</v>
+        <v>7015142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,11 +2113,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137794</v>
+        <v>129137738</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,21 +2150,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2179,10 +2174,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548459</v>
+        <v>548567</v>
       </c>
       <c r="R16" t="n">
-        <v>7015186</v>
+        <v>7014763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,6 +2210,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2241,32 +2241,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137820</v>
+        <v>129137869</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548328</v>
+        <v>548335</v>
       </c>
       <c r="R17" t="n">
-        <v>7014882</v>
+        <v>7014782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,11 +2312,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,7 +2338,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137801</v>
+        <v>129137820</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548686</v>
+        <v>548328</v>
       </c>
       <c r="R18" t="n">
-        <v>7014817</v>
+        <v>7014882</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,6 +2409,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,7 +2440,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137802</v>
+        <v>129137801</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548499</v>
+        <v>548686</v>
       </c>
       <c r="R19" t="n">
-        <v>7014902</v>
+        <v>7014817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,32 +2537,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137869</v>
+        <v>129137802</v>
       </c>
       <c r="B20" t="n">
-        <v>97555</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548335</v>
+        <v>548499</v>
       </c>
       <c r="R20" t="n">
-        <v>7014782</v>
+        <v>7014902</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137906</v>
+        <v>129137771</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>80174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548693</v>
+        <v>548360</v>
       </c>
       <c r="R21" t="n">
-        <v>7014874</v>
+        <v>7014942</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,32 +2731,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137819</v>
+        <v>129137862</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548318</v>
+        <v>548497</v>
       </c>
       <c r="R22" t="n">
-        <v>7014904</v>
+        <v>7015181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137771</v>
+        <v>129137819</v>
       </c>
       <c r="B23" t="n">
-        <v>80174</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548360</v>
+        <v>548318</v>
       </c>
       <c r="R23" t="n">
-        <v>7014942</v>
+        <v>7014904</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137862</v>
+        <v>129137906</v>
       </c>
       <c r="B24" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548497</v>
+        <v>548693</v>
       </c>
       <c r="R24" t="n">
-        <v>7015181</v>
+        <v>7014874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3226,32 +3226,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129125929</v>
+        <v>129137810</v>
       </c>
       <c r="B27" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548372</v>
+        <v>548538</v>
       </c>
       <c r="R27" t="n">
-        <v>7014829</v>
+        <v>7015259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137810</v>
+        <v>129137806</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548538</v>
+        <v>548632</v>
       </c>
       <c r="R28" t="n">
-        <v>7015259</v>
+        <v>7015246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,32 +3420,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137806</v>
+        <v>129137876</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>80174</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548632</v>
+        <v>548475</v>
       </c>
       <c r="R29" t="n">
-        <v>7015246</v>
+        <v>7015265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,32 +3517,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137876</v>
+        <v>129137749</v>
       </c>
       <c r="B30" t="n">
-        <v>80174</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548475</v>
+        <v>548618</v>
       </c>
       <c r="R30" t="n">
-        <v>7015265</v>
+        <v>7015211</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,6 +3588,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3614,32 +3619,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137749</v>
+        <v>129125929</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>97575</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3649,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548618</v>
+        <v>548372</v>
       </c>
       <c r="R31" t="n">
-        <v>7015211</v>
+        <v>7014829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3685,11 +3690,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3821,7 +3821,7 @@
         <v>129137789</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>129137896</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>129126213</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>129137843</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5302,32 +5302,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137783</v>
+        <v>129137766</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>97581</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548595</v>
+        <v>548366</v>
       </c>
       <c r="R48" t="n">
-        <v>7015162</v>
+        <v>7014942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5404,10 +5404,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137891</v>
+        <v>129137783</v>
       </c>
       <c r="B49" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548627</v>
+        <v>548595</v>
       </c>
       <c r="R49" t="n">
-        <v>7015253</v>
+        <v>7015162</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5506,32 +5506,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137792</v>
+        <v>129137891</v>
       </c>
       <c r="B50" t="n">
-        <v>105741</v>
+        <v>98704</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548368</v>
+        <v>548627</v>
       </c>
       <c r="R50" t="n">
-        <v>7014860</v>
+        <v>7015253</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,32 +5608,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137786</v>
+        <v>129137792</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>105767</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548402</v>
+        <v>548368</v>
       </c>
       <c r="R51" t="n">
-        <v>7015096</v>
+        <v>7014860</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>15 stycken kan finnas mer I mossan</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137766</v>
+        <v>129137786</v>
       </c>
       <c r="B52" t="n">
-        <v>97555</v>
+        <v>98704</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548366</v>
+        <v>548402</v>
       </c>
       <c r="R52" t="n">
-        <v>7014942</v>
+        <v>7015096</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>5 exemplar</t>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137739</v>
+        <v>129137905</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548460</v>
+        <v>548618</v>
       </c>
       <c r="R53" t="n">
-        <v>7014976</v>
+        <v>7015116</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,11 +5883,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5914,10 +5909,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137845</v>
+        <v>129126001</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5925,21 +5920,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5949,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548531</v>
+        <v>548299</v>
       </c>
       <c r="R54" t="n">
-        <v>7014817</v>
+        <v>7014876</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5985,11 +5980,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6016,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137746</v>
+        <v>129137877</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>80174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6051,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548355</v>
+        <v>548334</v>
       </c>
       <c r="R55" t="n">
-        <v>7014874</v>
+        <v>7015001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6087,11 +6077,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6118,10 +6103,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129126001</v>
+        <v>129137882</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6129,21 +6114,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6153,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548299</v>
+        <v>548510</v>
       </c>
       <c r="R56" t="n">
-        <v>7014876</v>
+        <v>7015191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6215,10 +6200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137905</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6226,21 +6211,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6250,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548618</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7015116</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6286,6 +6271,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6312,32 +6302,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137877</v>
+        <v>129137845</v>
       </c>
       <c r="B58" t="n">
-        <v>80174</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6347,10 +6337,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548334</v>
+        <v>548531</v>
       </c>
       <c r="R58" t="n">
-        <v>7015001</v>
+        <v>7014817</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6383,6 +6373,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6409,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137882</v>
+        <v>129137746</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6420,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6444,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548510</v>
+        <v>548355</v>
       </c>
       <c r="R59" t="n">
-        <v>7015191</v>
+        <v>7014874</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6480,6 +6475,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6713,7 +6713,7 @@
         <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7200,32 +7200,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137857</v>
+        <v>129137890</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548502</v>
+        <v>548594</v>
       </c>
       <c r="R67" t="n">
-        <v>7015176</v>
+        <v>7015211</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,10 +7302,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137858</v>
+        <v>129137791</v>
       </c>
       <c r="B68" t="n">
-        <v>56917</v>
+        <v>105767</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7313,21 +7313,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548400</v>
+        <v>548452</v>
       </c>
       <c r="R68" t="n">
-        <v>7015152</v>
+        <v>7014769</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,11 +7373,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7404,10 +7399,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137762</v>
+        <v>129137858</v>
       </c>
       <c r="B69" t="n">
-        <v>97555</v>
+        <v>56917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7415,21 +7410,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7439,10 +7434,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548603</v>
+        <v>548400</v>
       </c>
       <c r="R69" t="n">
-        <v>7014709</v>
+        <v>7015152</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7475,6 +7470,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7501,32 +7501,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137890</v>
+        <v>129137857</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548594</v>
+        <v>548502</v>
       </c>
       <c r="R70" t="n">
-        <v>7015211</v>
+        <v>7015176</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7603,10 +7603,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137791</v>
+        <v>129137762</v>
       </c>
       <c r="B71" t="n">
-        <v>105741</v>
+        <v>97581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548452</v>
+        <v>548603</v>
       </c>
       <c r="R71" t="n">
-        <v>7014769</v>
+        <v>7014709</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137902</v>
+        <v>129137773</v>
       </c>
       <c r="B72" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7711,21 +7711,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548480</v>
+        <v>548717</v>
       </c>
       <c r="R72" t="n">
-        <v>7015285</v>
+        <v>7014991</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7797,32 +7797,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137850</v>
+        <v>129137886</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>80182</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548629</v>
+        <v>548498</v>
       </c>
       <c r="R73" t="n">
-        <v>7015262</v>
+        <v>7015173</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7868,11 +7868,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7899,10 +7894,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137748</v>
+        <v>129137850</v>
       </c>
       <c r="B74" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7910,21 +7905,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7934,10 +7929,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548710</v>
+        <v>548629</v>
       </c>
       <c r="R74" t="n">
-        <v>7014904</v>
+        <v>7015262</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7974,7 +7969,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8001,32 +7996,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137780</v>
+        <v>129137902</v>
       </c>
       <c r="B75" t="n">
-        <v>98678</v>
+        <v>91558</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8036,10 +8031,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548594</v>
+        <v>548480</v>
       </c>
       <c r="R75" t="n">
-        <v>7015114</v>
+        <v>7015285</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8072,11 +8067,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8103,10 +8093,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137773</v>
+        <v>129137748</v>
       </c>
       <c r="B76" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8114,21 +8104,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8138,10 +8128,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548717</v>
+        <v>548710</v>
       </c>
       <c r="R76" t="n">
-        <v>7014991</v>
+        <v>7014904</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8174,6 +8164,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8200,32 +8195,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137886</v>
+        <v>129137780</v>
       </c>
       <c r="B77" t="n">
-        <v>80182</v>
+        <v>98704</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548498</v>
+        <v>548594</v>
       </c>
       <c r="R77" t="n">
-        <v>7015173</v>
+        <v>7015114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8271,6 +8266,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8297,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137818</v>
+        <v>129137759</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>97575</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548329</v>
+        <v>548487</v>
       </c>
       <c r="R78" t="n">
-        <v>7014932</v>
+        <v>7014855</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,32 +8394,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137759</v>
+        <v>129137779</v>
       </c>
       <c r="B79" t="n">
-        <v>97549</v>
+        <v>98704</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548487</v>
+        <v>548620</v>
       </c>
       <c r="R79" t="n">
-        <v>7014855</v>
+        <v>7014685</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8465,6 +8465,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8491,32 +8496,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137779</v>
+        <v>129137813</v>
       </c>
       <c r="B80" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8526,10 +8531,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548620</v>
+        <v>548374</v>
       </c>
       <c r="R80" t="n">
-        <v>7014685</v>
+        <v>7015064</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8562,11 +8567,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8593,7 +8593,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137813</v>
+        <v>129137818</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548374</v>
+        <v>548329</v>
       </c>
       <c r="R81" t="n">
-        <v>7015064</v>
+        <v>7014932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8690,10 +8690,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137805</v>
+        <v>129137745</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8701,21 +8701,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548613</v>
+        <v>548373</v>
       </c>
       <c r="R82" t="n">
-        <v>7015186</v>
+        <v>7014966</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8761,6 +8761,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8787,32 +8792,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137816</v>
+        <v>129137871</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8822,10 +8827,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548400</v>
+        <v>548457</v>
       </c>
       <c r="R83" t="n">
-        <v>7014970</v>
+        <v>7014764</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8884,32 +8889,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137796</v>
+        <v>129137872</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8919,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548559</v>
+        <v>548477</v>
       </c>
       <c r="R84" t="n">
-        <v>7014776</v>
+        <v>7015144</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8981,32 +8986,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137900</v>
+        <v>129137805</v>
       </c>
       <c r="B85" t="n">
-        <v>105741</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9016,10 +9021,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548451</v>
+        <v>548613</v>
       </c>
       <c r="R85" t="n">
-        <v>7014746</v>
+        <v>7015186</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9078,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137889</v>
+        <v>129137796</v>
       </c>
       <c r="B86" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9113,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548440</v>
+        <v>548559</v>
       </c>
       <c r="R86" t="n">
-        <v>7014752</v>
+        <v>7014776</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9149,11 +9154,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9180,32 +9180,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137781</v>
+        <v>129137816</v>
       </c>
       <c r="B87" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548433</v>
+        <v>548400</v>
       </c>
       <c r="R87" t="n">
-        <v>7014771</v>
+        <v>7014970</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9251,11 +9251,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,32 +9277,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137745</v>
+        <v>129137900</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>105767</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9312,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548373</v>
+        <v>548451</v>
       </c>
       <c r="R88" t="n">
-        <v>7014966</v>
+        <v>7014746</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,11 +9348,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9384,32 +9374,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137871</v>
+        <v>129137889</v>
       </c>
       <c r="B89" t="n">
-        <v>97555</v>
+        <v>98704</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9419,10 +9409,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548457</v>
+        <v>548440</v>
       </c>
       <c r="R89" t="n">
-        <v>7014764</v>
+        <v>7014752</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9455,6 +9445,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9476,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137872</v>
+        <v>129137781</v>
       </c>
       <c r="B90" t="n">
-        <v>97555</v>
+        <v>98704</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9511,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548477</v>
+        <v>548433</v>
       </c>
       <c r="R90" t="n">
-        <v>7015144</v>
+        <v>7014771</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9552,6 +9547,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9780,7 +9780,7 @@
         <v>129137901</v>
       </c>
       <c r="B93" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>129137790</v>
       </c>
       <c r="B94" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10262,10 +10262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137863</v>
+        <v>129137903</v>
       </c>
       <c r="B98" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10273,21 +10273,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548702</v>
+        <v>548633</v>
       </c>
       <c r="R98" t="n">
-        <v>7014752</v>
+        <v>7015045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10359,10 +10359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137912</v>
+        <v>129137874</v>
       </c>
       <c r="B99" t="n">
-        <v>96797</v>
+        <v>97581</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548604</v>
+        <v>548348</v>
       </c>
       <c r="R99" t="n">
-        <v>7015234</v>
+        <v>7014988</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10456,32 +10456,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137903</v>
+        <v>129137912</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>96823</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548633</v>
+        <v>548604</v>
       </c>
       <c r="R100" t="n">
-        <v>7015045</v>
+        <v>7015234</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137848</v>
+        <v>129137863</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10564,21 +10564,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10588,10 +10588,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548598</v>
+        <v>548702</v>
       </c>
       <c r="R101" t="n">
-        <v>7015227</v>
+        <v>7014752</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10624,11 +10624,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10655,32 +10650,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137788</v>
+        <v>129137848</v>
       </c>
       <c r="B102" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10690,10 +10685,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548605</v>
+        <v>548598</v>
       </c>
       <c r="R102" t="n">
-        <v>7014687</v>
+        <v>7015227</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10730,7 +10725,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10757,32 +10752,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137874</v>
+        <v>129137788</v>
       </c>
       <c r="B103" t="n">
-        <v>97555</v>
+        <v>98704</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10792,10 +10787,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548348</v>
+        <v>548605</v>
       </c>
       <c r="R103" t="n">
-        <v>7014988</v>
+        <v>7014687</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10828,6 +10823,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10854,10 +10854,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137753</v>
+        <v>129137883</v>
       </c>
       <c r="B104" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10865,21 +10865,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548681</v>
+        <v>548499</v>
       </c>
       <c r="R104" t="n">
-        <v>7015193</v>
+        <v>7015176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10951,32 +10951,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137883</v>
+        <v>129137758</v>
       </c>
       <c r="B105" t="n">
-        <v>80146</v>
+        <v>97575</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548499</v>
+        <v>548629</v>
       </c>
       <c r="R105" t="n">
-        <v>7015176</v>
+        <v>7014777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11048,32 +11048,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137758</v>
+        <v>129137753</v>
       </c>
       <c r="B106" t="n">
-        <v>97549</v>
+        <v>91837</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11083,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548629</v>
+        <v>548681</v>
       </c>
       <c r="R106" t="n">
-        <v>7014777</v>
+        <v>7015193</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
         <v>129137840</v>
       </c>
       <c r="B107" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11339,32 +11339,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137847</v>
+        <v>129137873</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>97581</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11374,10 +11374,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548490</v>
+        <v>548291</v>
       </c>
       <c r="R109" t="n">
-        <v>7014739</v>
+        <v>7015110</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11410,11 +11410,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11441,32 +11436,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137844</v>
+        <v>129137761</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>97575</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11476,10 +11471,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548672</v>
+        <v>548366</v>
       </c>
       <c r="R110" t="n">
-        <v>7014893</v>
+        <v>7015047</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11512,11 +11507,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11543,32 +11533,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137873</v>
+        <v>129137847</v>
       </c>
       <c r="B111" t="n">
-        <v>97555</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11578,10 +11568,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548291</v>
+        <v>548490</v>
       </c>
       <c r="R111" t="n">
-        <v>7015110</v>
+        <v>7014739</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11614,6 +11604,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11640,32 +11635,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137761</v>
+        <v>129137844</v>
       </c>
       <c r="B112" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11675,10 +11670,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548366</v>
+        <v>548672</v>
       </c>
       <c r="R112" t="n">
-        <v>7015047</v>
+        <v>7014893</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11711,6 +11706,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137751</v>
+        <v>129137817</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548268</v>
+        <v>548367</v>
       </c>
       <c r="R6" t="n">
-        <v>7014891</v>
+        <v>7014944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,11 +1215,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,32 +1241,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137787</v>
+        <v>129137797</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548366</v>
+        <v>548657</v>
       </c>
       <c r="R7" t="n">
-        <v>7014942</v>
+        <v>7014768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,11 +1312,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,32 +1338,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137870</v>
+        <v>129137815</v>
       </c>
       <c r="B8" t="n">
-        <v>97581</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548358</v>
+        <v>548398</v>
       </c>
       <c r="R8" t="n">
-        <v>7014777</v>
+        <v>7015004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,6 +1409,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137817</v>
+        <v>129137740</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548367</v>
+        <v>548618</v>
       </c>
       <c r="R9" t="n">
-        <v>7014944</v>
+        <v>7015211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,6 +1511,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137797</v>
+        <v>129137751</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548657</v>
+        <v>548268</v>
       </c>
       <c r="R10" t="n">
-        <v>7014768</v>
+        <v>7014891</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137815</v>
+        <v>129137870</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>97582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548398</v>
+        <v>548358</v>
       </c>
       <c r="R11" t="n">
-        <v>7015004</v>
+        <v>7014777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137740</v>
+        <v>129137787</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548618</v>
+        <v>548366</v>
       </c>
       <c r="R12" t="n">
-        <v>7015211</v>
+        <v>7014942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137794</v>
+        <v>129137738</v>
       </c>
       <c r="B13" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548459</v>
+        <v>548567</v>
       </c>
       <c r="R13" t="n">
-        <v>7015186</v>
+        <v>7014763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,6 +1914,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137795</v>
+        <v>129137794</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,23 +1956,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1975,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548538</v>
+        <v>548459</v>
       </c>
       <c r="R14" t="n">
-        <v>7014770</v>
+        <v>7015186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,11 +2012,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,7 +2038,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2077,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R15" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,6 +2109,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137738</v>
+        <v>129137804</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2174,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548567</v>
+        <v>548550</v>
       </c>
       <c r="R16" t="n">
-        <v>7014763</v>
+        <v>7015142</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,11 +2211,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2241,32 +2237,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137869</v>
+        <v>129137820</v>
       </c>
       <c r="B17" t="n">
-        <v>97581</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548335</v>
+        <v>548328</v>
       </c>
       <c r="R17" t="n">
-        <v>7014782</v>
+        <v>7014882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,6 +2308,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,7 +2339,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137820</v>
+        <v>129137801</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2373,10 +2374,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548328</v>
+        <v>548686</v>
       </c>
       <c r="R18" t="n">
-        <v>7014882</v>
+        <v>7014817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,7 +2436,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137801</v>
+        <v>129137802</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2475,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548686</v>
+        <v>548499</v>
       </c>
       <c r="R19" t="n">
-        <v>7014817</v>
+        <v>7014902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,32 +2533,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137802</v>
+        <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>97582</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548499</v>
+        <v>548335</v>
       </c>
       <c r="R20" t="n">
-        <v>7014902</v>
+        <v>7014782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,32 +2630,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137771</v>
+        <v>129137750</v>
       </c>
       <c r="B21" t="n">
-        <v>80174</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548360</v>
+        <v>548514</v>
       </c>
       <c r="R21" t="n">
-        <v>7014942</v>
+        <v>7015227</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,6 +2701,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2731,10 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137862</v>
+        <v>129137771</v>
       </c>
       <c r="B22" t="n">
-        <v>80175</v>
+        <v>80174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,21 +2743,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548497</v>
+        <v>548360</v>
       </c>
       <c r="R22" t="n">
-        <v>7015181</v>
+        <v>7014942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,32 +2829,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137819</v>
+        <v>129137862</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548318</v>
+        <v>548497</v>
       </c>
       <c r="R23" t="n">
-        <v>7014904</v>
+        <v>7015181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137750</v>
+        <v>129137819</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3057,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548514</v>
+        <v>548318</v>
       </c>
       <c r="R25" t="n">
-        <v>7015227</v>
+        <v>7014904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,11 +3094,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137810</v>
+        <v>129137749</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3261,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548538</v>
+        <v>548618</v>
       </c>
       <c r="R27" t="n">
-        <v>7015259</v>
+        <v>7015211</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,6 +3293,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3323,32 +3324,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137806</v>
+        <v>129125929</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3358,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548632</v>
+        <v>548372</v>
       </c>
       <c r="R28" t="n">
-        <v>7015246</v>
+        <v>7014829</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137749</v>
+        <v>129137810</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548618</v>
+        <v>548538</v>
       </c>
       <c r="R30" t="n">
-        <v>7015211</v>
+        <v>7015259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,11 +3589,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3619,32 +3615,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129125929</v>
+        <v>129137806</v>
       </c>
       <c r="B31" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548372</v>
+        <v>548632</v>
       </c>
       <c r="R31" t="n">
-        <v>7014829</v>
+        <v>7015246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137849</v>
+        <v>129137800</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3751,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548629</v>
+        <v>548708</v>
       </c>
       <c r="R32" t="n">
-        <v>7015247</v>
+        <v>7014937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,7 +3787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3818,32 +3814,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137789</v>
+        <v>129137821</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3853,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548461</v>
+        <v>548369</v>
       </c>
       <c r="R33" t="n">
-        <v>7015210</v>
+        <v>7014853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,11 +3885,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3920,10 +3911,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137896</v>
+        <v>129137789</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3955,10 +3946,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548260</v>
+        <v>548461</v>
       </c>
       <c r="R34" t="n">
-        <v>7014898</v>
+        <v>7015210</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,7 +3986,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4022,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129126213</v>
+        <v>129137896</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,21 +4041,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548265</v>
+        <v>548260</v>
       </c>
       <c r="R35" t="n">
-        <v>7014876</v>
+        <v>7014898</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,6 +4084,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,45 +4115,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137800</v>
+        <v>129126213</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548708</v>
+        <v>548265</v>
       </c>
       <c r="R36" t="n">
-        <v>7014937</v>
+        <v>7014876</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,11 +4190,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4225,10 +4216,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137821</v>
+        <v>129137849</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4236,21 +4227,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4260,10 +4251,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548369</v>
+        <v>548629</v>
       </c>
       <c r="R37" t="n">
-        <v>7014853</v>
+        <v>7015247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,6 +4287,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4322,32 +4318,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137774</v>
+        <v>129137772</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>80174</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4357,10 +4353,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548482</v>
+        <v>548364</v>
       </c>
       <c r="R38" t="n">
-        <v>7015213</v>
+        <v>7015065</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4419,32 +4415,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137772</v>
+        <v>129137774</v>
       </c>
       <c r="B39" t="n">
-        <v>80174</v>
+        <v>80146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4450,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548364</v>
+        <v>548482</v>
       </c>
       <c r="R39" t="n">
-        <v>7015065</v>
+        <v>7015213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4718,7 +4714,7 @@
         <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,32 +5007,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137803</v>
+        <v>129137766</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>97582</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5042,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548467</v>
+        <v>548366</v>
       </c>
       <c r="R45" t="n">
-        <v>7014995</v>
+        <v>7014942</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,6 +5078,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5108,7 +5109,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137814</v>
+        <v>129137803</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5143,10 +5144,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548376</v>
+        <v>548467</v>
       </c>
       <c r="R46" t="n">
-        <v>7015053</v>
+        <v>7014995</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5205,10 +5206,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137822</v>
+        <v>129137814</v>
       </c>
       <c r="B47" t="n">
-        <v>57648</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,21 +5217,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5241,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548346</v>
+        <v>548376</v>
       </c>
       <c r="R47" t="n">
-        <v>7015026</v>
+        <v>7015053</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5302,32 +5303,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137766</v>
+        <v>129137822</v>
       </c>
       <c r="B48" t="n">
-        <v>97581</v>
+        <v>57648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>100001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5337,10 +5338,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548366</v>
+        <v>548346</v>
       </c>
       <c r="R48" t="n">
-        <v>7014942</v>
+        <v>7015026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5373,11 +5374,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5404,10 +5400,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137783</v>
+        <v>129137786</v>
       </c>
       <c r="B49" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5439,10 +5435,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548595</v>
+        <v>548402</v>
       </c>
       <c r="R49" t="n">
-        <v>7015162</v>
+        <v>7015096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5479,7 +5475,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5506,32 +5502,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137891</v>
+        <v>129137792</v>
       </c>
       <c r="B50" t="n">
-        <v>98704</v>
+        <v>105769</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5541,10 +5537,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548627</v>
+        <v>548368</v>
       </c>
       <c r="R50" t="n">
-        <v>7015253</v>
+        <v>7014860</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5581,7 +5577,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,32 +5604,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137792</v>
+        <v>129137783</v>
       </c>
       <c r="B51" t="n">
-        <v>105767</v>
+        <v>98705</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548368</v>
+        <v>548595</v>
       </c>
       <c r="R51" t="n">
-        <v>7014860</v>
+        <v>7015162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5683,7 +5679,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,10 +5706,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137786</v>
+        <v>129137891</v>
       </c>
       <c r="B52" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5745,10 +5741,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548402</v>
+        <v>548627</v>
       </c>
       <c r="R52" t="n">
-        <v>7015096</v>
+        <v>7015253</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5785,7 +5781,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>15 stycken kan finnas mer I mossan</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,10 +5808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137905</v>
+        <v>129137739</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5823,21 +5819,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548618</v>
+        <v>548460</v>
       </c>
       <c r="R53" t="n">
-        <v>7015116</v>
+        <v>7014976</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,6 +5879,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5909,32 +5910,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129126001</v>
+        <v>129137877</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>80174</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5944,10 +5945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548299</v>
+        <v>548334</v>
       </c>
       <c r="R54" t="n">
-        <v>7014876</v>
+        <v>7015001</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6006,32 +6007,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137877</v>
+        <v>129137882</v>
       </c>
       <c r="B55" t="n">
-        <v>80174</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6042,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548334</v>
+        <v>548510</v>
       </c>
       <c r="R55" t="n">
-        <v>7015001</v>
+        <v>7015191</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,10 +6104,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137882</v>
+        <v>129137905</v>
       </c>
       <c r="B56" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,21 +6115,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6138,10 +6139,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548510</v>
+        <v>548618</v>
       </c>
       <c r="R56" t="n">
-        <v>7015191</v>
+        <v>7015116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6200,10 +6201,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137739</v>
+        <v>129126001</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6212,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6236,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548460</v>
+        <v>548299</v>
       </c>
       <c r="R57" t="n">
-        <v>7014976</v>
+        <v>7014876</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6271,11 +6272,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6302,7 +6298,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137845</v>
+        <v>129137746</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6337,10 +6333,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548531</v>
+        <v>548355</v>
       </c>
       <c r="R58" t="n">
-        <v>7014817</v>
+        <v>7014874</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6377,7 +6373,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6404,7 +6400,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137746</v>
+        <v>129137845</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6439,10 +6435,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548355</v>
+        <v>548531</v>
       </c>
       <c r="R59" t="n">
-        <v>7014874</v>
+        <v>7014817</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6479,7 +6475,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6713,7 +6709,7 @@
         <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6807,32 +6803,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137769</v>
+        <v>129137782</v>
       </c>
       <c r="B63" t="n">
-        <v>80174</v>
+        <v>98705</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6842,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548487</v>
+        <v>548485</v>
       </c>
       <c r="R63" t="n">
-        <v>7015073</v>
+        <v>7014854</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6878,6 +6874,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6904,7 +6905,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137875</v>
+        <v>129137769</v>
       </c>
       <c r="B64" t="n">
         <v>80174</v>
@@ -6939,10 +6940,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548581</v>
+        <v>548487</v>
       </c>
       <c r="R64" t="n">
-        <v>7015017</v>
+        <v>7015073</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7001,32 +7002,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137782</v>
+        <v>129137875</v>
       </c>
       <c r="B65" t="n">
-        <v>98704</v>
+        <v>80174</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7037,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548485</v>
+        <v>548581</v>
       </c>
       <c r="R65" t="n">
-        <v>7014854</v>
+        <v>7015017</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,11 +7073,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7103,32 +7099,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137811</v>
+        <v>129137890</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7138,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548458</v>
+        <v>548594</v>
       </c>
       <c r="R66" t="n">
-        <v>7015205</v>
+        <v>7015211</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,6 +7170,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,32 +7201,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137890</v>
+        <v>129137791</v>
       </c>
       <c r="B67" t="n">
-        <v>98704</v>
+        <v>105769</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7236,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548594</v>
+        <v>548452</v>
       </c>
       <c r="R67" t="n">
-        <v>7015211</v>
+        <v>7014769</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,11 +7272,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,32 +7298,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137791</v>
+        <v>129137811</v>
       </c>
       <c r="B68" t="n">
-        <v>105767</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7333,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548452</v>
+        <v>548458</v>
       </c>
       <c r="R68" t="n">
-        <v>7014769</v>
+        <v>7015205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7606,7 +7602,7 @@
         <v>129137762</v>
       </c>
       <c r="B71" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7894,10 +7890,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137850</v>
+        <v>129137748</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7905,21 +7901,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7929,10 +7925,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548629</v>
+        <v>548710</v>
       </c>
       <c r="R74" t="n">
-        <v>7015262</v>
+        <v>7014904</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7969,7 +7965,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,32 +7992,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137902</v>
+        <v>129137780</v>
       </c>
       <c r="B75" t="n">
-        <v>91558</v>
+        <v>98705</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8031,10 +8027,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548480</v>
+        <v>548594</v>
       </c>
       <c r="R75" t="n">
-        <v>7015285</v>
+        <v>7015114</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8067,6 +8063,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8093,10 +8094,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137748</v>
+        <v>129137902</v>
       </c>
       <c r="B76" t="n">
-        <v>57887</v>
+        <v>91560</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,23 +8105,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8128,10 +8125,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548710</v>
+        <v>548480</v>
       </c>
       <c r="R76" t="n">
-        <v>7014904</v>
+        <v>7015285</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8164,11 +8161,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8195,32 +8187,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137780</v>
+        <v>129137850</v>
       </c>
       <c r="B77" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8230,10 +8222,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548594</v>
+        <v>548629</v>
       </c>
       <c r="R77" t="n">
-        <v>7015114</v>
+        <v>7015262</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8262,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8297,32 +8289,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137759</v>
+        <v>129137813</v>
       </c>
       <c r="B78" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8332,10 +8324,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548487</v>
+        <v>548374</v>
       </c>
       <c r="R78" t="n">
-        <v>7014855</v>
+        <v>7015064</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,32 +8386,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B79" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8429,10 +8421,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R79" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8465,11 +8457,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8496,32 +8483,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137813</v>
+        <v>129137759</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8531,10 +8518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548374</v>
+        <v>548487</v>
       </c>
       <c r="R80" t="n">
-        <v>7015064</v>
+        <v>7014855</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,32 +8580,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137818</v>
+        <v>129137779</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8628,10 +8615,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548329</v>
+        <v>548620</v>
       </c>
       <c r="R81" t="n">
-        <v>7014932</v>
+        <v>7014685</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8664,6 +8651,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8690,10 +8682,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137745</v>
+        <v>129137805</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8701,21 +8693,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548373</v>
+        <v>548613</v>
       </c>
       <c r="R82" t="n">
-        <v>7014966</v>
+        <v>7015186</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8761,11 +8753,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8792,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137871</v>
+        <v>129137796</v>
       </c>
       <c r="B83" t="n">
-        <v>97581</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8827,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548457</v>
+        <v>548559</v>
       </c>
       <c r="R83" t="n">
-        <v>7014764</v>
+        <v>7014776</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8889,32 +8876,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137872</v>
+        <v>129137816</v>
       </c>
       <c r="B84" t="n">
-        <v>97581</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8924,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548477</v>
+        <v>548400</v>
       </c>
       <c r="R84" t="n">
-        <v>7015144</v>
+        <v>7014970</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8986,10 +8973,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137805</v>
+        <v>129137745</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8997,21 +8984,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9021,10 +9008,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548613</v>
+        <v>548373</v>
       </c>
       <c r="R85" t="n">
-        <v>7015186</v>
+        <v>7014966</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9057,6 +9044,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9083,32 +9075,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137796</v>
+        <v>129137871</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>97582</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9110,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548559</v>
+        <v>548457</v>
       </c>
       <c r="R86" t="n">
-        <v>7014776</v>
+        <v>7014764</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,32 +9172,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137816</v>
+        <v>129137872</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>97582</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9215,10 +9207,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548400</v>
+        <v>548477</v>
       </c>
       <c r="R87" t="n">
-        <v>7014970</v>
+        <v>7015144</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9277,32 +9269,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137900</v>
+        <v>129137781</v>
       </c>
       <c r="B88" t="n">
-        <v>105767</v>
+        <v>98705</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9312,10 +9304,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548451</v>
+        <v>548433</v>
       </c>
       <c r="R88" t="n">
-        <v>7014746</v>
+        <v>7014771</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9348,6 +9340,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9374,32 +9371,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137889</v>
+        <v>129137900</v>
       </c>
       <c r="B89" t="n">
-        <v>98704</v>
+        <v>105769</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9409,10 +9406,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548440</v>
+        <v>548451</v>
       </c>
       <c r="R89" t="n">
-        <v>7014752</v>
+        <v>7014746</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9445,11 +9442,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9476,10 +9468,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137781</v>
+        <v>129137889</v>
       </c>
       <c r="B90" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9511,10 +9503,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548433</v>
+        <v>548440</v>
       </c>
       <c r="R90" t="n">
-        <v>7014771</v>
+        <v>7014752</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,7 +9543,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>11 stycken kan finnas mer I mossan</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9578,32 +9570,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137878</v>
+        <v>129137778</v>
       </c>
       <c r="B91" t="n">
-        <v>80146</v>
+        <v>57831</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9613,10 +9605,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548705</v>
+        <v>548706</v>
       </c>
       <c r="R91" t="n">
-        <v>7014750</v>
+        <v>7014864</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9649,6 +9641,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9675,32 +9672,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137778</v>
+        <v>129137878</v>
       </c>
       <c r="B92" t="n">
-        <v>57831</v>
+        <v>80146</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9710,10 +9707,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548706</v>
+        <v>548705</v>
       </c>
       <c r="R92" t="n">
-        <v>7014864</v>
+        <v>7014750</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9746,11 +9743,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9777,10 +9769,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137901</v>
+        <v>129137764</v>
       </c>
       <c r="B93" t="n">
-        <v>105767</v>
+        <v>97582</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9788,21 +9780,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9812,10 +9804,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548281</v>
+        <v>548590</v>
       </c>
       <c r="R93" t="n">
-        <v>7015128</v>
+        <v>7015157</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9877,7 +9869,7 @@
         <v>129137790</v>
       </c>
       <c r="B94" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,10 +9963,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137764</v>
+        <v>129137901</v>
       </c>
       <c r="B95" t="n">
-        <v>97581</v>
+        <v>105769</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9982,21 +9974,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10006,10 +9998,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548590</v>
+        <v>548281</v>
       </c>
       <c r="R95" t="n">
-        <v>7015157</v>
+        <v>7015128</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10068,27 +10060,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10103,10 +10095,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R96" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10165,27 +10157,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137911</v>
+        <v>129137908</v>
       </c>
       <c r="B97" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10200,10 +10192,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548512</v>
+        <v>548306</v>
       </c>
       <c r="R97" t="n">
-        <v>7015192</v>
+        <v>7015082</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10262,32 +10254,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137903</v>
+        <v>129137788</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10297,10 +10289,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548633</v>
+        <v>548605</v>
       </c>
       <c r="R98" t="n">
-        <v>7015045</v>
+        <v>7014687</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10333,6 +10325,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10359,10 +10356,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137874</v>
+        <v>129137912</v>
       </c>
       <c r="B99" t="n">
-        <v>97581</v>
+        <v>96824</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10370,21 +10367,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10394,10 +10391,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548348</v>
+        <v>548604</v>
       </c>
       <c r="R99" t="n">
-        <v>7014988</v>
+        <v>7015234</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10456,32 +10453,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137912</v>
+        <v>129137863</v>
       </c>
       <c r="B100" t="n">
-        <v>96823</v>
+        <v>80147</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2869</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10491,10 +10488,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548604</v>
+        <v>548702</v>
       </c>
       <c r="R100" t="n">
-        <v>7015234</v>
+        <v>7014752</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10553,10 +10550,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137863</v>
+        <v>129137903</v>
       </c>
       <c r="B101" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10564,21 +10561,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10588,10 +10585,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548702</v>
+        <v>548633</v>
       </c>
       <c r="R101" t="n">
-        <v>7014752</v>
+        <v>7015045</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10752,32 +10749,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137788</v>
+        <v>129137874</v>
       </c>
       <c r="B103" t="n">
-        <v>98704</v>
+        <v>97582</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10787,10 +10784,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548605</v>
+        <v>548348</v>
       </c>
       <c r="R103" t="n">
-        <v>7014687</v>
+        <v>7014988</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10823,11 +10820,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10951,32 +10943,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137758</v>
+        <v>129137753</v>
       </c>
       <c r="B105" t="n">
-        <v>97575</v>
+        <v>91838</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10986,10 +10978,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548629</v>
+        <v>548681</v>
       </c>
       <c r="R105" t="n">
-        <v>7014777</v>
+        <v>7015193</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11048,10 +11040,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137753</v>
+        <v>129137840</v>
       </c>
       <c r="B106" t="n">
-        <v>91837</v>
+        <v>91540</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11059,21 +11051,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11083,10 +11075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548681</v>
+        <v>548660</v>
       </c>
       <c r="R106" t="n">
-        <v>7015193</v>
+        <v>7014820</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11145,32 +11137,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137840</v>
+        <v>129137758</v>
       </c>
       <c r="B107" t="n">
-        <v>91540</v>
+        <v>97576</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11180,10 +11172,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548660</v>
+        <v>548629</v>
       </c>
       <c r="R107" t="n">
-        <v>7014820</v>
+        <v>7014777</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11339,32 +11331,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137873</v>
+        <v>129137844</v>
       </c>
       <c r="B109" t="n">
-        <v>97581</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11374,10 +11366,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548291</v>
+        <v>548672</v>
       </c>
       <c r="R109" t="n">
-        <v>7015110</v>
+        <v>7014893</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11410,6 +11402,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11436,32 +11433,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137761</v>
+        <v>129137847</v>
       </c>
       <c r="B110" t="n">
-        <v>97575</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11471,10 +11468,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548366</v>
+        <v>548490</v>
       </c>
       <c r="R110" t="n">
-        <v>7015047</v>
+        <v>7014739</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11507,6 +11504,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11533,32 +11535,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137847</v>
+        <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>57727</v>
+        <v>97582</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11568,10 +11570,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548490</v>
+        <v>548291</v>
       </c>
       <c r="R111" t="n">
-        <v>7014739</v>
+        <v>7015110</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11604,11 +11606,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11635,32 +11632,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137844</v>
+        <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>57727</v>
+        <v>97576</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11670,10 +11667,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548672</v>
+        <v>548366</v>
       </c>
       <c r="R112" t="n">
-        <v>7014893</v>
+        <v>7015047</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11706,11 +11703,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137870</v>
+        <v>129137787</v>
       </c>
       <c r="B11" t="n">
-        <v>97582</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548358</v>
+        <v>548366</v>
       </c>
       <c r="R11" t="n">
-        <v>7014777</v>
+        <v>7014942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137787</v>
+        <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>97583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548366</v>
+        <v>548358</v>
       </c>
       <c r="R12" t="n">
-        <v>7014942</v>
+        <v>7014777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1817,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137738</v>
+        <v>129137795</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548567</v>
+        <v>548538</v>
       </c>
       <c r="R13" t="n">
-        <v>7014763</v>
+        <v>7014770</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B14" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,19 +1956,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1976,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R14" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137795</v>
+        <v>129137794</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,23 +2053,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548538</v>
+        <v>548459</v>
       </c>
       <c r="R15" t="n">
-        <v>7014770</v>
+        <v>7015186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,11 +2109,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137804</v>
+        <v>129137738</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,21 +2146,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548550</v>
+        <v>548567</v>
       </c>
       <c r="R16" t="n">
-        <v>7015142</v>
+        <v>7014763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,6 +2206,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2536,7 +2536,7 @@
         <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137750</v>
+        <v>129137906</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548514</v>
+        <v>548693</v>
       </c>
       <c r="R21" t="n">
-        <v>7015227</v>
+        <v>7014874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,11 +2701,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,32 +2824,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R23" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,32 +2921,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137906</v>
+        <v>129137862</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548693</v>
+        <v>548497</v>
       </c>
       <c r="R24" t="n">
-        <v>7014874</v>
+        <v>7015181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3018,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137819</v>
+        <v>129137744</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3029,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548318</v>
+        <v>548511</v>
       </c>
       <c r="R25" t="n">
-        <v>7014904</v>
+        <v>7015241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,6 +3089,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137744</v>
+        <v>129137750</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548511</v>
+        <v>548514</v>
       </c>
       <c r="R26" t="n">
-        <v>7015241</v>
+        <v>7015227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,7 +3327,7 @@
         <v>129125929</v>
       </c>
       <c r="B28" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137789</v>
+        <v>129137849</v>
       </c>
       <c r="B34" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548461</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015210</v>
+        <v>7015247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137896</v>
+        <v>129137789</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548260</v>
+        <v>548461</v>
       </c>
       <c r="R35" t="n">
-        <v>7014898</v>
+        <v>7015210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4115,10 +4115,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129126213</v>
+        <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,21 +4143,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548265</v>
+        <v>548260</v>
       </c>
       <c r="R36" t="n">
-        <v>7014876</v>
+        <v>7014898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,6 +4186,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4216,45 +4217,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137849</v>
+        <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548629</v>
+        <v>548265</v>
       </c>
       <c r="R37" t="n">
-        <v>7015247</v>
+        <v>7014876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4287,11 +4292,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4318,32 +4318,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137772</v>
+        <v>129137774</v>
       </c>
       <c r="B38" t="n">
-        <v>80174</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548364</v>
+        <v>548482</v>
       </c>
       <c r="R38" t="n">
-        <v>7015065</v>
+        <v>7015213</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4415,32 +4415,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137774</v>
+        <v>129137772</v>
       </c>
       <c r="B39" t="n">
-        <v>80146</v>
+        <v>80174</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548482</v>
+        <v>548364</v>
       </c>
       <c r="R39" t="n">
-        <v>7015213</v>
+        <v>7015065</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4512,32 +4512,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137812</v>
+        <v>129137895</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548395</v>
+        <v>548277</v>
       </c>
       <c r="R40" t="n">
-        <v>7015086</v>
+        <v>7015126</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4583,6 +4583,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4609,10 +4614,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137846</v>
+        <v>129137812</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4620,21 +4625,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548317</v>
+        <v>548395</v>
       </c>
       <c r="R41" t="n">
-        <v>7014833</v>
+        <v>7015086</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4680,11 +4685,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4711,32 +4711,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137895</v>
+        <v>129137846</v>
       </c>
       <c r="B42" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548277</v>
+        <v>548317</v>
       </c>
       <c r="R42" t="n">
-        <v>7015126</v>
+        <v>7014833</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4813,32 +4813,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137843</v>
+        <v>129137792</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>105770</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548488</v>
+        <v>548368</v>
       </c>
       <c r="R43" t="n">
-        <v>7015296</v>
+        <v>7014860</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4884,6 +4884,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4910,32 +4915,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137909</v>
+        <v>129137766</v>
       </c>
       <c r="B44" t="n">
-        <v>82873</v>
+        <v>97583</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4950,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548610</v>
+        <v>548366</v>
       </c>
       <c r="R44" t="n">
-        <v>7015229</v>
+        <v>7014942</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4981,6 +4986,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5007,32 +5017,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137766</v>
+        <v>129137822</v>
       </c>
       <c r="B45" t="n">
-        <v>97582</v>
+        <v>57648</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>100001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5042,10 +5052,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548366</v>
+        <v>548346</v>
       </c>
       <c r="R45" t="n">
-        <v>7014942</v>
+        <v>7015026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5078,11 +5088,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5109,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137803</v>
+        <v>129137843</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5120,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5144,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548467</v>
+        <v>548488</v>
       </c>
       <c r="R46" t="n">
-        <v>7014995</v>
+        <v>7015296</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5206,7 +5211,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137814</v>
+        <v>129137803</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5241,10 +5246,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548376</v>
+        <v>548467</v>
       </c>
       <c r="R47" t="n">
-        <v>7015053</v>
+        <v>7014995</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5303,10 +5308,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137822</v>
+        <v>129137814</v>
       </c>
       <c r="B48" t="n">
-        <v>57648</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5314,21 +5319,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5338,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548346</v>
+        <v>548376</v>
       </c>
       <c r="R48" t="n">
-        <v>7015026</v>
+        <v>7015053</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5400,32 +5405,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137786</v>
+        <v>129137909</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>82873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5435,10 +5440,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548402</v>
+        <v>548610</v>
       </c>
       <c r="R49" t="n">
-        <v>7015096</v>
+        <v>7015229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5471,11 +5476,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5502,32 +5502,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137792</v>
+        <v>129137783</v>
       </c>
       <c r="B50" t="n">
-        <v>105769</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548368</v>
+        <v>548595</v>
       </c>
       <c r="R50" t="n">
-        <v>7014860</v>
+        <v>7015162</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137783</v>
+        <v>129137891</v>
       </c>
       <c r="B51" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548595</v>
+        <v>548627</v>
       </c>
       <c r="R51" t="n">
-        <v>7015162</v>
+        <v>7015253</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5706,10 +5706,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137891</v>
+        <v>129137786</v>
       </c>
       <c r="B52" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548627</v>
+        <v>548402</v>
       </c>
       <c r="R52" t="n">
-        <v>7015253</v>
+        <v>7015096</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137739</v>
+        <v>129137860</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548460</v>
+        <v>548481</v>
       </c>
       <c r="R53" t="n">
-        <v>7014976</v>
+        <v>7015172</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5910,32 +5910,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137877</v>
+        <v>129137905</v>
       </c>
       <c r="B54" t="n">
-        <v>80174</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548334</v>
+        <v>548618</v>
       </c>
       <c r="R54" t="n">
-        <v>7015001</v>
+        <v>7015116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6007,32 +6007,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137882</v>
+        <v>129137877</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>80174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548510</v>
+        <v>548334</v>
       </c>
       <c r="R55" t="n">
-        <v>7015191</v>
+        <v>7015001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137905</v>
+        <v>129126001</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548618</v>
+        <v>548299</v>
       </c>
       <c r="R56" t="n">
-        <v>7015116</v>
+        <v>7014876</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6201,10 +6201,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129126001</v>
+        <v>129137882</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6212,21 +6212,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548299</v>
+        <v>548510</v>
       </c>
       <c r="R57" t="n">
-        <v>7014876</v>
+        <v>7015191</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6298,7 +6298,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137746</v>
+        <v>129137739</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548355</v>
+        <v>548460</v>
       </c>
       <c r="R58" t="n">
-        <v>7014874</v>
+        <v>7014976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,10 +6502,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137860</v>
+        <v>129137746</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6513,21 +6513,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548481</v>
+        <v>548355</v>
       </c>
       <c r="R60" t="n">
-        <v>7015172</v>
+        <v>7014874</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6803,32 +6803,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137782</v>
+        <v>129137769</v>
       </c>
       <c r="B63" t="n">
-        <v>98705</v>
+        <v>80174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548485</v>
+        <v>548487</v>
       </c>
       <c r="R63" t="n">
-        <v>7014854</v>
+        <v>7015073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,11 +6874,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6905,7 +6900,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B64" t="n">
         <v>80174</v>
@@ -6940,10 +6935,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R64" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7002,32 +6997,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137875</v>
+        <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>80174</v>
+        <v>98706</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7037,10 +7032,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548581</v>
+        <v>548485</v>
       </c>
       <c r="R65" t="n">
-        <v>7015017</v>
+        <v>7014854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,6 +7068,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7099,32 +7099,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137890</v>
+        <v>129137811</v>
       </c>
       <c r="B66" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548594</v>
+        <v>548458</v>
       </c>
       <c r="R66" t="n">
-        <v>7015211</v>
+        <v>7015205</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7170,11 +7170,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7201,32 +7196,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137791</v>
+        <v>129137857</v>
       </c>
       <c r="B67" t="n">
-        <v>105769</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7236,10 +7231,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548452</v>
+        <v>548502</v>
       </c>
       <c r="R67" t="n">
-        <v>7014769</v>
+        <v>7015176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7272,6 +7267,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7298,32 +7298,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137811</v>
+        <v>129137858</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7333,10 +7333,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548458</v>
+        <v>548400</v>
       </c>
       <c r="R68" t="n">
-        <v>7015205</v>
+        <v>7015152</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7369,6 +7369,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7395,10 +7400,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137858</v>
+        <v>129137762</v>
       </c>
       <c r="B69" t="n">
-        <v>56917</v>
+        <v>97583</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7406,21 +7411,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7430,10 +7435,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548400</v>
+        <v>548603</v>
       </c>
       <c r="R69" t="n">
-        <v>7015152</v>
+        <v>7014709</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7466,11 +7471,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7497,32 +7497,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137857</v>
+        <v>129137890</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548502</v>
+        <v>548594</v>
       </c>
       <c r="R70" t="n">
-        <v>7015176</v>
+        <v>7015211</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7599,10 +7599,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137762</v>
+        <v>129137791</v>
       </c>
       <c r="B71" t="n">
-        <v>97582</v>
+        <v>105770</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7610,21 +7610,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548603</v>
+        <v>548452</v>
       </c>
       <c r="R71" t="n">
-        <v>7014709</v>
+        <v>7014769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7696,10 +7696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137773</v>
+        <v>129137902</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,23 +7707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7731,10 +7727,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548717</v>
+        <v>548480</v>
       </c>
       <c r="R72" t="n">
-        <v>7014991</v>
+        <v>7015285</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7793,32 +7789,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137886</v>
+        <v>129137780</v>
       </c>
       <c r="B73" t="n">
-        <v>80182</v>
+        <v>98706</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7828,10 +7824,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548498</v>
+        <v>548594</v>
       </c>
       <c r="R73" t="n">
-        <v>7015173</v>
+        <v>7015114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7864,6 +7860,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7890,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137748</v>
+        <v>129137773</v>
       </c>
       <c r="B74" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7901,21 +7902,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7925,10 +7926,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548710</v>
+        <v>548717</v>
       </c>
       <c r="R74" t="n">
-        <v>7014904</v>
+        <v>7014991</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7961,11 +7962,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7992,32 +7988,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137780</v>
+        <v>129137886</v>
       </c>
       <c r="B75" t="n">
-        <v>98705</v>
+        <v>80182</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8027,10 +8023,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548594</v>
+        <v>548498</v>
       </c>
       <c r="R75" t="n">
-        <v>7015114</v>
+        <v>7015173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8063,11 +8059,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8094,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137902</v>
+        <v>129137850</v>
       </c>
       <c r="B76" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8105,19 +8096,23 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8125,10 +8120,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548480</v>
+        <v>548629</v>
       </c>
       <c r="R76" t="n">
-        <v>7015285</v>
+        <v>7015262</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8161,6 +8156,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8187,10 +8187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137850</v>
+        <v>129137748</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8198,21 +8198,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548629</v>
+        <v>548710</v>
       </c>
       <c r="R77" t="n">
-        <v>7015262</v>
+        <v>7014904</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8483,32 +8483,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137759</v>
+        <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>97576</v>
+        <v>98706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548487</v>
+        <v>548620</v>
       </c>
       <c r="R80" t="n">
-        <v>7014855</v>
+        <v>7014685</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8554,6 +8554,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8580,32 +8585,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137779</v>
+        <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>98705</v>
+        <v>97577</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8615,10 +8620,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548620</v>
+        <v>548487</v>
       </c>
       <c r="R81" t="n">
-        <v>7014685</v>
+        <v>7014855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8651,11 +8656,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8682,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137805</v>
+        <v>129137889</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548613</v>
+        <v>548440</v>
       </c>
       <c r="R82" t="n">
-        <v>7015186</v>
+        <v>7014752</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,6 +8753,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8779,32 +8784,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137796</v>
+        <v>129137781</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8814,10 +8819,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548559</v>
+        <v>548433</v>
       </c>
       <c r="R83" t="n">
-        <v>7014776</v>
+        <v>7014771</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,6 +8855,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,32 +8886,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137816</v>
+        <v>129137900</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>105770</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8921,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548400</v>
+        <v>548451</v>
       </c>
       <c r="R84" t="n">
-        <v>7014970</v>
+        <v>7014746</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8973,32 +8983,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137745</v>
+        <v>129137871</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>97583</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9008,10 +9018,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548373</v>
+        <v>548457</v>
       </c>
       <c r="R85" t="n">
-        <v>7014966</v>
+        <v>7014764</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9044,11 +9054,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9075,10 +9080,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137871</v>
+        <v>129137872</v>
       </c>
       <c r="B86" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9110,10 +9115,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548457</v>
+        <v>548477</v>
       </c>
       <c r="R86" t="n">
-        <v>7014764</v>
+        <v>7015144</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9172,32 +9177,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137872</v>
+        <v>129137805</v>
       </c>
       <c r="B87" t="n">
-        <v>97582</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9207,10 +9212,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548477</v>
+        <v>548613</v>
       </c>
       <c r="R87" t="n">
-        <v>7015144</v>
+        <v>7015186</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9269,32 +9274,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137781</v>
+        <v>129137796</v>
       </c>
       <c r="B88" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9304,10 +9309,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548433</v>
+        <v>548559</v>
       </c>
       <c r="R88" t="n">
-        <v>7014771</v>
+        <v>7014776</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9340,11 +9345,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9371,32 +9371,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137900</v>
+        <v>129137816</v>
       </c>
       <c r="B89" t="n">
-        <v>105769</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9406,10 +9406,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548451</v>
+        <v>548400</v>
       </c>
       <c r="R89" t="n">
-        <v>7014746</v>
+        <v>7014970</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9468,32 +9468,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137889</v>
+        <v>129137745</v>
       </c>
       <c r="B90" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9503,10 +9503,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548440</v>
+        <v>548373</v>
       </c>
       <c r="R90" t="n">
-        <v>7014752</v>
+        <v>7014966</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137878</v>
+        <v>129137901</v>
       </c>
       <c r="B92" t="n">
-        <v>80146</v>
+        <v>105770</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548705</v>
+        <v>548281</v>
       </c>
       <c r="R92" t="n">
-        <v>7014750</v>
+        <v>7015128</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9769,10 +9769,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137764</v>
+        <v>129137790</v>
       </c>
       <c r="B93" t="n">
-        <v>97582</v>
+        <v>105770</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9780,21 +9780,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548590</v>
+        <v>548558</v>
       </c>
       <c r="R93" t="n">
-        <v>7015157</v>
+        <v>7014771</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9866,10 +9866,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137790</v>
+        <v>129137764</v>
       </c>
       <c r="B94" t="n">
-        <v>105769</v>
+        <v>97583</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9877,21 +9877,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9901,10 +9901,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548558</v>
+        <v>548590</v>
       </c>
       <c r="R94" t="n">
-        <v>7014771</v>
+        <v>7015157</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9963,32 +9963,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137901</v>
+        <v>129137878</v>
       </c>
       <c r="B95" t="n">
-        <v>105769</v>
+        <v>80146</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9998,10 +9998,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548281</v>
+        <v>548705</v>
       </c>
       <c r="R95" t="n">
-        <v>7015128</v>
+        <v>7014750</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10060,27 +10060,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137911</v>
+        <v>129137908</v>
       </c>
       <c r="B96" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548512</v>
+        <v>548306</v>
       </c>
       <c r="R96" t="n">
-        <v>7015192</v>
+        <v>7015082</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10157,27 +10157,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10192,10 +10192,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R97" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10254,32 +10254,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137788</v>
+        <v>129137912</v>
       </c>
       <c r="B98" t="n">
-        <v>98705</v>
+        <v>96825</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548605</v>
+        <v>548604</v>
       </c>
       <c r="R98" t="n">
-        <v>7014687</v>
+        <v>7015234</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10325,11 +10325,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10356,32 +10351,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137912</v>
+        <v>129137863</v>
       </c>
       <c r="B99" t="n">
-        <v>96824</v>
+        <v>80147</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2869</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10391,10 +10386,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548604</v>
+        <v>548702</v>
       </c>
       <c r="R99" t="n">
-        <v>7015234</v>
+        <v>7014752</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10453,32 +10448,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137863</v>
+        <v>129137874</v>
       </c>
       <c r="B100" t="n">
-        <v>80147</v>
+        <v>97583</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10488,10 +10483,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548702</v>
+        <v>548348</v>
       </c>
       <c r="R100" t="n">
-        <v>7014752</v>
+        <v>7014988</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10749,32 +10744,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137874</v>
+        <v>129137788</v>
       </c>
       <c r="B103" t="n">
-        <v>97582</v>
+        <v>98706</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10784,10 +10779,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548348</v>
+        <v>548605</v>
       </c>
       <c r="R103" t="n">
-        <v>7014988</v>
+        <v>7014687</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10820,6 +10815,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10846,10 +10846,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137883</v>
+        <v>129137840</v>
       </c>
       <c r="B104" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548499</v>
+        <v>548660</v>
       </c>
       <c r="R104" t="n">
-        <v>7015176</v>
+        <v>7014820</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11040,10 +11040,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137840</v>
+        <v>129137883</v>
       </c>
       <c r="B106" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11051,21 +11051,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11075,10 +11075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548660</v>
+        <v>548499</v>
       </c>
       <c r="R106" t="n">
-        <v>7014820</v>
+        <v>7015176</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11140,7 +11140,7 @@
         <v>129137758</v>
       </c>
       <c r="B107" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,32 +11234,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137768</v>
+        <v>129137847</v>
       </c>
       <c r="B108" t="n">
-        <v>80174</v>
+        <v>57727</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11269,10 +11269,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548723</v>
+        <v>548490</v>
       </c>
       <c r="R108" t="n">
-        <v>7014940</v>
+        <v>7014739</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11305,6 +11305,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11331,32 +11336,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137844</v>
+        <v>129137768</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>80174</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11366,10 +11371,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548672</v>
+        <v>548723</v>
       </c>
       <c r="R109" t="n">
-        <v>7014893</v>
+        <v>7014940</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11402,11 +11407,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11433,7 +11433,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137847</v>
+        <v>129137844</v>
       </c>
       <c r="B110" t="n">
         <v>57727</v>
@@ -11468,10 +11468,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548490</v>
+        <v>548672</v>
       </c>
       <c r="R110" t="n">
-        <v>7014739</v>
+        <v>7014893</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11538,7 +11538,7 @@
         <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>129137817</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>129137797</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>129137815</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>129137787</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137795</v>
+        <v>129137794</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,23 +1854,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1878,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548538</v>
+        <v>548459</v>
       </c>
       <c r="R13" t="n">
-        <v>7014770</v>
+        <v>7015186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,11 +1910,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R14" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,6 +2007,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2038,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,19 +2049,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R15" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2240,7 @@
         <v>129137820</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>129137801</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>129137802</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>129137906</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137771</v>
+        <v>129137819</v>
       </c>
       <c r="B22" t="n">
-        <v>80174</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548360</v>
+        <v>548318</v>
       </c>
       <c r="R22" t="n">
-        <v>7014942</v>
+        <v>7014904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137819</v>
+        <v>129137744</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548318</v>
+        <v>548511</v>
       </c>
       <c r="R23" t="n">
-        <v>7014904</v>
+        <v>7015241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2895,6 +2895,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2921,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137862</v>
+        <v>129137771</v>
       </c>
       <c r="B24" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548497</v>
+        <v>548360</v>
       </c>
       <c r="R24" t="n">
-        <v>7015181</v>
+        <v>7014942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,32 +3023,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137744</v>
+        <v>129137862</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3053,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548511</v>
+        <v>548497</v>
       </c>
       <c r="R25" t="n">
-        <v>7015241</v>
+        <v>7015181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3089,11 +3094,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137749</v>
+        <v>129137810</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548618</v>
+        <v>548538</v>
       </c>
       <c r="R27" t="n">
-        <v>7015211</v>
+        <v>7015259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3293,11 +3293,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3324,32 +3319,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129125929</v>
+        <v>129137806</v>
       </c>
       <c r="B28" t="n">
-        <v>97577</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548372</v>
+        <v>548632</v>
       </c>
       <c r="R28" t="n">
-        <v>7014829</v>
+        <v>7015246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,32 +3416,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137876</v>
+        <v>129137749</v>
       </c>
       <c r="B29" t="n">
-        <v>80174</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3456,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548475</v>
+        <v>548618</v>
       </c>
       <c r="R29" t="n">
-        <v>7015265</v>
+        <v>7015211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,6 +3487,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,32 +3518,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137810</v>
+        <v>129125929</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548538</v>
+        <v>548372</v>
       </c>
       <c r="R30" t="n">
-        <v>7015259</v>
+        <v>7014829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137806</v>
+        <v>129137876</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>80176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548632</v>
+        <v>548475</v>
       </c>
       <c r="R31" t="n">
-        <v>7015246</v>
+        <v>7015265</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137800</v>
+        <v>129137849</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548708</v>
+        <v>548629</v>
       </c>
       <c r="R32" t="n">
-        <v>7014937</v>
+        <v>7015247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,32 +3814,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137821</v>
+        <v>129137789</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548369</v>
+        <v>548461</v>
       </c>
       <c r="R33" t="n">
-        <v>7014853</v>
+        <v>7015210</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,6 +3885,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3911,32 +3916,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137849</v>
+        <v>129137896</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548260</v>
       </c>
       <c r="R34" t="n">
-        <v>7015247</v>
+        <v>7014898</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,7 +3991,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4013,10 +4018,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137789</v>
+        <v>129126213</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4041,17 +4046,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548461</v>
+        <v>548265</v>
       </c>
       <c r="R35" t="n">
-        <v>7015210</v>
+        <v>7014876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4084,11 +4093,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4115,32 +4119,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137896</v>
+        <v>129137800</v>
       </c>
       <c r="B36" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4150,10 +4154,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548260</v>
+        <v>548708</v>
       </c>
       <c r="R36" t="n">
-        <v>7014898</v>
+        <v>7014937</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,7 +4194,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4217,49 +4221,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129126213</v>
+        <v>129137821</v>
       </c>
       <c r="B37" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548265</v>
+        <v>548369</v>
       </c>
       <c r="R37" t="n">
-        <v>7014876</v>
+        <v>7014853</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
         <v>129137774</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>129137772</v>
       </c>
       <c r="B39" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4512,32 +4512,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137895</v>
+        <v>129137846</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548277</v>
+        <v>548317</v>
       </c>
       <c r="R40" t="n">
-        <v>7015126</v>
+        <v>7014833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4617,7 +4617,7 @@
         <v>129137812</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4711,32 +4711,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137846</v>
+        <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548317</v>
+        <v>548277</v>
       </c>
       <c r="R42" t="n">
-        <v>7014833</v>
+        <v>7015126</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4813,32 +4813,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137792</v>
+        <v>129137803</v>
       </c>
       <c r="B43" t="n">
-        <v>105770</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548368</v>
+        <v>548467</v>
       </c>
       <c r="R43" t="n">
-        <v>7014860</v>
+        <v>7014995</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4884,11 +4884,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4915,32 +4910,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137766</v>
+        <v>129137814</v>
       </c>
       <c r="B44" t="n">
-        <v>97583</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4950,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548366</v>
+        <v>548376</v>
       </c>
       <c r="R44" t="n">
-        <v>7014942</v>
+        <v>7015053</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4986,11 +4981,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5017,10 +5007,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137822</v>
+        <v>129137843</v>
       </c>
       <c r="B45" t="n">
-        <v>57648</v>
+        <v>91543</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5028,21 +5018,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100001</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5052,10 +5042,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548346</v>
+        <v>548488</v>
       </c>
       <c r="R45" t="n">
-        <v>7015026</v>
+        <v>7015296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5114,10 +5104,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137843</v>
+        <v>129137909</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>82877</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5115,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5139,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548488</v>
+        <v>548610</v>
       </c>
       <c r="R46" t="n">
-        <v>7015296</v>
+        <v>7015229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5211,10 +5201,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137803</v>
+        <v>129137822</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>57648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,21 +5212,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5246,10 +5236,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548467</v>
+        <v>548346</v>
       </c>
       <c r="R47" t="n">
-        <v>7014995</v>
+        <v>7015026</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5308,32 +5298,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137814</v>
+        <v>129137891</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5343,10 +5333,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548376</v>
+        <v>548627</v>
       </c>
       <c r="R48" t="n">
-        <v>7015053</v>
+        <v>7015253</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,6 +5369,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5405,32 +5400,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137909</v>
+        <v>129137786</v>
       </c>
       <c r="B49" t="n">
-        <v>82873</v>
+        <v>98710</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5440,10 +5435,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548610</v>
+        <v>548402</v>
       </c>
       <c r="R49" t="n">
-        <v>7015229</v>
+        <v>7015096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5476,6 +5471,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5505,7 +5505,7 @@
         <v>129137783</v>
       </c>
       <c r="B50" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5604,32 +5604,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137891</v>
+        <v>129137792</v>
       </c>
       <c r="B51" t="n">
-        <v>98706</v>
+        <v>105774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548627</v>
+        <v>548368</v>
       </c>
       <c r="R51" t="n">
-        <v>7015253</v>
+        <v>7014860</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5706,32 +5706,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137786</v>
+        <v>129137766</v>
       </c>
       <c r="B52" t="n">
-        <v>98706</v>
+        <v>97587</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548402</v>
+        <v>548366</v>
       </c>
       <c r="R52" t="n">
-        <v>7015096</v>
+        <v>7014942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>15 stycken kan finnas mer I mossan</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137860</v>
+        <v>129137739</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548481</v>
+        <v>548460</v>
       </c>
       <c r="R53" t="n">
-        <v>7015172</v>
+        <v>7014976</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5910,10 +5910,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137905</v>
+        <v>129137845</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5921,21 +5921,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548618</v>
+        <v>548531</v>
       </c>
       <c r="R54" t="n">
-        <v>7015116</v>
+        <v>7014817</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5981,6 +5981,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6007,32 +6012,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137877</v>
+        <v>129137746</v>
       </c>
       <c r="B55" t="n">
-        <v>80174</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6042,10 +6047,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548334</v>
+        <v>548355</v>
       </c>
       <c r="R55" t="n">
-        <v>7015001</v>
+        <v>7014874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,6 +6083,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6104,10 +6114,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129126001</v>
+        <v>129137860</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6115,21 +6125,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6139,10 +6149,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548299</v>
+        <v>548481</v>
       </c>
       <c r="R56" t="n">
-        <v>7014876</v>
+        <v>7015172</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,6 +6185,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6201,10 +6216,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137882</v>
+        <v>129137859</v>
       </c>
       <c r="B57" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6212,21 +6227,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6236,10 +6251,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548510</v>
+        <v>548434</v>
       </c>
       <c r="R57" t="n">
-        <v>7015191</v>
+        <v>7014792</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,6 +6287,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6298,32 +6318,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137739</v>
+        <v>129137877</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80176</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6333,10 +6353,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548460</v>
+        <v>548334</v>
       </c>
       <c r="R58" t="n">
-        <v>7014976</v>
+        <v>7015001</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6369,11 +6389,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6400,10 +6415,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137845</v>
+        <v>129137882</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6411,21 +6426,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6435,10 +6450,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548531</v>
+        <v>548510</v>
       </c>
       <c r="R59" t="n">
-        <v>7014817</v>
+        <v>7015191</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6471,11 +6486,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6502,10 +6512,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137746</v>
+        <v>129137905</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6513,21 +6523,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6537,10 +6547,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548355</v>
+        <v>548618</v>
       </c>
       <c r="R60" t="n">
-        <v>7014874</v>
+        <v>7015116</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6573,11 +6583,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6604,10 +6609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137859</v>
+        <v>129126001</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,21 +6620,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6639,10 +6644,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548434</v>
+        <v>548299</v>
       </c>
       <c r="R61" t="n">
-        <v>7014792</v>
+        <v>7014876</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6675,11 +6680,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6706,10 +6706,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B62" t="n">
-        <v>92822</v>
+        <v>80176</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R62" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6803,10 +6803,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B63" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R63" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6900,32 +6900,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137875</v>
+        <v>129137782</v>
       </c>
       <c r="B64" t="n">
-        <v>80174</v>
+        <v>98710</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548581</v>
+        <v>548485</v>
       </c>
       <c r="R64" t="n">
-        <v>7015017</v>
+        <v>7014854</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,6 +6971,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6997,32 +7002,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137782</v>
+        <v>129137910</v>
       </c>
       <c r="B65" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7032,10 +7037,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548485</v>
+        <v>548510</v>
       </c>
       <c r="R65" t="n">
-        <v>7014854</v>
+        <v>7014986</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,11 +7073,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7099,32 +7099,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137811</v>
+        <v>129137791</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>105774</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548458</v>
+        <v>548452</v>
       </c>
       <c r="R66" t="n">
-        <v>7015205</v>
+        <v>7014769</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7196,32 +7196,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137857</v>
+        <v>129137762</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>97587</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548502</v>
+        <v>548603</v>
       </c>
       <c r="R67" t="n">
-        <v>7015176</v>
+        <v>7014709</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7267,11 +7267,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7298,32 +7293,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137858</v>
+        <v>129137890</v>
       </c>
       <c r="B68" t="n">
-        <v>56917</v>
+        <v>98710</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7333,10 +7328,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548400</v>
+        <v>548594</v>
       </c>
       <c r="R68" t="n">
-        <v>7015152</v>
+        <v>7015211</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,7 +7368,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>1 ex, förbiflygande</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7400,32 +7395,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137762</v>
+        <v>129137811</v>
       </c>
       <c r="B69" t="n">
-        <v>97583</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7435,10 +7430,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548603</v>
+        <v>548458</v>
       </c>
       <c r="R69" t="n">
-        <v>7014709</v>
+        <v>7015205</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7497,32 +7492,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137890</v>
+        <v>129137857</v>
       </c>
       <c r="B70" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7532,10 +7527,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548594</v>
+        <v>548502</v>
       </c>
       <c r="R70" t="n">
-        <v>7015211</v>
+        <v>7015176</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7572,7 +7567,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7599,10 +7594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137791</v>
+        <v>129137858</v>
       </c>
       <c r="B71" t="n">
-        <v>105770</v>
+        <v>56917</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7610,21 +7605,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7629,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548452</v>
+        <v>548400</v>
       </c>
       <c r="R71" t="n">
-        <v>7014769</v>
+        <v>7015152</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7670,6 +7665,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137902</v>
+        <v>129137748</v>
       </c>
       <c r="B72" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,19 +7707,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7727,10 +7731,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548480</v>
+        <v>548710</v>
       </c>
       <c r="R72" t="n">
-        <v>7015285</v>
+        <v>7014904</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7763,6 +7767,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7789,34 +7798,30 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137780</v>
+        <v>129137902</v>
       </c>
       <c r="B73" t="n">
-        <v>98706</v>
+        <v>91563</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7824,10 +7829,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548594</v>
+        <v>548480</v>
       </c>
       <c r="R73" t="n">
-        <v>7015114</v>
+        <v>7015285</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7860,11 +7865,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7894,7 +7894,7 @@
         <v>129137773</v>
       </c>
       <c r="B74" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>129137886</v>
       </c>
       <c r="B75" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8187,32 +8187,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137748</v>
+        <v>129137780</v>
       </c>
       <c r="B77" t="n">
-        <v>57887</v>
+        <v>98710</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548710</v>
+        <v>548594</v>
       </c>
       <c r="R77" t="n">
-        <v>7014904</v>
+        <v>7015114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8289,32 +8289,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137813</v>
+        <v>129137779</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548374</v>
+        <v>548620</v>
       </c>
       <c r="R78" t="n">
-        <v>7015064</v>
+        <v>7014685</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8360,6 +8360,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8386,10 +8391,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137818</v>
+        <v>129137813</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8421,10 +8426,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548329</v>
+        <v>548374</v>
       </c>
       <c r="R79" t="n">
-        <v>7014932</v>
+        <v>7015064</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8483,32 +8488,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B80" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R80" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8588,7 +8588,7 @@
         <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8682,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137889</v>
+        <v>129137805</v>
       </c>
       <c r="B82" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548440</v>
+        <v>548613</v>
       </c>
       <c r="R82" t="n">
-        <v>7014752</v>
+        <v>7015186</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,11 +8753,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8784,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137781</v>
+        <v>129137796</v>
       </c>
       <c r="B83" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548433</v>
+        <v>548559</v>
       </c>
       <c r="R83" t="n">
-        <v>7014771</v>
+        <v>7014776</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8855,11 +8850,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8886,32 +8876,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137900</v>
+        <v>129137816</v>
       </c>
       <c r="B84" t="n">
-        <v>105770</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8921,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548451</v>
+        <v>548400</v>
       </c>
       <c r="R84" t="n">
-        <v>7014746</v>
+        <v>7014970</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8983,32 +8973,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137871</v>
+        <v>129137745</v>
       </c>
       <c r="B85" t="n">
-        <v>97583</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9018,10 +9008,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548457</v>
+        <v>548373</v>
       </c>
       <c r="R85" t="n">
-        <v>7014764</v>
+        <v>7014966</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9054,6 +9044,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9080,32 +9075,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137872</v>
+        <v>129137889</v>
       </c>
       <c r="B86" t="n">
-        <v>97583</v>
+        <v>98710</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9115,10 +9110,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548477</v>
+        <v>548440</v>
       </c>
       <c r="R86" t="n">
-        <v>7015144</v>
+        <v>7014752</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9151,6 +9146,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,32 +9177,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137805</v>
+        <v>129137781</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9212,10 +9212,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548613</v>
+        <v>548433</v>
       </c>
       <c r="R87" t="n">
-        <v>7015186</v>
+        <v>7014771</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9248,6 +9248,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9274,32 +9279,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137796</v>
+        <v>129137900</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>105774</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9309,10 +9314,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548559</v>
+        <v>548451</v>
       </c>
       <c r="R88" t="n">
-        <v>7014776</v>
+        <v>7014746</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9371,32 +9376,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137816</v>
+        <v>129137871</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>97587</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9406,10 +9411,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548400</v>
+        <v>548457</v>
       </c>
       <c r="R89" t="n">
-        <v>7014970</v>
+        <v>7014764</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9468,32 +9473,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137745</v>
+        <v>129137872</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>97587</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9503,10 +9508,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548373</v>
+        <v>548477</v>
       </c>
       <c r="R90" t="n">
-        <v>7014966</v>
+        <v>7015144</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9539,11 +9544,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9570,32 +9570,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137778</v>
+        <v>129137878</v>
       </c>
       <c r="B91" t="n">
-        <v>57831</v>
+        <v>80148</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548706</v>
+        <v>548705</v>
       </c>
       <c r="R91" t="n">
-        <v>7014864</v>
+        <v>7014750</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9641,11 +9641,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9672,10 +9667,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137901</v>
+        <v>129137778</v>
       </c>
       <c r="B92" t="n">
-        <v>105770</v>
+        <v>57831</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9683,21 +9678,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>103031</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9707,10 +9702,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548281</v>
+        <v>548706</v>
       </c>
       <c r="R92" t="n">
-        <v>7015128</v>
+        <v>7014864</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9743,6 +9738,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9769,10 +9769,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137790</v>
+        <v>129137901</v>
       </c>
       <c r="B93" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548558</v>
+        <v>548281</v>
       </c>
       <c r="R93" t="n">
-        <v>7014771</v>
+        <v>7015128</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9866,10 +9866,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137764</v>
+        <v>129137790</v>
       </c>
       <c r="B94" t="n">
-        <v>97583</v>
+        <v>105774</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9877,21 +9877,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9901,10 +9901,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548590</v>
+        <v>548558</v>
       </c>
       <c r="R94" t="n">
-        <v>7015157</v>
+        <v>7014771</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9963,32 +9963,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137878</v>
+        <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>80146</v>
+        <v>97587</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9998,10 +9998,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548705</v>
+        <v>548590</v>
       </c>
       <c r="R95" t="n">
-        <v>7014750</v>
+        <v>7015157</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10060,27 +10060,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>80183</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R96" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10157,27 +10157,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137911</v>
+        <v>129137908</v>
       </c>
       <c r="B97" t="n">
-        <v>80181</v>
+        <v>79043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10192,10 +10192,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548512</v>
+        <v>548306</v>
       </c>
       <c r="R97" t="n">
-        <v>7015192</v>
+        <v>7015082</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10254,32 +10254,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137912</v>
+        <v>129137788</v>
       </c>
       <c r="B98" t="n">
-        <v>96825</v>
+        <v>98710</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548604</v>
+        <v>548605</v>
       </c>
       <c r="R98" t="n">
-        <v>7015234</v>
+        <v>7014687</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10325,6 +10325,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10351,32 +10356,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137863</v>
+        <v>129137874</v>
       </c>
       <c r="B99" t="n">
-        <v>80147</v>
+        <v>97587</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10386,10 +10391,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548702</v>
+        <v>548348</v>
       </c>
       <c r="R99" t="n">
-        <v>7014752</v>
+        <v>7014988</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10448,32 +10453,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137874</v>
+        <v>129137863</v>
       </c>
       <c r="B100" t="n">
-        <v>97583</v>
+        <v>80149</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10483,10 +10488,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548348</v>
+        <v>548702</v>
       </c>
       <c r="R100" t="n">
-        <v>7014988</v>
+        <v>7014752</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10545,32 +10550,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137903</v>
+        <v>129137912</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>96829</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10580,10 +10585,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548633</v>
+        <v>548604</v>
       </c>
       <c r="R101" t="n">
-        <v>7015045</v>
+        <v>7015234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10642,10 +10647,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137848</v>
+        <v>129137903</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10653,21 +10658,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10677,10 +10682,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548598</v>
+        <v>548633</v>
       </c>
       <c r="R102" t="n">
-        <v>7015227</v>
+        <v>7015045</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10713,11 +10718,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10744,32 +10744,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137788</v>
+        <v>129137848</v>
       </c>
       <c r="B103" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548605</v>
+        <v>548598</v>
       </c>
       <c r="R103" t="n">
-        <v>7014687</v>
+        <v>7015227</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10846,32 +10846,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137840</v>
+        <v>129137758</v>
       </c>
       <c r="B104" t="n">
-        <v>91540</v>
+        <v>97581</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548660</v>
+        <v>548629</v>
       </c>
       <c r="R104" t="n">
-        <v>7014820</v>
+        <v>7014777</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10943,10 +10943,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137753</v>
+        <v>129137840</v>
       </c>
       <c r="B105" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548681</v>
+        <v>548660</v>
       </c>
       <c r="R105" t="n">
-        <v>7015193</v>
+        <v>7014820</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11040,10 +11040,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137883</v>
+        <v>129137753</v>
       </c>
       <c r="B106" t="n">
-        <v>80146</v>
+        <v>91841</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11051,21 +11051,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11075,10 +11075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548499</v>
+        <v>548681</v>
       </c>
       <c r="R106" t="n">
-        <v>7015176</v>
+        <v>7015193</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11137,32 +11137,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137758</v>
+        <v>129137883</v>
       </c>
       <c r="B107" t="n">
-        <v>97577</v>
+        <v>80148</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548629</v>
+        <v>548499</v>
       </c>
       <c r="R107" t="n">
-        <v>7014777</v>
+        <v>7015176</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11234,32 +11234,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137847</v>
+        <v>129137768</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>80176</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11269,10 +11269,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548490</v>
+        <v>548723</v>
       </c>
       <c r="R108" t="n">
-        <v>7014739</v>
+        <v>7014940</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11305,11 +11305,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11336,32 +11331,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137768</v>
+        <v>129137847</v>
       </c>
       <c r="B109" t="n">
-        <v>80174</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11371,10 +11366,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548723</v>
+        <v>548490</v>
       </c>
       <c r="R109" t="n">
-        <v>7014940</v>
+        <v>7014739</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11407,6 +11402,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11538,7 +11538,7 @@
         <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -2630,32 +2630,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137906</v>
+        <v>129137771</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>80176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548693</v>
+        <v>548360</v>
       </c>
       <c r="R21" t="n">
-        <v>7014874</v>
+        <v>7014942</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137819</v>
+        <v>129137862</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>80177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548318</v>
+        <v>548497</v>
       </c>
       <c r="R22" t="n">
-        <v>7014904</v>
+        <v>7015181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137744</v>
+        <v>129137750</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548511</v>
+        <v>548514</v>
       </c>
       <c r="R23" t="n">
-        <v>7015241</v>
+        <v>7015227</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137771</v>
+        <v>129137906</v>
       </c>
       <c r="B24" t="n">
-        <v>80176</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548360</v>
+        <v>548693</v>
       </c>
       <c r="R24" t="n">
-        <v>7014942</v>
+        <v>7014874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B25" t="n">
-        <v>80177</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R25" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137750</v>
+        <v>129137744</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548514</v>
+        <v>548511</v>
       </c>
       <c r="R26" t="n">
-        <v>7015227</v>
+        <v>7015241</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4512,10 +4512,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137846</v>
+        <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548317</v>
+        <v>548395</v>
       </c>
       <c r="R40" t="n">
-        <v>7014833</v>
+        <v>7015086</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4583,11 +4583,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4614,10 +4609,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137812</v>
+        <v>129137846</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4625,21 +4620,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548395</v>
+        <v>548317</v>
       </c>
       <c r="R41" t="n">
-        <v>7015086</v>
+        <v>7014833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4685,6 +4680,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4813,32 +4813,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137803</v>
+        <v>129137891</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548467</v>
+        <v>548627</v>
       </c>
       <c r="R43" t="n">
-        <v>7014995</v>
+        <v>7015253</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4884,6 +4884,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4910,32 +4915,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137814</v>
+        <v>129137786</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4950,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548376</v>
+        <v>548402</v>
       </c>
       <c r="R44" t="n">
-        <v>7015053</v>
+        <v>7015096</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4981,6 +4986,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,10 +5211,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137822</v>
+        <v>129137803</v>
       </c>
       <c r="B47" t="n">
-        <v>57648</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5212,21 +5222,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5236,10 +5246,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548346</v>
+        <v>548467</v>
       </c>
       <c r="R47" t="n">
-        <v>7015026</v>
+        <v>7014995</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5298,32 +5308,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137891</v>
+        <v>129137814</v>
       </c>
       <c r="B48" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5333,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548627</v>
+        <v>548376</v>
       </c>
       <c r="R48" t="n">
-        <v>7015253</v>
+        <v>7015053</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5369,11 +5379,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5400,32 +5405,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137786</v>
+        <v>129137822</v>
       </c>
       <c r="B49" t="n">
-        <v>98710</v>
+        <v>57648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5435,10 +5440,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548402</v>
+        <v>548346</v>
       </c>
       <c r="R49" t="n">
-        <v>7015096</v>
+        <v>7015026</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5471,11 +5476,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6318,32 +6318,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137877</v>
+        <v>129137905</v>
       </c>
       <c r="B58" t="n">
-        <v>80176</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548334</v>
+        <v>548618</v>
       </c>
       <c r="R58" t="n">
-        <v>7015001</v>
+        <v>7015116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137882</v>
+        <v>129126001</v>
       </c>
       <c r="B59" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6426,21 +6426,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548510</v>
+        <v>548299</v>
       </c>
       <c r="R59" t="n">
-        <v>7015191</v>
+        <v>7014876</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6512,32 +6512,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137905</v>
+        <v>129137877</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>80176</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548618</v>
+        <v>548334</v>
       </c>
       <c r="R60" t="n">
-        <v>7015116</v>
+        <v>7015001</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129126001</v>
+        <v>129137882</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548299</v>
+        <v>548510</v>
       </c>
       <c r="R61" t="n">
-        <v>7014876</v>
+        <v>7015191</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137769</v>
+        <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>80176</v>
+        <v>92825</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548487</v>
+        <v>548510</v>
       </c>
       <c r="R62" t="n">
-        <v>7015073</v>
+        <v>7014986</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6803,7 +6803,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137875</v>
+        <v>129137769</v>
       </c>
       <c r="B63" t="n">
         <v>80176</v>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548581</v>
+        <v>548487</v>
       </c>
       <c r="R63" t="n">
-        <v>7015017</v>
+        <v>7015073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6900,32 +6900,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137782</v>
+        <v>129137875</v>
       </c>
       <c r="B64" t="n">
-        <v>98710</v>
+        <v>80176</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548485</v>
+        <v>548581</v>
       </c>
       <c r="R64" t="n">
-        <v>7014854</v>
+        <v>7015017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,11 +6971,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7002,32 +6997,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137910</v>
+        <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>92825</v>
+        <v>98710</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7037,10 +7032,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548510</v>
+        <v>548485</v>
       </c>
       <c r="R65" t="n">
-        <v>7014986</v>
+        <v>7014854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,6 +7068,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137748</v>
+        <v>129137902</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>91563</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,23 +7707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7731,10 +7727,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548710</v>
+        <v>548480</v>
       </c>
       <c r="R72" t="n">
-        <v>7014904</v>
+        <v>7015285</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7767,11 +7763,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7798,30 +7789,34 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137902</v>
+        <v>129137780</v>
       </c>
       <c r="B73" t="n">
-        <v>91563</v>
+        <v>98710</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7829,10 +7824,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548480</v>
+        <v>548594</v>
       </c>
       <c r="R73" t="n">
-        <v>7015285</v>
+        <v>7015114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7865,6 +7860,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8187,32 +8187,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137780</v>
+        <v>129137748</v>
       </c>
       <c r="B77" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548594</v>
+        <v>548710</v>
       </c>
       <c r="R77" t="n">
-        <v>7015114</v>
+        <v>7014904</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8682,10 +8682,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137805</v>
+        <v>129137745</v>
       </c>
       <c r="B82" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8693,21 +8693,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548613</v>
+        <v>548373</v>
       </c>
       <c r="R82" t="n">
-        <v>7015186</v>
+        <v>7014966</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,6 +8753,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8779,32 +8784,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137796</v>
+        <v>129137889</v>
       </c>
       <c r="B83" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8814,10 +8819,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548559</v>
+        <v>548440</v>
       </c>
       <c r="R83" t="n">
-        <v>7014776</v>
+        <v>7014752</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,6 +8855,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,32 +8886,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137816</v>
+        <v>129137781</v>
       </c>
       <c r="B84" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8921,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548400</v>
+        <v>548433</v>
       </c>
       <c r="R84" t="n">
-        <v>7014970</v>
+        <v>7014771</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8947,6 +8957,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8973,32 +8988,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137745</v>
+        <v>129137900</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>105774</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9008,10 +9023,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548373</v>
+        <v>548451</v>
       </c>
       <c r="R85" t="n">
-        <v>7014966</v>
+        <v>7014746</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9044,11 +9059,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9075,32 +9085,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137889</v>
+        <v>129137871</v>
       </c>
       <c r="B86" t="n">
-        <v>98710</v>
+        <v>97587</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9110,10 +9120,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548440</v>
+        <v>548457</v>
       </c>
       <c r="R86" t="n">
-        <v>7014752</v>
+        <v>7014764</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9146,11 +9156,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,32 +9182,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137781</v>
+        <v>129137872</v>
       </c>
       <c r="B87" t="n">
-        <v>98710</v>
+        <v>97587</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9212,10 +9217,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548433</v>
+        <v>548477</v>
       </c>
       <c r="R87" t="n">
-        <v>7014771</v>
+        <v>7015144</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9248,11 +9253,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9279,32 +9279,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137900</v>
+        <v>129137805</v>
       </c>
       <c r="B88" t="n">
-        <v>105774</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548451</v>
+        <v>548613</v>
       </c>
       <c r="R88" t="n">
-        <v>7014746</v>
+        <v>7015186</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9376,32 +9376,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137871</v>
+        <v>129137796</v>
       </c>
       <c r="B89" t="n">
-        <v>97587</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9411,10 +9411,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548457</v>
+        <v>548559</v>
       </c>
       <c r="R89" t="n">
-        <v>7014764</v>
+        <v>7014776</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9473,32 +9473,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137872</v>
+        <v>129137816</v>
       </c>
       <c r="B90" t="n">
-        <v>97587</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548477</v>
+        <v>548400</v>
       </c>
       <c r="R90" t="n">
-        <v>7015144</v>
+        <v>7014970</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>129137817</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>129137797</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>129137815</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137787</v>
+        <v>129137870</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>97589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548366</v>
+        <v>548358</v>
       </c>
       <c r="R11" t="n">
-        <v>7014942</v>
+        <v>7014777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137870</v>
+        <v>129137787</v>
       </c>
       <c r="B12" t="n">
-        <v>97587</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548358</v>
+        <v>548366</v>
       </c>
       <c r="R12" t="n">
-        <v>7014777</v>
+        <v>7014942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,7 +1846,7 @@
         <v>129137794</v>
       </c>
       <c r="B13" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137795</v>
+        <v>129137804</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548538</v>
+        <v>548550</v>
       </c>
       <c r="R14" t="n">
-        <v>7014770</v>
+        <v>7015142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,11 +2007,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R15" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,6 +2104,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2240,7 @@
         <v>129137820</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137801</v>
+        <v>129137802</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548686</v>
+        <v>548499</v>
       </c>
       <c r="R18" t="n">
-        <v>7014817</v>
+        <v>7014902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137802</v>
+        <v>129137801</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548499</v>
+        <v>548686</v>
       </c>
       <c r="R19" t="n">
-        <v>7014902</v>
+        <v>7014817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2536,7 @@
         <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>129137771</v>
       </c>
       <c r="B21" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>129137862</v>
       </c>
       <c r="B22" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137750</v>
+        <v>129137744</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548514</v>
+        <v>548511</v>
       </c>
       <c r="R23" t="n">
-        <v>7015227</v>
+        <v>7015241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137906</v>
+        <v>129137750</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548693</v>
+        <v>548514</v>
       </c>
       <c r="R24" t="n">
-        <v>7014874</v>
+        <v>7015227</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,6 +2997,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3023,10 +3028,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137819</v>
+        <v>129137906</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3058,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548318</v>
+        <v>548693</v>
       </c>
       <c r="R25" t="n">
-        <v>7014904</v>
+        <v>7014874</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137744</v>
+        <v>129137819</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3160,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548511</v>
+        <v>548318</v>
       </c>
       <c r="R26" t="n">
-        <v>7015241</v>
+        <v>7014904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,11 +3196,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137810</v>
+        <v>129137749</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548538</v>
+        <v>548618</v>
       </c>
       <c r="R27" t="n">
-        <v>7015259</v>
+        <v>7015211</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3293,6 +3293,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3319,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137806</v>
+        <v>129137810</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548632</v>
+        <v>548538</v>
       </c>
       <c r="R28" t="n">
-        <v>7015246</v>
+        <v>7015259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,10 +3421,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137749</v>
+        <v>129137806</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3432,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548618</v>
+        <v>548632</v>
       </c>
       <c r="R29" t="n">
-        <v>7015211</v>
+        <v>7015246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,11 +3492,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129125929</v>
+        <v>129137876</v>
       </c>
       <c r="B30" t="n">
-        <v>97581</v>
+        <v>80177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548372</v>
+        <v>548475</v>
       </c>
       <c r="R30" t="n">
-        <v>7014829</v>
+        <v>7015265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137876</v>
+        <v>129125929</v>
       </c>
       <c r="B31" t="n">
-        <v>80176</v>
+        <v>97583</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548475</v>
+        <v>548372</v>
       </c>
       <c r="R31" t="n">
-        <v>7015265</v>
+        <v>7014829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,32 +3712,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137849</v>
+        <v>129137789</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548629</v>
+        <v>548461</v>
       </c>
       <c r="R32" t="n">
-        <v>7015247</v>
+        <v>7015210</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137789</v>
+        <v>129137896</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548461</v>
+        <v>548260</v>
       </c>
       <c r="R33" t="n">
-        <v>7015210</v>
+        <v>7014898</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3916,10 +3916,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137896</v>
+        <v>129126213</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3944,17 +3944,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548260</v>
+        <v>548265</v>
       </c>
       <c r="R34" t="n">
-        <v>7014898</v>
+        <v>7014876</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3987,11 +3991,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4018,49 +4017,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129126213</v>
+        <v>129137800</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548265</v>
+        <v>548708</v>
       </c>
       <c r="R35" t="n">
-        <v>7014876</v>
+        <v>7014937</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,6 +4088,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,10 +4119,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137800</v>
+        <v>129137821</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548708</v>
+        <v>548369</v>
       </c>
       <c r="R36" t="n">
-        <v>7014937</v>
+        <v>7014853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,11 +4190,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4221,10 +4216,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137821</v>
+        <v>129137849</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4232,21 +4227,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548369</v>
+        <v>548629</v>
       </c>
       <c r="R37" t="n">
-        <v>7014853</v>
+        <v>7015247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4292,6 +4287,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4321,7 +4321,7 @@
         <v>129137774</v>
       </c>
       <c r="B38" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>129137772</v>
       </c>
       <c r="B39" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137891</v>
+        <v>129137792</v>
       </c>
       <c r="B43" t="n">
-        <v>98710</v>
+        <v>105776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548627</v>
+        <v>548368</v>
       </c>
       <c r="R43" t="n">
-        <v>7015253</v>
+        <v>7014860</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4915,32 +4915,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137786</v>
+        <v>129137843</v>
       </c>
       <c r="B44" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548402</v>
+        <v>548488</v>
       </c>
       <c r="R44" t="n">
-        <v>7015096</v>
+        <v>7015296</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4986,11 +4986,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5017,10 +5012,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137843</v>
+        <v>129137909</v>
       </c>
       <c r="B45" t="n">
-        <v>91543</v>
+        <v>82878</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5028,21 +5023,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5052,10 +5047,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548488</v>
+        <v>548610</v>
       </c>
       <c r="R45" t="n">
-        <v>7015296</v>
+        <v>7015229</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5114,10 +5109,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137909</v>
+        <v>129137822</v>
       </c>
       <c r="B46" t="n">
-        <v>82877</v>
+        <v>57648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5120,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5144,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548610</v>
+        <v>548346</v>
       </c>
       <c r="R46" t="n">
-        <v>7015229</v>
+        <v>7015026</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5211,32 +5206,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137803</v>
+        <v>129137783</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5246,10 +5241,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548467</v>
+        <v>548595</v>
       </c>
       <c r="R47" t="n">
-        <v>7014995</v>
+        <v>7015162</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5282,6 +5277,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5308,32 +5308,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137814</v>
+        <v>129137891</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548376</v>
+        <v>548627</v>
       </c>
       <c r="R48" t="n">
-        <v>7015053</v>
+        <v>7015253</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,6 +5379,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5405,32 +5410,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137822</v>
+        <v>129137786</v>
       </c>
       <c r="B49" t="n">
-        <v>57648</v>
+        <v>98712</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5440,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548346</v>
+        <v>548402</v>
       </c>
       <c r="R49" t="n">
-        <v>7015026</v>
+        <v>7015096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5476,6 +5481,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5502,32 +5512,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137783</v>
+        <v>129137766</v>
       </c>
       <c r="B50" t="n">
-        <v>98710</v>
+        <v>97589</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5537,10 +5547,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548595</v>
+        <v>548366</v>
       </c>
       <c r="R50" t="n">
-        <v>7015162</v>
+        <v>7014942</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5577,7 +5587,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5604,32 +5614,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137792</v>
+        <v>129137814</v>
       </c>
       <c r="B51" t="n">
-        <v>105774</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5639,10 +5649,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548368</v>
+        <v>548376</v>
       </c>
       <c r="R51" t="n">
-        <v>7014860</v>
+        <v>7015053</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,11 +5685,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5706,32 +5711,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137766</v>
+        <v>129137803</v>
       </c>
       <c r="B52" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548366</v>
+        <v>548467</v>
       </c>
       <c r="R52" t="n">
-        <v>7014942</v>
+        <v>7014995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,11 +5782,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137739</v>
+        <v>129126001</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548460</v>
+        <v>548299</v>
       </c>
       <c r="R53" t="n">
-        <v>7014976</v>
+        <v>7014876</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,11 +5879,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5910,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137845</v>
+        <v>129137905</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5921,21 +5916,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548531</v>
+        <v>548618</v>
       </c>
       <c r="R54" t="n">
-        <v>7014817</v>
+        <v>7015116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5981,11 +5976,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6012,32 +6002,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137746</v>
+        <v>129137877</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6047,10 +6037,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548355</v>
+        <v>548334</v>
       </c>
       <c r="R55" t="n">
-        <v>7014874</v>
+        <v>7015001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6083,11 +6073,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6114,10 +6099,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137860</v>
+        <v>129137882</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6125,21 +6110,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6149,10 +6134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548481</v>
+        <v>548510</v>
       </c>
       <c r="R56" t="n">
-        <v>7015172</v>
+        <v>7015191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6185,11 +6170,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6216,10 +6196,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137859</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,21 +6207,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6251,10 +6231,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548434</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7014792</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6291,7 +6271,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6318,10 +6298,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137905</v>
+        <v>129137845</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6329,21 +6309,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6353,10 +6333,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548618</v>
+        <v>548531</v>
       </c>
       <c r="R58" t="n">
-        <v>7015116</v>
+        <v>7014817</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6389,6 +6369,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6415,10 +6400,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129126001</v>
+        <v>129137746</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6426,21 +6411,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6450,10 +6435,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548299</v>
+        <v>548355</v>
       </c>
       <c r="R59" t="n">
-        <v>7014876</v>
+        <v>7014874</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6486,6 +6471,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6512,32 +6502,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137877</v>
+        <v>129137860</v>
       </c>
       <c r="B60" t="n">
-        <v>80176</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6547,10 +6537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548334</v>
+        <v>548481</v>
       </c>
       <c r="R60" t="n">
-        <v>7015001</v>
+        <v>7015172</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6583,6 +6573,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6609,10 +6604,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137882</v>
+        <v>129137859</v>
       </c>
       <c r="B61" t="n">
-        <v>80148</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6620,21 +6615,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6644,10 +6639,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548510</v>
+        <v>548434</v>
       </c>
       <c r="R61" t="n">
-        <v>7015191</v>
+        <v>7014792</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,6 +6675,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6709,7 +6709,7 @@
         <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6803,32 +6803,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137769</v>
+        <v>129137782</v>
       </c>
       <c r="B63" t="n">
-        <v>80176</v>
+        <v>98712</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548487</v>
+        <v>548485</v>
       </c>
       <c r="R63" t="n">
-        <v>7015073</v>
+        <v>7014854</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,6 +6874,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6900,10 +6905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137875</v>
+        <v>129137769</v>
       </c>
       <c r="B64" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6935,10 +6940,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548581</v>
+        <v>548487</v>
       </c>
       <c r="R64" t="n">
-        <v>7015017</v>
+        <v>7015073</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6997,32 +7002,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137782</v>
+        <v>129137875</v>
       </c>
       <c r="B65" t="n">
-        <v>98710</v>
+        <v>80177</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7032,10 +7037,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548485</v>
+        <v>548581</v>
       </c>
       <c r="R65" t="n">
-        <v>7014854</v>
+        <v>7015017</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,11 +7073,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7099,32 +7099,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137791</v>
+        <v>129137857</v>
       </c>
       <c r="B66" t="n">
-        <v>105774</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548452</v>
+        <v>548502</v>
       </c>
       <c r="R66" t="n">
-        <v>7014769</v>
+        <v>7015176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7170,6 +7170,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7196,32 +7201,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137762</v>
+        <v>129137890</v>
       </c>
       <c r="B67" t="n">
-        <v>97587</v>
+        <v>98712</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7231,10 +7236,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548603</v>
+        <v>548594</v>
       </c>
       <c r="R67" t="n">
-        <v>7014709</v>
+        <v>7015211</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7267,6 +7272,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7293,32 +7303,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137890</v>
+        <v>129137791</v>
       </c>
       <c r="B68" t="n">
-        <v>98710</v>
+        <v>105776</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7328,10 +7338,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548594</v>
+        <v>548452</v>
       </c>
       <c r="R68" t="n">
-        <v>7015211</v>
+        <v>7014769</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7364,11 +7374,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7398,7 +7403,7 @@
         <v>129137811</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7492,32 +7497,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137857</v>
+        <v>129137858</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>56917</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7527,10 +7532,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548502</v>
+        <v>548400</v>
       </c>
       <c r="R70" t="n">
-        <v>7015176</v>
+        <v>7015152</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7567,7 +7572,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7594,10 +7599,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137858</v>
+        <v>129137762</v>
       </c>
       <c r="B71" t="n">
-        <v>56917</v>
+        <v>97589</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7605,21 +7610,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7629,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548400</v>
+        <v>548603</v>
       </c>
       <c r="R71" t="n">
-        <v>7015152</v>
+        <v>7014709</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7665,11 +7670,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7696,10 +7696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137902</v>
+        <v>129137850</v>
       </c>
       <c r="B72" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,19 +7707,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7727,10 +7731,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548480</v>
+        <v>548629</v>
       </c>
       <c r="R72" t="n">
-        <v>7015285</v>
+        <v>7015262</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7763,6 +7767,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7792,7 +7801,7 @@
         <v>129137780</v>
       </c>
       <c r="B73" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,10 +7900,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137773</v>
+        <v>129137902</v>
       </c>
       <c r="B74" t="n">
-        <v>80148</v>
+        <v>91565</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,23 +7911,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -7926,10 +7931,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548717</v>
+        <v>548480</v>
       </c>
       <c r="R74" t="n">
-        <v>7014991</v>
+        <v>7015285</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,32 +7993,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137886</v>
+        <v>129137773</v>
       </c>
       <c r="B75" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8023,10 +8028,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548498</v>
+        <v>548717</v>
       </c>
       <c r="R75" t="n">
-        <v>7015173</v>
+        <v>7014991</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8085,32 +8090,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137850</v>
+        <v>129137886</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8120,10 +8125,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548629</v>
+        <v>548498</v>
       </c>
       <c r="R76" t="n">
-        <v>7015262</v>
+        <v>7015173</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,11 +8161,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8289,32 +8289,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B78" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R78" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8360,11 +8360,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8394,7 +8389,7 @@
         <v>129137813</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8488,32 +8483,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137818</v>
+        <v>129137759</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>97583</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548329</v>
+        <v>548487</v>
       </c>
       <c r="R80" t="n">
-        <v>7014932</v>
+        <v>7014855</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,32 +8580,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137759</v>
+        <v>129137779</v>
       </c>
       <c r="B81" t="n">
-        <v>97581</v>
+        <v>98712</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8620,10 +8615,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548487</v>
+        <v>548620</v>
       </c>
       <c r="R81" t="n">
-        <v>7014855</v>
+        <v>7014685</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8656,6 +8651,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8682,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137745</v>
+        <v>129137889</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548373</v>
+        <v>548440</v>
       </c>
       <c r="R82" t="n">
-        <v>7014966</v>
+        <v>7014752</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8784,10 +8784,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137889</v>
+        <v>129137781</v>
       </c>
       <c r="B83" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548440</v>
+        <v>548433</v>
       </c>
       <c r="R83" t="n">
-        <v>7014752</v>
+        <v>7014771</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137781</v>
+        <v>129137871</v>
       </c>
       <c r="B84" t="n">
-        <v>98710</v>
+        <v>97589</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548433</v>
+        <v>548457</v>
       </c>
       <c r="R84" t="n">
-        <v>7014771</v>
+        <v>7014764</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8957,11 +8957,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8988,10 +8983,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137900</v>
+        <v>129137872</v>
       </c>
       <c r="B85" t="n">
-        <v>105774</v>
+        <v>97589</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8999,21 +8994,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9023,10 +9018,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548451</v>
+        <v>548477</v>
       </c>
       <c r="R85" t="n">
-        <v>7014746</v>
+        <v>7015144</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9085,32 +9080,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137871</v>
+        <v>129137796</v>
       </c>
       <c r="B86" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9120,10 +9115,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548457</v>
+        <v>548559</v>
       </c>
       <c r="R86" t="n">
-        <v>7014764</v>
+        <v>7014776</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9182,32 +9177,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137872</v>
+        <v>129137816</v>
       </c>
       <c r="B87" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9217,10 +9212,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548477</v>
+        <v>548400</v>
       </c>
       <c r="R87" t="n">
-        <v>7015144</v>
+        <v>7014970</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9282,7 +9277,7 @@
         <v>129137805</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9376,10 +9371,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137796</v>
+        <v>129137745</v>
       </c>
       <c r="B89" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9387,21 +9382,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9411,10 +9406,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548559</v>
+        <v>548373</v>
       </c>
       <c r="R89" t="n">
-        <v>7014776</v>
+        <v>7014966</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9447,6 +9442,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9473,32 +9473,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137816</v>
+        <v>129137900</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>105776</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548400</v>
+        <v>548451</v>
       </c>
       <c r="R90" t="n">
-        <v>7014970</v>
+        <v>7014746</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9573,7 +9573,7 @@
         <v>129137878</v>
       </c>
       <c r="B91" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>129137901</v>
       </c>
       <c r="B93" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129137790</v>
       </c>
       <c r="B94" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>129137911</v>
       </c>
       <c r="B96" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>129137908</v>
       </c>
       <c r="B97" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10254,32 +10254,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137788</v>
+        <v>129137912</v>
       </c>
       <c r="B98" t="n">
-        <v>98710</v>
+        <v>96831</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548605</v>
+        <v>548604</v>
       </c>
       <c r="R98" t="n">
-        <v>7014687</v>
+        <v>7015234</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10325,11 +10325,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10356,32 +10351,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137874</v>
+        <v>129137863</v>
       </c>
       <c r="B99" t="n">
-        <v>97587</v>
+        <v>80150</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10391,10 +10386,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548348</v>
+        <v>548702</v>
       </c>
       <c r="R99" t="n">
-        <v>7014988</v>
+        <v>7014752</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10453,32 +10448,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137863</v>
+        <v>129137788</v>
       </c>
       <c r="B100" t="n">
-        <v>80149</v>
+        <v>98712</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10488,10 +10483,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548702</v>
+        <v>548605</v>
       </c>
       <c r="R100" t="n">
-        <v>7014752</v>
+        <v>7014687</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10524,6 +10519,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10550,32 +10550,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137912</v>
+        <v>129137903</v>
       </c>
       <c r="B101" t="n">
-        <v>96829</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548604</v>
+        <v>548633</v>
       </c>
       <c r="R101" t="n">
-        <v>7015234</v>
+        <v>7015045</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10647,10 +10647,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137903</v>
+        <v>129137848</v>
       </c>
       <c r="B102" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10658,21 +10658,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10682,10 +10682,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548633</v>
+        <v>548598</v>
       </c>
       <c r="R102" t="n">
-        <v>7015045</v>
+        <v>7015227</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10718,6 +10718,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10744,32 +10749,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137848</v>
+        <v>129137874</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>97589</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10779,10 +10784,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548598</v>
+        <v>548348</v>
       </c>
       <c r="R103" t="n">
-        <v>7015227</v>
+        <v>7014988</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10815,11 +10820,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10846,32 +10846,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137758</v>
+        <v>129137883</v>
       </c>
       <c r="B104" t="n">
-        <v>97581</v>
+        <v>80149</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548629</v>
+        <v>548499</v>
       </c>
       <c r="R104" t="n">
-        <v>7014777</v>
+        <v>7015176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10943,32 +10943,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137840</v>
+        <v>129137758</v>
       </c>
       <c r="B105" t="n">
-        <v>91543</v>
+        <v>97583</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548660</v>
+        <v>548629</v>
       </c>
       <c r="R105" t="n">
-        <v>7014820</v>
+        <v>7014777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
         <v>129137753</v>
       </c>
       <c r="B106" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137883</v>
+        <v>129137840</v>
       </c>
       <c r="B107" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11148,21 +11148,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548499</v>
+        <v>548660</v>
       </c>
       <c r="R107" t="n">
-        <v>7015176</v>
+        <v>7014820</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11237,7 +11237,7 @@
         <v>129137768</v>
       </c>
       <c r="B108" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137740</v>
+        <v>129137751</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548618</v>
+        <v>548268</v>
       </c>
       <c r="R9" t="n">
-        <v>7015211</v>
+        <v>7014891</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137751</v>
+        <v>129137787</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548268</v>
+        <v>548366</v>
       </c>
       <c r="R10" t="n">
-        <v>7014891</v>
+        <v>7014942</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137870</v>
+        <v>129137740</v>
       </c>
       <c r="B11" t="n">
-        <v>97589</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548358</v>
+        <v>548618</v>
       </c>
       <c r="R11" t="n">
-        <v>7014777</v>
+        <v>7015211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137787</v>
+        <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>97593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548366</v>
+        <v>548358</v>
       </c>
       <c r="R12" t="n">
-        <v>7014942</v>
+        <v>7014777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,11 +1817,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B13" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,19 +1854,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1874,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R13" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137804</v>
+        <v>129137794</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,23 +1951,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548550</v>
+        <v>548459</v>
       </c>
       <c r="R14" t="n">
-        <v>7015142</v>
+        <v>7015186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137802</v>
+        <v>129137801</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548499</v>
+        <v>548686</v>
       </c>
       <c r="R18" t="n">
-        <v>7014902</v>
+        <v>7014817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137801</v>
+        <v>129137802</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548686</v>
+        <v>548499</v>
       </c>
       <c r="R19" t="n">
-        <v>7014817</v>
+        <v>7014902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2536,7 @@
         <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,32 +2630,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137771</v>
+        <v>129137906</v>
       </c>
       <c r="B21" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548360</v>
+        <v>548693</v>
       </c>
       <c r="R21" t="n">
-        <v>7014942</v>
+        <v>7014874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,32 +2727,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B22" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R22" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2824,32 +2824,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137744</v>
+        <v>129137771</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548511</v>
+        <v>548360</v>
       </c>
       <c r="R23" t="n">
-        <v>7015241</v>
+        <v>7014942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2895,11 +2895,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2926,32 +2921,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137750</v>
+        <v>129137862</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548514</v>
+        <v>548497</v>
       </c>
       <c r="R24" t="n">
-        <v>7015227</v>
+        <v>7015181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,11 +2992,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3028,10 +3018,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137906</v>
+        <v>129137744</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,21 +3029,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548693</v>
+        <v>548511</v>
       </c>
       <c r="R25" t="n">
-        <v>7014874</v>
+        <v>7015241</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3099,6 +3089,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137819</v>
+        <v>129137750</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548318</v>
+        <v>548514</v>
       </c>
       <c r="R26" t="n">
-        <v>7014904</v>
+        <v>7015227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,6 +3191,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3222,32 +3222,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137749</v>
+        <v>129137876</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>80177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548618</v>
+        <v>548475</v>
       </c>
       <c r="R27" t="n">
-        <v>7015211</v>
+        <v>7015265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3293,11 +3293,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3324,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137810</v>
+        <v>129137749</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,21 +3330,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548538</v>
+        <v>548618</v>
       </c>
       <c r="R28" t="n">
-        <v>7015259</v>
+        <v>7015211</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3395,6 +3390,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3421,32 +3421,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137806</v>
+        <v>129125929</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>97587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548632</v>
+        <v>548372</v>
       </c>
       <c r="R29" t="n">
-        <v>7015246</v>
+        <v>7014829</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B30" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R30" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129125929</v>
+        <v>129137806</v>
       </c>
       <c r="B31" t="n">
-        <v>97583</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548372</v>
+        <v>548632</v>
       </c>
       <c r="R31" t="n">
-        <v>7014829</v>
+        <v>7015246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,32 +3712,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137789</v>
+        <v>129137800</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548461</v>
+        <v>548708</v>
       </c>
       <c r="R32" t="n">
-        <v>7015210</v>
+        <v>7014937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,32 +3814,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B33" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R33" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3916,49 +3911,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129126213</v>
+        <v>129137849</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548265</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7014876</v>
+        <v>7015247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3991,6 +3982,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,32 +4013,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137800</v>
+        <v>129137789</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4052,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548708</v>
+        <v>548461</v>
       </c>
       <c r="R35" t="n">
-        <v>7014937</v>
+        <v>7015210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,7 +4088,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,32 +4115,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4154,10 +4150,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R36" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,6 +4186,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4216,45 +4217,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137849</v>
+        <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548629</v>
+        <v>548265</v>
       </c>
       <c r="R37" t="n">
-        <v>7015247</v>
+        <v>7014876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4287,11 +4292,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,7 +4714,7 @@
         <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137792</v>
+        <v>129137766</v>
       </c>
       <c r="B43" t="n">
-        <v>105776</v>
+        <v>97593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548368</v>
+        <v>548366</v>
       </c>
       <c r="R43" t="n">
-        <v>7014860</v>
+        <v>7014942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4915,32 +4915,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137843</v>
+        <v>129137792</v>
       </c>
       <c r="B44" t="n">
-        <v>91545</v>
+        <v>105780</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548488</v>
+        <v>548368</v>
       </c>
       <c r="R44" t="n">
-        <v>7015296</v>
+        <v>7014860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4986,6 +4986,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5012,32 +5017,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137909</v>
+        <v>129137891</v>
       </c>
       <c r="B45" t="n">
-        <v>82878</v>
+        <v>98716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5047,10 +5052,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548610</v>
+        <v>548627</v>
       </c>
       <c r="R45" t="n">
-        <v>7015229</v>
+        <v>7015253</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5083,6 +5088,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5109,32 +5119,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137822</v>
+        <v>129137783</v>
       </c>
       <c r="B46" t="n">
-        <v>57648</v>
+        <v>98716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5144,10 +5154,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548346</v>
+        <v>548595</v>
       </c>
       <c r="R46" t="n">
-        <v>7015026</v>
+        <v>7015162</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5180,6 +5190,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5206,10 +5221,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137783</v>
+        <v>129137786</v>
       </c>
       <c r="B47" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5241,10 +5256,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548595</v>
+        <v>548402</v>
       </c>
       <c r="R47" t="n">
-        <v>7015162</v>
+        <v>7015096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5281,7 +5296,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5308,32 +5323,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B48" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5343,10 +5358,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R48" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,11 +5394,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5410,32 +5420,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137786</v>
+        <v>129137909</v>
       </c>
       <c r="B49" t="n">
-        <v>98712</v>
+        <v>82878</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5445,10 +5455,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548402</v>
+        <v>548610</v>
       </c>
       <c r="R49" t="n">
-        <v>7015096</v>
+        <v>7015229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,11 +5491,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5512,32 +5517,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137766</v>
+        <v>129137803</v>
       </c>
       <c r="B50" t="n">
-        <v>97589</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5547,10 +5552,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548366</v>
+        <v>548467</v>
       </c>
       <c r="R50" t="n">
-        <v>7014942</v>
+        <v>7014995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,11 +5588,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137803</v>
+        <v>129137822</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57648</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548467</v>
+        <v>548346</v>
       </c>
       <c r="R52" t="n">
-        <v>7014995</v>
+        <v>7015026</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129126001</v>
+        <v>129137845</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548299</v>
+        <v>548531</v>
       </c>
       <c r="R53" t="n">
-        <v>7014876</v>
+        <v>7014817</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,6 +5879,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5905,10 +5910,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137905</v>
+        <v>129137746</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,21 +5921,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5940,10 +5945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548618</v>
+        <v>548355</v>
       </c>
       <c r="R54" t="n">
-        <v>7015116</v>
+        <v>7014874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5976,6 +5981,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6002,32 +6012,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137877</v>
+        <v>129137739</v>
       </c>
       <c r="B55" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6037,10 +6047,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548334</v>
+        <v>548460</v>
       </c>
       <c r="R55" t="n">
-        <v>7015001</v>
+        <v>7014976</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6073,6 +6083,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6099,10 +6114,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137882</v>
+        <v>129137905</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6110,21 +6125,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6134,10 +6149,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548510</v>
+        <v>548618</v>
       </c>
       <c r="R56" t="n">
-        <v>7015191</v>
+        <v>7015116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6196,10 +6211,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137739</v>
+        <v>129126001</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6207,21 +6222,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6231,10 +6246,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548460</v>
+        <v>548299</v>
       </c>
       <c r="R57" t="n">
-        <v>7014976</v>
+        <v>7014876</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,11 +6282,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6298,32 +6308,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137845</v>
+        <v>129137877</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6333,10 +6343,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548531</v>
+        <v>548334</v>
       </c>
       <c r="R58" t="n">
-        <v>7014817</v>
+        <v>7015001</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6369,11 +6379,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6400,10 +6405,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137746</v>
+        <v>129137882</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6411,21 +6416,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6435,10 +6440,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548355</v>
+        <v>548510</v>
       </c>
       <c r="R59" t="n">
-        <v>7014874</v>
+        <v>7015191</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6471,11 +6476,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6706,32 +6706,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137910</v>
+        <v>129137782</v>
       </c>
       <c r="B62" t="n">
-        <v>92827</v>
+        <v>98716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548510</v>
+        <v>548485</v>
       </c>
       <c r="R62" t="n">
-        <v>7014986</v>
+        <v>7014854</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6777,6 +6777,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6803,32 +6808,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137782</v>
+        <v>129137910</v>
       </c>
       <c r="B63" t="n">
-        <v>98712</v>
+        <v>92831</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6838,10 +6843,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548485</v>
+        <v>548510</v>
       </c>
       <c r="R63" t="n">
-        <v>7014854</v>
+        <v>7014986</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,11 +6879,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7201,32 +7201,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137890</v>
+        <v>129137858</v>
       </c>
       <c r="B67" t="n">
-        <v>98712</v>
+        <v>56917</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548594</v>
+        <v>548400</v>
       </c>
       <c r="R67" t="n">
-        <v>7015211</v>
+        <v>7015152</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7303,32 +7303,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137791</v>
+        <v>129137811</v>
       </c>
       <c r="B68" t="n">
-        <v>105776</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548452</v>
+        <v>548458</v>
       </c>
       <c r="R68" t="n">
-        <v>7014769</v>
+        <v>7015205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7400,32 +7400,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137811</v>
+        <v>129137890</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548458</v>
+        <v>548594</v>
       </c>
       <c r="R69" t="n">
-        <v>7015205</v>
+        <v>7015211</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7471,6 +7471,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7497,10 +7502,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137858</v>
+        <v>129137762</v>
       </c>
       <c r="B70" t="n">
-        <v>56917</v>
+        <v>97593</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7508,21 +7513,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7532,10 +7537,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548400</v>
+        <v>548603</v>
       </c>
       <c r="R70" t="n">
-        <v>7015152</v>
+        <v>7014709</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7568,11 +7573,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7599,10 +7599,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137762</v>
+        <v>129137791</v>
       </c>
       <c r="B71" t="n">
-        <v>97589</v>
+        <v>105780</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7610,21 +7610,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548603</v>
+        <v>548452</v>
       </c>
       <c r="R71" t="n">
-        <v>7014709</v>
+        <v>7014769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7696,10 +7696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137850</v>
+        <v>129137902</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,23 +7707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7731,10 +7727,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548629</v>
+        <v>548480</v>
       </c>
       <c r="R72" t="n">
-        <v>7015262</v>
+        <v>7015285</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7767,11 +7763,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7801,7 +7792,7 @@
         <v>129137780</v>
       </c>
       <c r="B73" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7900,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137902</v>
+        <v>129137773</v>
       </c>
       <c r="B74" t="n">
-        <v>91565</v>
+        <v>80149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7911,19 +7902,23 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -7931,10 +7926,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548480</v>
+        <v>548717</v>
       </c>
       <c r="R74" t="n">
-        <v>7015285</v>
+        <v>7014991</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7993,32 +7988,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137773</v>
+        <v>129137886</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8028,10 +8023,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548717</v>
+        <v>548498</v>
       </c>
       <c r="R75" t="n">
-        <v>7014991</v>
+        <v>7015173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8090,32 +8085,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137886</v>
+        <v>129137850</v>
       </c>
       <c r="B76" t="n">
-        <v>80185</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8125,10 +8120,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548498</v>
+        <v>548629</v>
       </c>
       <c r="R76" t="n">
-        <v>7015173</v>
+        <v>7015262</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8161,6 +8156,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8289,7 +8289,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137818</v>
+        <v>129137813</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548329</v>
+        <v>548374</v>
       </c>
       <c r="R78" t="n">
-        <v>7014932</v>
+        <v>7015064</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137813</v>
+        <v>129137818</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548374</v>
+        <v>548329</v>
       </c>
       <c r="R79" t="n">
-        <v>7015064</v>
+        <v>7014932</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8483,32 +8483,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137759</v>
+        <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>97583</v>
+        <v>98716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548487</v>
+        <v>548620</v>
       </c>
       <c r="R80" t="n">
-        <v>7014855</v>
+        <v>7014685</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8554,6 +8554,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8580,32 +8585,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137779</v>
+        <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>98712</v>
+        <v>97587</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8615,10 +8620,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548620</v>
+        <v>548487</v>
       </c>
       <c r="R81" t="n">
-        <v>7014685</v>
+        <v>7014855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8651,11 +8656,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8682,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137889</v>
+        <v>129137805</v>
       </c>
       <c r="B82" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548440</v>
+        <v>548613</v>
       </c>
       <c r="R82" t="n">
-        <v>7014752</v>
+        <v>7015186</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,11 +8753,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8784,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137781</v>
+        <v>129137796</v>
       </c>
       <c r="B83" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548433</v>
+        <v>548559</v>
       </c>
       <c r="R83" t="n">
-        <v>7014771</v>
+        <v>7014776</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8855,11 +8850,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8886,32 +8876,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137871</v>
+        <v>129137816</v>
       </c>
       <c r="B84" t="n">
-        <v>97589</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8921,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548457</v>
+        <v>548400</v>
       </c>
       <c r="R84" t="n">
-        <v>7014764</v>
+        <v>7014970</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8983,32 +8973,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137872</v>
+        <v>129137745</v>
       </c>
       <c r="B85" t="n">
-        <v>97589</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9018,10 +9008,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548477</v>
+        <v>548373</v>
       </c>
       <c r="R85" t="n">
-        <v>7015144</v>
+        <v>7014966</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9054,6 +9044,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9080,32 +9075,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137796</v>
+        <v>129137781</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9115,10 +9110,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548559</v>
+        <v>548433</v>
       </c>
       <c r="R86" t="n">
-        <v>7014776</v>
+        <v>7014771</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9151,6 +9146,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,32 +9177,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137816</v>
+        <v>129137900</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>105780</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9212,10 +9212,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548400</v>
+        <v>548451</v>
       </c>
       <c r="R87" t="n">
-        <v>7014970</v>
+        <v>7014746</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9274,32 +9274,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137805</v>
+        <v>129137889</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548613</v>
+        <v>548440</v>
       </c>
       <c r="R88" t="n">
-        <v>7015186</v>
+        <v>7014752</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9345,6 +9345,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9371,32 +9376,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137745</v>
+        <v>129137872</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>97593</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9406,10 +9411,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548373</v>
+        <v>548477</v>
       </c>
       <c r="R89" t="n">
-        <v>7014966</v>
+        <v>7015144</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9442,11 +9447,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9473,10 +9473,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137900</v>
+        <v>129137871</v>
       </c>
       <c r="B90" t="n">
-        <v>105776</v>
+        <v>97593</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9484,21 +9484,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548451</v>
+        <v>548457</v>
       </c>
       <c r="R90" t="n">
-        <v>7014746</v>
+        <v>7014764</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9769,10 +9769,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137901</v>
+        <v>129137790</v>
       </c>
       <c r="B93" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548281</v>
+        <v>548558</v>
       </c>
       <c r="R93" t="n">
-        <v>7015128</v>
+        <v>7014771</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9866,10 +9866,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129137790</v>
+        <v>129137901</v>
       </c>
       <c r="B94" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9901,10 +9901,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548558</v>
+        <v>548281</v>
       </c>
       <c r="R94" t="n">
-        <v>7014771</v>
+        <v>7015128</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9966,7 +9966,7 @@
         <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10254,10 +10254,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137912</v>
+        <v>129137874</v>
       </c>
       <c r="B98" t="n">
-        <v>96831</v>
+        <v>97593</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548604</v>
+        <v>548348</v>
       </c>
       <c r="R98" t="n">
-        <v>7015234</v>
+        <v>7014988</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10351,32 +10351,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137863</v>
+        <v>129137788</v>
       </c>
       <c r="B99" t="n">
-        <v>80150</v>
+        <v>98716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548702</v>
+        <v>548605</v>
       </c>
       <c r="R99" t="n">
-        <v>7014752</v>
+        <v>7014687</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10422,6 +10422,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10448,32 +10453,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137788</v>
+        <v>129137903</v>
       </c>
       <c r="B100" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10483,10 +10488,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548605</v>
+        <v>548633</v>
       </c>
       <c r="R100" t="n">
-        <v>7014687</v>
+        <v>7015045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10519,11 +10524,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10550,32 +10550,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137903</v>
+        <v>129137912</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>96835</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548633</v>
+        <v>548604</v>
       </c>
       <c r="R101" t="n">
-        <v>7015045</v>
+        <v>7015234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10647,10 +10647,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137848</v>
+        <v>129137863</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10658,21 +10658,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10682,10 +10682,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548598</v>
+        <v>548702</v>
       </c>
       <c r="R102" t="n">
-        <v>7015227</v>
+        <v>7014752</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10718,11 +10718,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10749,32 +10744,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137874</v>
+        <v>129137848</v>
       </c>
       <c r="B103" t="n">
-        <v>97589</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10784,10 +10779,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548348</v>
+        <v>548598</v>
       </c>
       <c r="R103" t="n">
-        <v>7014988</v>
+        <v>7015227</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10820,6 +10815,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10846,32 +10846,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137883</v>
+        <v>129137758</v>
       </c>
       <c r="B104" t="n">
-        <v>80149</v>
+        <v>97587</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548499</v>
+        <v>548629</v>
       </c>
       <c r="R104" t="n">
-        <v>7015176</v>
+        <v>7014777</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10943,32 +10943,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137758</v>
+        <v>129137883</v>
       </c>
       <c r="B105" t="n">
-        <v>97583</v>
+        <v>80149</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548629</v>
+        <v>548499</v>
       </c>
       <c r="R105" t="n">
-        <v>7014777</v>
+        <v>7015176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
         <v>129137753</v>
       </c>
       <c r="B106" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>129137840</v>
       </c>
       <c r="B107" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11535,10 +11535,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137873</v>
+        <v>129137761</v>
       </c>
       <c r="B111" t="n">
-        <v>97589</v>
+        <v>97587</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11546,16 +11546,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11570,10 +11570,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548291</v>
+        <v>548366</v>
       </c>
       <c r="R111" t="n">
-        <v>7015110</v>
+        <v>7015047</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11632,10 +11632,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137761</v>
+        <v>129137873</v>
       </c>
       <c r="B112" t="n">
-        <v>97583</v>
+        <v>97593</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11643,16 +11643,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11667,10 +11667,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548366</v>
+        <v>548291</v>
       </c>
       <c r="R112" t="n">
-        <v>7015047</v>
+        <v>7015110</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137817</v>
+        <v>129137740</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548367</v>
+        <v>548618</v>
       </c>
       <c r="R6" t="n">
-        <v>7014944</v>
+        <v>7015211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,6 +1215,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,32 +1246,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137797</v>
+        <v>129137787</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548657</v>
+        <v>548366</v>
       </c>
       <c r="R7" t="n">
-        <v>7014768</v>
+        <v>7014942</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,6 +1317,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137815</v>
+        <v>129137817</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1373,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548398</v>
+        <v>548367</v>
       </c>
       <c r="R8" t="n">
-        <v>7015004</v>
+        <v>7014944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,11 +1419,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137751</v>
+        <v>129137797</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548268</v>
+        <v>548657</v>
       </c>
       <c r="R9" t="n">
-        <v>7014891</v>
+        <v>7014768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,11 +1516,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137787</v>
+        <v>129137815</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548366</v>
+        <v>548398</v>
       </c>
       <c r="R10" t="n">
-        <v>7014942</v>
+        <v>7015004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137740</v>
+        <v>129137751</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548618</v>
+        <v>548268</v>
       </c>
       <c r="R11" t="n">
-        <v>7015211</v>
+        <v>7014891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,7 +1749,7 @@
         <v>129137870</v>
       </c>
       <c r="B12" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R13" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,6 +1914,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B14" t="n">
-        <v>91569</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,19 +1956,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1971,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R14" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137795</v>
+        <v>129137794</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,23 +2053,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2068,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548538</v>
+        <v>548459</v>
       </c>
       <c r="R15" t="n">
-        <v>7014770</v>
+        <v>7015186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,11 +2109,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2536,7 +2536,7 @@
         <v>129137869</v>
       </c>
       <c r="B20" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137906</v>
+        <v>129137750</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548693</v>
+        <v>548514</v>
       </c>
       <c r="R21" t="n">
-        <v>7014874</v>
+        <v>7015227</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,6 +2701,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2727,10 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137819</v>
+        <v>129137744</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,21 +2743,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548318</v>
+        <v>548511</v>
       </c>
       <c r="R22" t="n">
-        <v>7014904</v>
+        <v>7015241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2798,6 +2803,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,10 +3028,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137744</v>
+        <v>129137906</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3029,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3053,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548511</v>
+        <v>548693</v>
       </c>
       <c r="R25" t="n">
-        <v>7015241</v>
+        <v>7014874</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3089,11 +3099,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3120,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137750</v>
+        <v>129137819</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3160,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548514</v>
+        <v>548318</v>
       </c>
       <c r="R26" t="n">
-        <v>7015227</v>
+        <v>7014904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,11 +3196,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3222,32 +3222,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B27" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R27" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137749</v>
+        <v>129137806</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548618</v>
+        <v>548632</v>
       </c>
       <c r="R28" t="n">
-        <v>7015211</v>
+        <v>7015246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3390,11 +3390,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3421,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129125929</v>
+        <v>129137876</v>
       </c>
       <c r="B29" t="n">
-        <v>97587</v>
+        <v>80177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3456,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548372</v>
+        <v>548475</v>
       </c>
       <c r="R29" t="n">
-        <v>7014829</v>
+        <v>7015265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,32 +3513,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137810</v>
+        <v>129125929</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548538</v>
+        <v>548372</v>
       </c>
       <c r="R30" t="n">
-        <v>7015259</v>
+        <v>7014829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,10 +3610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137806</v>
+        <v>129137749</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3621,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548632</v>
+        <v>548618</v>
       </c>
       <c r="R31" t="n">
-        <v>7015246</v>
+        <v>7015211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3686,6 +3681,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3712,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137800</v>
+        <v>129137849</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548708</v>
+        <v>548629</v>
       </c>
       <c r="R32" t="n">
-        <v>7014937</v>
+        <v>7015247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,7 +3814,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137821</v>
+        <v>129137800</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548369</v>
+        <v>548708</v>
       </c>
       <c r="R33" t="n">
-        <v>7014853</v>
+        <v>7014937</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,6 +3885,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3911,10 +3916,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137849</v>
+        <v>129137821</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,21 +3927,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548369</v>
       </c>
       <c r="R34" t="n">
-        <v>7015247</v>
+        <v>7014853</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,11 +3987,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4016,7 +4016,7 @@
         <v>129137789</v>
       </c>
       <c r="B35" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137766</v>
+        <v>129137803</v>
       </c>
       <c r="B43" t="n">
-        <v>97593</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548366</v>
+        <v>548467</v>
       </c>
       <c r="R43" t="n">
-        <v>7014942</v>
+        <v>7014995</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4884,11 +4884,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4915,32 +4910,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137792</v>
+        <v>129137814</v>
       </c>
       <c r="B44" t="n">
-        <v>105780</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4950,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548368</v>
+        <v>548376</v>
       </c>
       <c r="R44" t="n">
-        <v>7014860</v>
+        <v>7015053</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4986,11 +4981,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5017,32 +5007,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B45" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5052,10 +5042,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R45" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5088,11 +5078,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5119,32 +5104,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137783</v>
+        <v>129137909</v>
       </c>
       <c r="B46" t="n">
-        <v>98716</v>
+        <v>82878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5154,10 +5139,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548595</v>
+        <v>548610</v>
       </c>
       <c r="R46" t="n">
-        <v>7015162</v>
+        <v>7015229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5190,11 +5175,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5221,32 +5201,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137786</v>
+        <v>129137822</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>57648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5256,10 +5236,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548402</v>
+        <v>548346</v>
       </c>
       <c r="R47" t="n">
-        <v>7015096</v>
+        <v>7015026</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5292,11 +5272,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5323,32 +5298,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137843</v>
+        <v>129137786</v>
       </c>
       <c r="B48" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5358,10 +5333,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548488</v>
+        <v>548402</v>
       </c>
       <c r="R48" t="n">
-        <v>7015296</v>
+        <v>7015096</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5394,6 +5369,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5420,32 +5400,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137909</v>
+        <v>129137792</v>
       </c>
       <c r="B49" t="n">
-        <v>82878</v>
+        <v>105790</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5455,10 +5435,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548610</v>
+        <v>548368</v>
       </c>
       <c r="R49" t="n">
-        <v>7015229</v>
+        <v>7014860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5491,6 +5471,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5517,32 +5502,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137803</v>
+        <v>129137783</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5552,10 +5537,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548467</v>
+        <v>548595</v>
       </c>
       <c r="R50" t="n">
-        <v>7014995</v>
+        <v>7015162</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,6 +5573,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5614,32 +5604,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137814</v>
+        <v>129137891</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5649,10 +5639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548376</v>
+        <v>548627</v>
       </c>
       <c r="R51" t="n">
-        <v>7015053</v>
+        <v>7015253</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,6 +5675,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5711,32 +5706,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137822</v>
+        <v>129137766</v>
       </c>
       <c r="B52" t="n">
-        <v>57648</v>
+        <v>97601</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100001</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5746,10 +5741,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548346</v>
+        <v>548366</v>
       </c>
       <c r="R52" t="n">
-        <v>7015026</v>
+        <v>7014942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5782,6 +5777,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137845</v>
+        <v>129137860</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548531</v>
+        <v>548481</v>
       </c>
       <c r="R53" t="n">
-        <v>7014817</v>
+        <v>7015172</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5910,10 +5910,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137746</v>
+        <v>129137859</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5921,21 +5921,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548355</v>
+        <v>548434</v>
       </c>
       <c r="R54" t="n">
-        <v>7014874</v>
+        <v>7014792</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6012,10 +6012,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137739</v>
+        <v>129137905</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6023,21 +6023,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548460</v>
+        <v>548618</v>
       </c>
       <c r="R55" t="n">
-        <v>7014976</v>
+        <v>7015116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6083,11 +6083,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6114,7 +6109,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137905</v>
+        <v>129126001</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548618</v>
+        <v>548299</v>
       </c>
       <c r="R56" t="n">
-        <v>7015116</v>
+        <v>7014876</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6211,10 +6206,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129126001</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6222,21 +6217,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6246,10 +6241,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548299</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7014876</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6282,6 +6277,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6308,32 +6308,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137877</v>
+        <v>129137845</v>
       </c>
       <c r="B58" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548334</v>
+        <v>548531</v>
       </c>
       <c r="R58" t="n">
-        <v>7015001</v>
+        <v>7014817</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6379,6 +6379,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6405,10 +6410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137882</v>
+        <v>129137746</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6416,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6440,10 +6445,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548510</v>
+        <v>548355</v>
       </c>
       <c r="R59" t="n">
-        <v>7015191</v>
+        <v>7014874</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6476,6 +6481,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6502,32 +6512,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137860</v>
+        <v>129137877</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>80177</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6537,10 +6547,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548481</v>
+        <v>548334</v>
       </c>
       <c r="R60" t="n">
-        <v>7015172</v>
+        <v>7015001</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6573,11 +6583,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6604,10 +6609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137859</v>
+        <v>129137882</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,21 +6620,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6639,10 +6644,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548434</v>
+        <v>548510</v>
       </c>
       <c r="R61" t="n">
-        <v>7014792</v>
+        <v>7015191</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6675,11 +6680,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6706,32 +6706,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137782</v>
+        <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>98716</v>
+        <v>92832</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548485</v>
+        <v>548510</v>
       </c>
       <c r="R62" t="n">
-        <v>7014854</v>
+        <v>7014986</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6777,11 +6777,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6808,10 +6803,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B63" t="n">
-        <v>92831</v>
+        <v>80177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6819,21 +6814,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6843,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R63" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6905,7 +6900,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B64" t="n">
         <v>80177</v>
@@ -6940,10 +6935,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R64" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7002,32 +6997,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129137875</v>
+        <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>80177</v>
+        <v>98724</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7037,10 +7032,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548581</v>
+        <v>548485</v>
       </c>
       <c r="R65" t="n">
-        <v>7015017</v>
+        <v>7014854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,6 +7068,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>80 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7099,10 +7099,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137857</v>
+        <v>129137811</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7110,21 +7110,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548502</v>
+        <v>548458</v>
       </c>
       <c r="R66" t="n">
-        <v>7015176</v>
+        <v>7015205</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7170,11 +7170,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7201,32 +7196,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137858</v>
+        <v>129137857</v>
       </c>
       <c r="B67" t="n">
-        <v>56917</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7236,10 +7231,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548400</v>
+        <v>548502</v>
       </c>
       <c r="R67" t="n">
-        <v>7015152</v>
+        <v>7015176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7276,7 +7271,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>1 ex, förbiflygande</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7303,32 +7298,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137811</v>
+        <v>129137858</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7338,10 +7333,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548458</v>
+        <v>548400</v>
       </c>
       <c r="R68" t="n">
-        <v>7015205</v>
+        <v>7015152</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7374,6 +7369,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7403,7 +7403,7 @@
         <v>129137890</v>
       </c>
       <c r="B69" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137762</v>
+        <v>129137791</v>
       </c>
       <c r="B70" t="n">
-        <v>97593</v>
+        <v>105790</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7513,21 +7513,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548603</v>
+        <v>548452</v>
       </c>
       <c r="R70" t="n">
-        <v>7014709</v>
+        <v>7014769</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7599,10 +7599,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137791</v>
+        <v>129137762</v>
       </c>
       <c r="B71" t="n">
-        <v>105780</v>
+        <v>97601</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7610,21 +7610,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548452</v>
+        <v>548603</v>
       </c>
       <c r="R71" t="n">
-        <v>7014769</v>
+        <v>7014709</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7696,10 +7696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137902</v>
+        <v>129137850</v>
       </c>
       <c r="B72" t="n">
-        <v>91569</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,19 +7707,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7727,10 +7731,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548480</v>
+        <v>548629</v>
       </c>
       <c r="R72" t="n">
-        <v>7015285</v>
+        <v>7015262</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7763,6 +7767,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7789,32 +7798,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137780</v>
+        <v>129137773</v>
       </c>
       <c r="B73" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7824,10 +7833,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548594</v>
+        <v>548717</v>
       </c>
       <c r="R73" t="n">
-        <v>7015114</v>
+        <v>7014991</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7860,11 +7869,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7891,32 +7895,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137773</v>
+        <v>129137886</v>
       </c>
       <c r="B74" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7926,10 +7930,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548717</v>
+        <v>548498</v>
       </c>
       <c r="R74" t="n">
-        <v>7014991</v>
+        <v>7015173</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,32 +7992,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137886</v>
+        <v>129137780</v>
       </c>
       <c r="B75" t="n">
-        <v>80185</v>
+        <v>98724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8023,10 +8027,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548498</v>
+        <v>548594</v>
       </c>
       <c r="R75" t="n">
-        <v>7015173</v>
+        <v>7015114</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,6 +8063,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8085,10 +8094,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137850</v>
+        <v>129137902</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,23 +8105,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8120,10 +8125,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548629</v>
+        <v>548480</v>
       </c>
       <c r="R76" t="n">
-        <v>7015262</v>
+        <v>7015285</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,11 +8161,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8486,7 +8486,7 @@
         <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>129137759</v>
       </c>
       <c r="B81" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8682,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137805</v>
+        <v>129137871</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548613</v>
+        <v>548457</v>
       </c>
       <c r="R82" t="n">
-        <v>7015186</v>
+        <v>7014764</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8779,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137796</v>
+        <v>129137872</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548559</v>
+        <v>548477</v>
       </c>
       <c r="R83" t="n">
-        <v>7014776</v>
+        <v>7015144</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8876,7 +8876,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137816</v>
+        <v>129137805</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548400</v>
+        <v>548613</v>
       </c>
       <c r="R84" t="n">
-        <v>7014970</v>
+        <v>7015186</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8973,10 +8973,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137745</v>
+        <v>129137796</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8984,21 +8984,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548373</v>
+        <v>548559</v>
       </c>
       <c r="R85" t="n">
-        <v>7014966</v>
+        <v>7014776</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9044,11 +9044,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9075,32 +9070,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137781</v>
+        <v>129137816</v>
       </c>
       <c r="B86" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9110,10 +9105,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548433</v>
+        <v>548400</v>
       </c>
       <c r="R86" t="n">
-        <v>7014771</v>
+        <v>7014970</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9146,11 +9141,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,32 +9167,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137900</v>
+        <v>129137745</v>
       </c>
       <c r="B87" t="n">
-        <v>105780</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9212,10 +9202,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548451</v>
+        <v>548373</v>
       </c>
       <c r="R87" t="n">
-        <v>7014746</v>
+        <v>7014966</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9248,6 +9238,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9274,10 +9269,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137889</v>
+        <v>129137781</v>
       </c>
       <c r="B88" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9309,10 +9304,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548440</v>
+        <v>548433</v>
       </c>
       <c r="R88" t="n">
-        <v>7014752</v>
+        <v>7014771</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9349,7 +9344,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9376,10 +9371,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129137872</v>
+        <v>129137900</v>
       </c>
       <c r="B89" t="n">
-        <v>97593</v>
+        <v>105790</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9387,21 +9382,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9411,10 +9406,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548477</v>
+        <v>548451</v>
       </c>
       <c r="R89" t="n">
-        <v>7015144</v>
+        <v>7014746</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9473,32 +9468,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129137871</v>
+        <v>129137889</v>
       </c>
       <c r="B90" t="n">
-        <v>97593</v>
+        <v>98724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548457</v>
+        <v>548440</v>
       </c>
       <c r="R90" t="n">
-        <v>7014764</v>
+        <v>7014752</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9544,6 +9539,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9772,7 +9772,7 @@
         <v>129137790</v>
       </c>
       <c r="B93" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129137901</v>
       </c>
       <c r="B94" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>129137764</v>
       </c>
       <c r="B95" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10060,27 +10060,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137911</v>
+        <v>129137908</v>
       </c>
       <c r="B96" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548512</v>
+        <v>548306</v>
       </c>
       <c r="R96" t="n">
-        <v>7015192</v>
+        <v>7015082</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10157,27 +10157,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10192,10 +10192,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R97" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10254,32 +10254,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137874</v>
+        <v>129137848</v>
       </c>
       <c r="B98" t="n">
-        <v>97593</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548348</v>
+        <v>548598</v>
       </c>
       <c r="R98" t="n">
-        <v>7014988</v>
+        <v>7015227</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10325,6 +10325,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10351,32 +10356,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137788</v>
+        <v>129137912</v>
       </c>
       <c r="B99" t="n">
-        <v>98716</v>
+        <v>96843</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10386,10 +10391,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548605</v>
+        <v>548604</v>
       </c>
       <c r="R99" t="n">
-        <v>7014687</v>
+        <v>7015234</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10422,11 +10427,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10453,10 +10453,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137903</v>
+        <v>129137863</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548633</v>
+        <v>548702</v>
       </c>
       <c r="R100" t="n">
-        <v>7015045</v>
+        <v>7014752</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10550,32 +10550,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137912</v>
+        <v>129137903</v>
       </c>
       <c r="B101" t="n">
-        <v>96835</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548604</v>
+        <v>548633</v>
       </c>
       <c r="R101" t="n">
-        <v>7015234</v>
+        <v>7015045</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10647,32 +10647,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137863</v>
+        <v>129137788</v>
       </c>
       <c r="B102" t="n">
-        <v>80150</v>
+        <v>98724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10682,10 +10682,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548702</v>
+        <v>548605</v>
       </c>
       <c r="R102" t="n">
-        <v>7014752</v>
+        <v>7014687</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10718,6 +10718,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10744,32 +10749,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137848</v>
+        <v>129137874</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>97601</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10779,10 +10784,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548598</v>
+        <v>548348</v>
       </c>
       <c r="R103" t="n">
-        <v>7015227</v>
+        <v>7014988</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10815,11 +10820,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10849,7 +10849,7 @@
         <v>129137758</v>
       </c>
       <c r="B104" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,10 +10943,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137883</v>
+        <v>129137840</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548499</v>
+        <v>548660</v>
       </c>
       <c r="R105" t="n">
-        <v>7015176</v>
+        <v>7014820</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
         <v>129137753</v>
       </c>
       <c r="B106" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137840</v>
+        <v>129137883</v>
       </c>
       <c r="B107" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11148,21 +11148,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548660</v>
+        <v>548499</v>
       </c>
       <c r="R107" t="n">
-        <v>7014820</v>
+        <v>7015176</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11234,32 +11234,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129137768</v>
+        <v>129137847</v>
       </c>
       <c r="B108" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11269,10 +11269,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548723</v>
+        <v>548490</v>
       </c>
       <c r="R108" t="n">
-        <v>7014940</v>
+        <v>7014739</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11305,6 +11305,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11331,7 +11336,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129137847</v>
+        <v>129137844</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11366,10 +11371,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548490</v>
+        <v>548672</v>
       </c>
       <c r="R109" t="n">
-        <v>7014739</v>
+        <v>7014893</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11406,7 +11411,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11433,32 +11438,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129137844</v>
+        <v>129137768</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11468,10 +11473,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548672</v>
+        <v>548723</v>
       </c>
       <c r="R110" t="n">
-        <v>7014893</v>
+        <v>7014940</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,11 +11509,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11535,10 +11535,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129137761</v>
+        <v>129137873</v>
       </c>
       <c r="B111" t="n">
-        <v>97587</v>
+        <v>97601</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11546,16 +11546,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11570,10 +11570,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548366</v>
+        <v>548291</v>
       </c>
       <c r="R111" t="n">
-        <v>7015047</v>
+        <v>7015110</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11632,10 +11632,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129137873</v>
+        <v>129137761</v>
       </c>
       <c r="B112" t="n">
-        <v>97593</v>
+        <v>97595</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11643,16 +11643,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11667,10 +11667,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548291</v>
+        <v>548366</v>
       </c>
       <c r="R112" t="n">
-        <v>7015110</v>
+        <v>7015047</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1246,32 +1246,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137787</v>
+        <v>129137751</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548366</v>
+        <v>548268</v>
       </c>
       <c r="R7" t="n">
-        <v>7014942</v>
+        <v>7014891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,32 +1348,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137817</v>
+        <v>129137870</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548367</v>
+        <v>548358</v>
       </c>
       <c r="R8" t="n">
-        <v>7014944</v>
+        <v>7014777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,32 +1445,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137797</v>
+        <v>129137787</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548657</v>
+        <v>548366</v>
       </c>
       <c r="R9" t="n">
-        <v>7014768</v>
+        <v>7014942</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,6 +1516,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,7 +1547,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137815</v>
+        <v>129137817</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548398</v>
+        <v>548367</v>
       </c>
       <c r="R10" t="n">
-        <v>7015004</v>
+        <v>7014944</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137751</v>
+        <v>129137797</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548268</v>
+        <v>548657</v>
       </c>
       <c r="R11" t="n">
-        <v>7014891</v>
+        <v>7014768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137870</v>
+        <v>129137815</v>
       </c>
       <c r="B12" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548358</v>
+        <v>548398</v>
       </c>
       <c r="R12" t="n">
-        <v>7014777</v>
+        <v>7015004</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137820</v>
+        <v>129137802</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548328</v>
+        <v>548499</v>
       </c>
       <c r="R17" t="n">
-        <v>7014882</v>
+        <v>7014902</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,11 +2308,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,7 +2334,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137801</v>
+        <v>129137820</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548686</v>
+        <v>548328</v>
       </c>
       <c r="R18" t="n">
-        <v>7014817</v>
+        <v>7014882</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,6 +2405,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,7 +2436,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137802</v>
+        <v>129137801</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548499</v>
+        <v>548686</v>
       </c>
       <c r="R19" t="n">
-        <v>7014902</v>
+        <v>7014817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137750</v>
+        <v>129137906</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548514</v>
+        <v>548693</v>
       </c>
       <c r="R21" t="n">
-        <v>7015227</v>
+        <v>7014874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,11 +2701,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2732,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137744</v>
+        <v>129137819</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2743,21 +2738,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2767,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548511</v>
+        <v>548318</v>
       </c>
       <c r="R22" t="n">
-        <v>7015241</v>
+        <v>7014904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,11 +2798,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2834,32 +2824,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137771</v>
+        <v>129137744</v>
       </c>
       <c r="B23" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2869,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548360</v>
+        <v>548511</v>
       </c>
       <c r="R23" t="n">
-        <v>7014942</v>
+        <v>7015241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2905,6 +2895,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2931,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137862</v>
+        <v>129137771</v>
       </c>
       <c r="B24" t="n">
-        <v>80178</v>
+        <v>80177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548497</v>
+        <v>548360</v>
       </c>
       <c r="R24" t="n">
-        <v>7015181</v>
+        <v>7014942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,32 +3023,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137906</v>
+        <v>129137862</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548693</v>
+        <v>548497</v>
       </c>
       <c r="R25" t="n">
-        <v>7014874</v>
+        <v>7015181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137819</v>
+        <v>129137750</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548318</v>
+        <v>548514</v>
       </c>
       <c r="R26" t="n">
-        <v>7014904</v>
+        <v>7015227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,6 +3191,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137810</v>
+        <v>129137749</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548538</v>
+        <v>548618</v>
       </c>
       <c r="R27" t="n">
-        <v>7015259</v>
+        <v>7015211</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3293,6 +3293,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3319,32 +3324,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137806</v>
+        <v>129137876</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3354,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548632</v>
+        <v>548475</v>
       </c>
       <c r="R28" t="n">
-        <v>7015246</v>
+        <v>7015265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,32 +3421,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B29" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R29" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,32 +3518,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129125929</v>
+        <v>129137806</v>
       </c>
       <c r="B30" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548372</v>
+        <v>548632</v>
       </c>
       <c r="R30" t="n">
-        <v>7014829</v>
+        <v>7015246</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,32 +3615,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137749</v>
+        <v>129125929</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>97595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548618</v>
+        <v>548372</v>
       </c>
       <c r="R31" t="n">
-        <v>7015211</v>
+        <v>7014829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3681,11 +3686,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3712,32 +3712,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137849</v>
+        <v>129137789</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548629</v>
+        <v>548461</v>
       </c>
       <c r="R32" t="n">
-        <v>7015247</v>
+        <v>7015210</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,32 +3814,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137800</v>
+        <v>129137896</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548708</v>
+        <v>548260</v>
       </c>
       <c r="R33" t="n">
-        <v>7014937</v>
+        <v>7014898</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3916,45 +3916,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137821</v>
+        <v>129126213</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548369</v>
+        <v>548265</v>
       </c>
       <c r="R34" t="n">
-        <v>7014853</v>
+        <v>7014876</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4013,32 +4017,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137789</v>
+        <v>129137800</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4052,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548461</v>
+        <v>548708</v>
       </c>
       <c r="R35" t="n">
-        <v>7015210</v>
+        <v>7014937</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4115,32 +4119,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4150,10 +4154,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R36" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,11 +4190,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4217,49 +4216,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129126213</v>
+        <v>129137849</v>
       </c>
       <c r="B37" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548265</v>
+        <v>548629</v>
       </c>
       <c r="R37" t="n">
-        <v>7014876</v>
+        <v>7015247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4292,6 +4287,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,10 +4512,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137812</v>
+        <v>129137846</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548395</v>
+        <v>548317</v>
       </c>
       <c r="R40" t="n">
-        <v>7015086</v>
+        <v>7014833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4583,6 +4583,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4609,32 +4614,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137846</v>
+        <v>129137895</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548317</v>
+        <v>548277</v>
       </c>
       <c r="R41" t="n">
-        <v>7014833</v>
+        <v>7015126</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,7 +4689,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4711,32 +4716,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137895</v>
+        <v>129137812</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4746,10 +4751,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548277</v>
+        <v>548395</v>
       </c>
       <c r="R42" t="n">
-        <v>7015126</v>
+        <v>7015086</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4782,11 +4787,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4813,10 +4813,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137803</v>
+        <v>129137822</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>57648</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548467</v>
+        <v>548346</v>
       </c>
       <c r="R43" t="n">
-        <v>7014995</v>
+        <v>7015026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4910,10 +4910,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137814</v>
+        <v>129137909</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4921,21 +4921,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548376</v>
+        <v>548610</v>
       </c>
       <c r="R44" t="n">
-        <v>7015053</v>
+        <v>7015229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137843</v>
+        <v>129137803</v>
       </c>
       <c r="B45" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5018,21 +5018,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548488</v>
+        <v>548467</v>
       </c>
       <c r="R45" t="n">
-        <v>7015296</v>
+        <v>7014995</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5104,32 +5104,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137909</v>
+        <v>129137783</v>
       </c>
       <c r="B46" t="n">
-        <v>82878</v>
+        <v>98724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548610</v>
+        <v>548595</v>
       </c>
       <c r="R46" t="n">
-        <v>7015229</v>
+        <v>7015162</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5175,6 +5175,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,32 +5206,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137822</v>
+        <v>129137891</v>
       </c>
       <c r="B47" t="n">
-        <v>57648</v>
+        <v>98724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5236,10 +5241,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548346</v>
+        <v>548627</v>
       </c>
       <c r="R47" t="n">
-        <v>7015026</v>
+        <v>7015253</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5272,6 +5277,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5400,10 +5410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137792</v>
+        <v>129137766</v>
       </c>
       <c r="B49" t="n">
-        <v>105790</v>
+        <v>97601</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5411,21 +5421,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5435,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548368</v>
+        <v>548366</v>
       </c>
       <c r="R49" t="n">
-        <v>7014860</v>
+        <v>7014942</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5475,7 +5485,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5502,32 +5512,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137783</v>
+        <v>129137792</v>
       </c>
       <c r="B50" t="n">
-        <v>98724</v>
+        <v>105790</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5537,10 +5547,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548595</v>
+        <v>548368</v>
       </c>
       <c r="R50" t="n">
-        <v>7015162</v>
+        <v>7014860</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5577,7 +5587,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>160 stycken ca möjlitvis mer.</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5604,32 +5614,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B51" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5639,10 +5649,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R51" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,11 +5685,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5706,32 +5711,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137766</v>
+        <v>129137814</v>
       </c>
       <c r="B52" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548366</v>
+        <v>548376</v>
       </c>
       <c r="R52" t="n">
-        <v>7014942</v>
+        <v>7015053</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,11 +5782,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137860</v>
+        <v>129137845</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548481</v>
+        <v>548531</v>
       </c>
       <c r="R53" t="n">
-        <v>7015172</v>
+        <v>7014817</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5910,10 +5910,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137859</v>
+        <v>129137746</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5921,21 +5921,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548434</v>
+        <v>548355</v>
       </c>
       <c r="R54" t="n">
-        <v>7014792</v>
+        <v>7014874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Lockläte/ övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6012,32 +6012,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137905</v>
+        <v>129137877</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548618</v>
+        <v>548334</v>
       </c>
       <c r="R55" t="n">
-        <v>7015116</v>
+        <v>7015001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6109,10 +6109,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129126001</v>
+        <v>129137882</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6120,21 +6120,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548299</v>
+        <v>548510</v>
       </c>
       <c r="R56" t="n">
-        <v>7014876</v>
+        <v>7015191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137739</v>
+        <v>129137905</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6217,21 +6217,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548460</v>
+        <v>548618</v>
       </c>
       <c r="R57" t="n">
-        <v>7014976</v>
+        <v>7015116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6277,11 +6277,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6308,10 +6303,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137845</v>
+        <v>129126001</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6319,21 +6314,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6343,10 +6338,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548531</v>
+        <v>548299</v>
       </c>
       <c r="R58" t="n">
-        <v>7014817</v>
+        <v>7014876</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6379,11 +6374,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6410,7 +6400,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137746</v>
+        <v>129137739</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6445,10 +6435,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548355</v>
+        <v>548460</v>
       </c>
       <c r="R59" t="n">
-        <v>7014874</v>
+        <v>7014976</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6485,7 +6475,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6512,32 +6502,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137877</v>
+        <v>129137860</v>
       </c>
       <c r="B60" t="n">
-        <v>80177</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6547,10 +6537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548334</v>
+        <v>548481</v>
       </c>
       <c r="R60" t="n">
-        <v>7015001</v>
+        <v>7015172</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6583,6 +6573,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6609,10 +6604,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137882</v>
+        <v>129137859</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6620,21 +6615,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6644,10 +6639,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548510</v>
+        <v>548434</v>
       </c>
       <c r="R61" t="n">
-        <v>7015191</v>
+        <v>7014792</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,6 +6675,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6706,10 +6706,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137910</v>
+        <v>129137769</v>
       </c>
       <c r="B62" t="n">
-        <v>92832</v>
+        <v>80177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548510</v>
+        <v>548487</v>
       </c>
       <c r="R62" t="n">
-        <v>7014986</v>
+        <v>7015073</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6803,7 +6803,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137769</v>
+        <v>129137875</v>
       </c>
       <c r="B63" t="n">
         <v>80177</v>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548487</v>
+        <v>548581</v>
       </c>
       <c r="R63" t="n">
-        <v>7015073</v>
+        <v>7015017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137875</v>
+        <v>129137910</v>
       </c>
       <c r="B64" t="n">
-        <v>80177</v>
+        <v>92832</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548581</v>
+        <v>548510</v>
       </c>
       <c r="R64" t="n">
-        <v>7015017</v>
+        <v>7014986</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7099,32 +7099,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137811</v>
+        <v>129137890</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548458</v>
+        <v>548594</v>
       </c>
       <c r="R66" t="n">
-        <v>7015205</v>
+        <v>7015211</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7170,6 +7170,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7196,32 +7201,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137857</v>
+        <v>129137791</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>105790</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7231,10 +7236,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548502</v>
+        <v>548452</v>
       </c>
       <c r="R67" t="n">
-        <v>7015176</v>
+        <v>7014769</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7267,11 +7272,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7298,32 +7298,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137858</v>
+        <v>129137857</v>
       </c>
       <c r="B68" t="n">
-        <v>56917</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7333,10 +7333,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548400</v>
+        <v>548502</v>
       </c>
       <c r="R68" t="n">
-        <v>7015152</v>
+        <v>7015176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>1 ex, förbiflygande</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7400,32 +7400,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137890</v>
+        <v>129137858</v>
       </c>
       <c r="B69" t="n">
-        <v>98724</v>
+        <v>56917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548594</v>
+        <v>548400</v>
       </c>
       <c r="R69" t="n">
-        <v>7015211</v>
+        <v>7015152</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7502,10 +7502,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137791</v>
+        <v>129137762</v>
       </c>
       <c r="B70" t="n">
-        <v>105790</v>
+        <v>97601</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7513,21 +7513,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548452</v>
+        <v>548603</v>
       </c>
       <c r="R70" t="n">
-        <v>7014769</v>
+        <v>7014709</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7599,32 +7599,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137762</v>
+        <v>129137811</v>
       </c>
       <c r="B71" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548603</v>
+        <v>548458</v>
       </c>
       <c r="R71" t="n">
-        <v>7014709</v>
+        <v>7015205</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7696,10 +7696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137850</v>
+        <v>129137902</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,23 +7707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7731,10 +7727,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548629</v>
+        <v>548480</v>
       </c>
       <c r="R72" t="n">
-        <v>7015262</v>
+        <v>7015285</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7767,11 +7763,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7798,10 +7789,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129137773</v>
+        <v>129137748</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7809,21 +7800,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7833,10 +7824,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548717</v>
+        <v>548710</v>
       </c>
       <c r="R73" t="n">
-        <v>7014991</v>
+        <v>7014904</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7869,6 +7860,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>2 övriga läten</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7895,32 +7891,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137886</v>
+        <v>129137780</v>
       </c>
       <c r="B74" t="n">
-        <v>80185</v>
+        <v>98724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7930,10 +7926,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548498</v>
+        <v>548594</v>
       </c>
       <c r="R74" t="n">
-        <v>7015173</v>
+        <v>7015114</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7966,6 +7962,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7992,32 +7993,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129137780</v>
+        <v>129137773</v>
       </c>
       <c r="B75" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8027,10 +8028,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548594</v>
+        <v>548717</v>
       </c>
       <c r="R75" t="n">
-        <v>7015114</v>
+        <v>7014991</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8063,11 +8064,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8094,30 +8090,34 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129137902</v>
+        <v>129137886</v>
       </c>
       <c r="B76" t="n">
-        <v>91570</v>
+        <v>80185</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548480</v>
+        <v>548498</v>
       </c>
       <c r="R76" t="n">
-        <v>7015285</v>
+        <v>7015173</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129137748</v>
+        <v>129137850</v>
       </c>
       <c r="B77" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8198,21 +8198,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548710</v>
+        <v>548629</v>
       </c>
       <c r="R77" t="n">
-        <v>7014904</v>
+        <v>7015262</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>2 övriga läten</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8289,32 +8289,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137813</v>
+        <v>129137759</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548374</v>
+        <v>548487</v>
       </c>
       <c r="R78" t="n">
-        <v>7015064</v>
+        <v>7014855</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8386,32 +8386,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137818</v>
+        <v>129137779</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548329</v>
+        <v>548620</v>
       </c>
       <c r="R79" t="n">
-        <v>7014932</v>
+        <v>7014685</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8457,6 +8457,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8483,32 +8488,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B80" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R80" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8585,32 +8585,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137759</v>
+        <v>129137813</v>
       </c>
       <c r="B81" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8620,10 +8620,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548487</v>
+        <v>548374</v>
       </c>
       <c r="R81" t="n">
-        <v>7014855</v>
+        <v>7015064</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8682,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137871</v>
+        <v>129137816</v>
       </c>
       <c r="B82" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548457</v>
+        <v>548400</v>
       </c>
       <c r="R82" t="n">
-        <v>7014764</v>
+        <v>7014970</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8779,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137872</v>
+        <v>129137745</v>
       </c>
       <c r="B83" t="n">
-        <v>97601</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548477</v>
+        <v>548373</v>
       </c>
       <c r="R83" t="n">
-        <v>7015144</v>
+        <v>7014966</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,6 +8850,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,32 +8881,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137805</v>
+        <v>129137871</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8916,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548613</v>
+        <v>548457</v>
       </c>
       <c r="R84" t="n">
-        <v>7015186</v>
+        <v>7014764</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8973,32 +8978,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137796</v>
+        <v>129137872</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9008,10 +9013,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548559</v>
+        <v>548477</v>
       </c>
       <c r="R85" t="n">
-        <v>7014776</v>
+        <v>7015144</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9070,7 +9075,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137816</v>
+        <v>129137805</v>
       </c>
       <c r="B86" t="n">
         <v>79044</v>
@@ -9105,10 +9110,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548400</v>
+        <v>548613</v>
       </c>
       <c r="R86" t="n">
-        <v>7014970</v>
+        <v>7015186</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9167,10 +9172,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137745</v>
+        <v>129137796</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9178,21 +9183,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9202,10 +9207,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548373</v>
+        <v>548559</v>
       </c>
       <c r="R87" t="n">
-        <v>7014966</v>
+        <v>7014776</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9238,11 +9243,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9570,32 +9570,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129137878</v>
+        <v>129137778</v>
       </c>
       <c r="B91" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548705</v>
+        <v>548706</v>
       </c>
       <c r="R91" t="n">
-        <v>7014750</v>
+        <v>7014864</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9641,6 +9641,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9667,32 +9672,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129137778</v>
+        <v>129137878</v>
       </c>
       <c r="B92" t="n">
-        <v>57831</v>
+        <v>80149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9702,10 +9707,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548706</v>
+        <v>548705</v>
       </c>
       <c r="R92" t="n">
-        <v>7014864</v>
+        <v>7014750</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9738,11 +9743,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>3 stycken, två längre bort. En nyfiken på mig kom närmre.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9769,10 +9769,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129137790</v>
+        <v>129137764</v>
       </c>
       <c r="B93" t="n">
-        <v>105790</v>
+        <v>97601</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9780,21 +9780,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548558</v>
+        <v>548590</v>
       </c>
       <c r="R93" t="n">
-        <v>7014771</v>
+        <v>7015157</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9963,10 +9963,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129137764</v>
+        <v>129137790</v>
       </c>
       <c r="B95" t="n">
-        <v>97601</v>
+        <v>105790</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9974,21 +9974,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9998,10 +9998,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548590</v>
+        <v>548558</v>
       </c>
       <c r="R95" t="n">
-        <v>7015157</v>
+        <v>7014771</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10060,27 +10060,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129137908</v>
+        <v>129137911</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548306</v>
+        <v>548512</v>
       </c>
       <c r="R96" t="n">
-        <v>7015082</v>
+        <v>7015192</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10157,27 +10157,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129137911</v>
+        <v>129137908</v>
       </c>
       <c r="B97" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10192,10 +10192,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548512</v>
+        <v>548306</v>
       </c>
       <c r="R97" t="n">
-        <v>7015192</v>
+        <v>7015082</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10254,10 +10254,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129137848</v>
+        <v>129137903</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548598</v>
+        <v>548633</v>
       </c>
       <c r="R98" t="n">
-        <v>7015227</v>
+        <v>7015045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10325,11 +10325,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10356,32 +10351,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129137912</v>
+        <v>129137848</v>
       </c>
       <c r="B99" t="n">
-        <v>96843</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10391,10 +10386,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548604</v>
+        <v>548598</v>
       </c>
       <c r="R99" t="n">
-        <v>7015234</v>
+        <v>7015227</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10427,6 +10422,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10453,32 +10453,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129137863</v>
+        <v>129137788</v>
       </c>
       <c r="B100" t="n">
-        <v>80150</v>
+        <v>98724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548702</v>
+        <v>548605</v>
       </c>
       <c r="R100" t="n">
-        <v>7014752</v>
+        <v>7014687</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10524,6 +10524,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10550,32 +10555,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129137903</v>
+        <v>129137874</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10585,10 +10590,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548633</v>
+        <v>548348</v>
       </c>
       <c r="R101" t="n">
-        <v>7015045</v>
+        <v>7014988</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10647,32 +10652,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129137788</v>
+        <v>129137912</v>
       </c>
       <c r="B102" t="n">
-        <v>98724</v>
+        <v>96843</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10682,10 +10687,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548605</v>
+        <v>548604</v>
       </c>
       <c r="R102" t="n">
-        <v>7014687</v>
+        <v>7015234</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10718,11 +10723,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10749,32 +10749,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129137874</v>
+        <v>129137863</v>
       </c>
       <c r="B103" t="n">
-        <v>97601</v>
+        <v>80150</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548348</v>
+        <v>548702</v>
       </c>
       <c r="R103" t="n">
-        <v>7014988</v>
+        <v>7014752</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10846,32 +10846,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137758</v>
+        <v>129137883</v>
       </c>
       <c r="B104" t="n">
-        <v>97595</v>
+        <v>80149</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548629</v>
+        <v>548499</v>
       </c>
       <c r="R104" t="n">
-        <v>7014777</v>
+        <v>7015176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10943,32 +10943,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137840</v>
+        <v>129137758</v>
       </c>
       <c r="B105" t="n">
-        <v>91550</v>
+        <v>97595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548660</v>
+        <v>548629</v>
       </c>
       <c r="R105" t="n">
-        <v>7014820</v>
+        <v>7014777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11040,10 +11040,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137753</v>
+        <v>129137840</v>
       </c>
       <c r="B106" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11051,21 +11051,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11075,10 +11075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548681</v>
+        <v>548660</v>
       </c>
       <c r="R106" t="n">
-        <v>7015193</v>
+        <v>7014820</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11137,10 +11137,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137883</v>
+        <v>129137753</v>
       </c>
       <c r="B107" t="n">
-        <v>80149</v>
+        <v>91848</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11148,21 +11148,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548499</v>
+        <v>548681</v>
       </c>
       <c r="R107" t="n">
-        <v>7015176</v>
+        <v>7015193</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137740</v>
+        <v>129137817</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548618</v>
+        <v>548367</v>
       </c>
       <c r="R6" t="n">
-        <v>7015211</v>
+        <v>7014944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,11 +1215,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137751</v>
+        <v>129137797</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548268</v>
+        <v>548657</v>
       </c>
       <c r="R7" t="n">
-        <v>7014891</v>
+        <v>7014768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,11 +1312,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,32 +1338,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137870</v>
+        <v>129137815</v>
       </c>
       <c r="B8" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548358</v>
+        <v>548398</v>
       </c>
       <c r="R8" t="n">
-        <v>7014777</v>
+        <v>7015004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,6 +1409,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,32 +1440,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137787</v>
+        <v>129137751</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548366</v>
+        <v>548268</v>
       </c>
       <c r="R9" t="n">
-        <v>7014942</v>
+        <v>7014891</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137817</v>
+        <v>129137787</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1582,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548367</v>
+        <v>548366</v>
       </c>
       <c r="R10" t="n">
-        <v>7014944</v>
+        <v>7014942</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137797</v>
+        <v>129137870</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548657</v>
+        <v>548358</v>
       </c>
       <c r="R11" t="n">
-        <v>7014768</v>
+        <v>7014777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137815</v>
+        <v>129137740</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548398</v>
+        <v>548618</v>
       </c>
       <c r="R12" t="n">
-        <v>7015004</v>
+        <v>7015211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137802</v>
+        <v>129137820</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548499</v>
+        <v>548328</v>
       </c>
       <c r="R17" t="n">
-        <v>7014902</v>
+        <v>7014882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,6 +2308,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,7 +2339,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137820</v>
+        <v>129137801</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548328</v>
+        <v>548686</v>
       </c>
       <c r="R18" t="n">
-        <v>7014882</v>
+        <v>7014817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,7 +2436,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137801</v>
+        <v>129137802</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548686</v>
+        <v>548499</v>
       </c>
       <c r="R19" t="n">
-        <v>7014817</v>
+        <v>7014902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137906</v>
+        <v>129137744</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548693</v>
+        <v>548511</v>
       </c>
       <c r="R21" t="n">
-        <v>7014874</v>
+        <v>7015241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,6 +2701,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2727,32 +2732,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137819</v>
+        <v>129137771</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548318</v>
+        <v>548360</v>
       </c>
       <c r="R22" t="n">
-        <v>7014904</v>
+        <v>7014942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2824,32 +2829,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137744</v>
+        <v>129137862</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548511</v>
+        <v>548497</v>
       </c>
       <c r="R23" t="n">
-        <v>7015241</v>
+        <v>7015181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2895,11 +2900,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137771</v>
+        <v>129137906</v>
       </c>
       <c r="B24" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548360</v>
+        <v>548693</v>
       </c>
       <c r="R24" t="n">
-        <v>7014942</v>
+        <v>7014874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137862</v>
+        <v>129137819</v>
       </c>
       <c r="B25" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548497</v>
+        <v>548318</v>
       </c>
       <c r="R25" t="n">
-        <v>7015181</v>
+        <v>7014904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,32 +3222,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137749</v>
+        <v>129137876</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>80177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548618</v>
+        <v>548475</v>
       </c>
       <c r="R27" t="n">
-        <v>7015211</v>
+        <v>7015265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3293,11 +3293,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3324,32 +3319,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137876</v>
+        <v>129137810</v>
       </c>
       <c r="B28" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548475</v>
+        <v>548538</v>
       </c>
       <c r="R28" t="n">
-        <v>7015265</v>
+        <v>7015259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,7 +3416,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137810</v>
+        <v>129137806</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3456,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548538</v>
+        <v>548632</v>
       </c>
       <c r="R29" t="n">
-        <v>7015259</v>
+        <v>7015246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,32 +3513,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137806</v>
+        <v>129125929</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548632</v>
+        <v>548372</v>
       </c>
       <c r="R30" t="n">
-        <v>7015246</v>
+        <v>7014829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,32 +3610,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129125929</v>
+        <v>129137749</v>
       </c>
       <c r="B31" t="n">
-        <v>97595</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548372</v>
+        <v>548618</v>
       </c>
       <c r="R31" t="n">
-        <v>7014829</v>
+        <v>7015211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3686,6 +3681,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3712,32 +3712,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137789</v>
+        <v>129137800</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548461</v>
+        <v>548708</v>
       </c>
       <c r="R32" t="n">
-        <v>7015210</v>
+        <v>7014937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,32 +3814,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137896</v>
+        <v>129137821</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548260</v>
+        <v>548369</v>
       </c>
       <c r="R33" t="n">
-        <v>7014898</v>
+        <v>7014853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3916,49 +3911,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129126213</v>
+        <v>129137849</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548265</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7014876</v>
+        <v>7015247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3991,6 +3982,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,32 +4013,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137800</v>
+        <v>129137789</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4052,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548708</v>
+        <v>548461</v>
       </c>
       <c r="R35" t="n">
-        <v>7014937</v>
+        <v>7015210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,7 +4088,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4119,32 +4115,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137821</v>
+        <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4154,10 +4150,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548369</v>
+        <v>548260</v>
       </c>
       <c r="R36" t="n">
-        <v>7014853</v>
+        <v>7014898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,6 +4186,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4216,45 +4217,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137849</v>
+        <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548629</v>
+        <v>548265</v>
       </c>
       <c r="R37" t="n">
-        <v>7015247</v>
+        <v>7014876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4287,11 +4292,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,10 +4512,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137846</v>
+        <v>129137812</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548317</v>
+        <v>548395</v>
       </c>
       <c r="R40" t="n">
-        <v>7014833</v>
+        <v>7015086</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4583,11 +4583,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4614,32 +4609,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137895</v>
+        <v>129137846</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548277</v>
+        <v>548317</v>
       </c>
       <c r="R41" t="n">
-        <v>7015126</v>
+        <v>7014833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,7 +4684,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4716,32 +4711,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137812</v>
+        <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4751,10 +4746,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548395</v>
+        <v>548277</v>
       </c>
       <c r="R42" t="n">
-        <v>7015086</v>
+        <v>7015126</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,6 +4782,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4813,10 +4813,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137822</v>
+        <v>129137909</v>
       </c>
       <c r="B43" t="n">
-        <v>57648</v>
+        <v>82878</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100001</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548346</v>
+        <v>548610</v>
       </c>
       <c r="R43" t="n">
-        <v>7015026</v>
+        <v>7015229</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4910,10 +4910,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137909</v>
+        <v>129137803</v>
       </c>
       <c r="B44" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4921,21 +4921,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548610</v>
+        <v>548467</v>
       </c>
       <c r="R44" t="n">
-        <v>7015229</v>
+        <v>7014995</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5007,7 +5007,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137803</v>
+        <v>129137814</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548467</v>
+        <v>548376</v>
       </c>
       <c r="R45" t="n">
-        <v>7014995</v>
+        <v>7015053</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5711,10 +5711,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137814</v>
+        <v>129137822</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57648</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548376</v>
+        <v>548346</v>
       </c>
       <c r="R52" t="n">
-        <v>7015053</v>
+        <v>7015026</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5808,32 +5808,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137845</v>
+        <v>129137877</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548531</v>
+        <v>548334</v>
       </c>
       <c r="R53" t="n">
-        <v>7014817</v>
+        <v>7015001</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,11 +5879,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5910,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137746</v>
+        <v>129137905</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5921,21 +5916,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548355</v>
+        <v>548618</v>
       </c>
       <c r="R54" t="n">
-        <v>7014874</v>
+        <v>7015116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5981,11 +5976,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6012,32 +6002,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129137877</v>
+        <v>129126001</v>
       </c>
       <c r="B55" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6047,10 +6037,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548334</v>
+        <v>548299</v>
       </c>
       <c r="R55" t="n">
-        <v>7015001</v>
+        <v>7014876</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6109,10 +6099,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137882</v>
+        <v>129137739</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6120,21 +6110,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6144,10 +6134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548510</v>
+        <v>548460</v>
       </c>
       <c r="R56" t="n">
-        <v>7015191</v>
+        <v>7014976</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6180,6 +6170,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6206,10 +6201,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137905</v>
+        <v>129137845</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6217,21 +6212,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6241,10 +6236,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548618</v>
+        <v>548531</v>
       </c>
       <c r="R57" t="n">
-        <v>7015116</v>
+        <v>7014817</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6277,6 +6272,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6303,10 +6303,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129126001</v>
+        <v>129137746</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6314,21 +6314,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548299</v>
+        <v>548355</v>
       </c>
       <c r="R58" t="n">
-        <v>7014876</v>
+        <v>7014874</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6374,6 +6374,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6400,10 +6405,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137739</v>
+        <v>129137860</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6411,21 +6416,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6435,10 +6440,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548460</v>
+        <v>548481</v>
       </c>
       <c r="R59" t="n">
-        <v>7014976</v>
+        <v>7015172</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6475,7 +6480,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6502,7 +6507,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137860</v>
+        <v>129137859</v>
       </c>
       <c r="B60" t="n">
         <v>57887</v>
@@ -6537,10 +6542,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548481</v>
+        <v>548434</v>
       </c>
       <c r="R60" t="n">
-        <v>7015172</v>
+        <v>7014792</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6577,7 +6582,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6604,10 +6609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137859</v>
+        <v>129137882</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,21 +6620,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6639,10 +6644,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548434</v>
+        <v>548510</v>
       </c>
       <c r="R61" t="n">
-        <v>7014792</v>
+        <v>7015191</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6675,11 +6680,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8386,32 +8386,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137779</v>
+        <v>129137818</v>
       </c>
       <c r="B79" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548620</v>
+        <v>548329</v>
       </c>
       <c r="R79" t="n">
-        <v>7014685</v>
+        <v>7014932</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8457,11 +8457,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8488,32 +8483,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137818</v>
+        <v>129137779</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548329</v>
+        <v>548620</v>
       </c>
       <c r="R80" t="n">
-        <v>7014932</v>
+        <v>7014685</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8559,6 +8554,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8682,7 +8682,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129137816</v>
+        <v>129137805</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548400</v>
+        <v>548613</v>
       </c>
       <c r="R82" t="n">
-        <v>7014970</v>
+        <v>7015186</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8779,10 +8779,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129137745</v>
+        <v>129137796</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548373</v>
+        <v>548559</v>
       </c>
       <c r="R83" t="n">
-        <v>7014966</v>
+        <v>7014776</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,11 +8850,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8881,32 +8876,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129137871</v>
+        <v>129137816</v>
       </c>
       <c r="B84" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8916,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548457</v>
+        <v>548400</v>
       </c>
       <c r="R84" t="n">
-        <v>7014764</v>
+        <v>7014970</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8978,32 +8973,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129137872</v>
+        <v>129137781</v>
       </c>
       <c r="B85" t="n">
-        <v>97601</v>
+        <v>98724</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9013,10 +9008,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548477</v>
+        <v>548433</v>
       </c>
       <c r="R85" t="n">
-        <v>7015144</v>
+        <v>7014771</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9049,6 +9044,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>11 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9075,32 +9075,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129137805</v>
+        <v>129137871</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548613</v>
+        <v>548457</v>
       </c>
       <c r="R86" t="n">
-        <v>7015186</v>
+        <v>7014764</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9172,32 +9172,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129137796</v>
+        <v>129137872</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548559</v>
+        <v>548477</v>
       </c>
       <c r="R87" t="n">
-        <v>7014776</v>
+        <v>7015144</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9269,32 +9269,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129137781</v>
+        <v>129137745</v>
       </c>
       <c r="B88" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9304,10 +9304,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548433</v>
+        <v>548373</v>
       </c>
       <c r="R88" t="n">
-        <v>7014771</v>
+        <v>7014966</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>11 stycken kan finnas mer I mossan</t>
+          <t>Ringhack av tretåig hackspett på gran ( äldre exemplar) visar på lång användning av området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10846,10 +10846,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129137883</v>
+        <v>129137840</v>
       </c>
       <c r="B104" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548499</v>
+        <v>548660</v>
       </c>
       <c r="R104" t="n">
-        <v>7015176</v>
+        <v>7014820</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10943,32 +10943,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129137758</v>
+        <v>129137753</v>
       </c>
       <c r="B105" t="n">
-        <v>97595</v>
+        <v>91848</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548629</v>
+        <v>548681</v>
       </c>
       <c r="R105" t="n">
-        <v>7014777</v>
+        <v>7015193</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11040,10 +11040,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129137840</v>
+        <v>129137883</v>
       </c>
       <c r="B106" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11051,21 +11051,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11075,10 +11075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548660</v>
+        <v>548499</v>
       </c>
       <c r="R106" t="n">
-        <v>7014820</v>
+        <v>7015176</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11137,32 +11137,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129137753</v>
+        <v>129137758</v>
       </c>
       <c r="B107" t="n">
-        <v>91848</v>
+        <v>97595</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548681</v>
+        <v>548629</v>
       </c>
       <c r="R107" t="n">
-        <v>7015193</v>
+        <v>7014777</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 41877-2025 artfynd.xlsx
+++ b/artfynd/A 41877-2025 artfynd.xlsx
@@ -1144,7 +1144,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137817</v>
+        <v>129137797</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548367</v>
+        <v>548657</v>
       </c>
       <c r="R6" t="n">
-        <v>7014944</v>
+        <v>7014768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137797</v>
+        <v>129137740</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548657</v>
+        <v>548618</v>
       </c>
       <c r="R7" t="n">
-        <v>7014768</v>
+        <v>7015211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,6 +1312,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137815</v>
+        <v>129137751</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548398</v>
+        <v>548268</v>
       </c>
       <c r="R8" t="n">
-        <v>7015004</v>
+        <v>7014891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1418,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137751</v>
+        <v>129137817</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548268</v>
+        <v>548367</v>
       </c>
       <c r="R9" t="n">
-        <v>7014891</v>
+        <v>7014944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,11 +1516,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 individer upprörda läten ( övriga läten ) och nyfikna på oss. Sågs i träden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,32 +1542,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137787</v>
+        <v>129137815</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548366</v>
+        <v>548398</v>
       </c>
       <c r="R10" t="n">
-        <v>7014942</v>
+        <v>7015004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,7 +1647,7 @@
         <v>129137870</v>
       </c>
       <c r="B11" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129137740</v>
+        <v>129137787</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548618</v>
+        <v>548366</v>
       </c>
       <c r="R12" t="n">
-        <v>7015211</v>
+        <v>7014942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre exemplar</t>
+          <t>60 exemplar kan möjlitvis finnas fler I mossan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129137795</v>
+        <v>129137794</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,23 +1854,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1878,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548538</v>
+        <v>548459</v>
       </c>
       <c r="R13" t="n">
-        <v>7014770</v>
+        <v>7015186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,11 +1910,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,7 +1936,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137804</v>
+        <v>129137795</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1980,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548550</v>
+        <v>548538</v>
       </c>
       <c r="R14" t="n">
-        <v>7015142</v>
+        <v>7014770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,6 +2007,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2038,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137794</v>
+        <v>129137804</v>
       </c>
       <c r="B15" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,19 +2049,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548459</v>
+        <v>548550</v>
       </c>
       <c r="R15" t="n">
-        <v>7015186</v>
+        <v>7015142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137820</v>
+        <v>129137869</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>97604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548328</v>
+        <v>548335</v>
       </c>
       <c r="R17" t="n">
-        <v>7014882</v>
+        <v>7014782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,11 +2308,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,7 +2334,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137801</v>
+        <v>129137820</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548686</v>
+        <v>548328</v>
       </c>
       <c r="R18" t="n">
-        <v>7014817</v>
+        <v>7014882</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,6 +2405,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,32 +2533,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137869</v>
+        <v>129137801</v>
       </c>
       <c r="B20" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548335</v>
+        <v>548686</v>
       </c>
       <c r="R20" t="n">
-        <v>7014782</v>
+        <v>7014817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137744</v>
+        <v>129137906</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548511</v>
+        <v>548693</v>
       </c>
       <c r="R21" t="n">
-        <v>7015241</v>
+        <v>7014874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,11 +2701,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2732,32 +2727,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137771</v>
+        <v>129137819</v>
       </c>
       <c r="B22" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2767,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548360</v>
+        <v>548318</v>
       </c>
       <c r="R22" t="n">
-        <v>7014942</v>
+        <v>7014904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,32 +2824,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137862</v>
+        <v>129137750</v>
       </c>
       <c r="B23" t="n">
-        <v>80178</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548497</v>
+        <v>548514</v>
       </c>
       <c r="R23" t="n">
-        <v>7015181</v>
+        <v>7015227</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,6 +2895,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137906</v>
+        <v>129137771</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548693</v>
+        <v>548360</v>
       </c>
       <c r="R24" t="n">
-        <v>7014874</v>
+        <v>7014942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137819</v>
+        <v>129137862</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548318</v>
+        <v>548497</v>
       </c>
       <c r="R25" t="n">
-        <v>7014904</v>
+        <v>7015181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137750</v>
+        <v>129137744</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548514</v>
+        <v>548511</v>
       </c>
       <c r="R26" t="n">
-        <v>7015227</v>
+        <v>7015241</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Äldre ringhack och färska på samma träd av tretåig hackspett på gran , visar att arten använt området under en längre tid och fortfarande använder området.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3222,32 +3222,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137876</v>
+        <v>129137749</v>
       </c>
       <c r="B27" t="n">
-        <v>80177</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548475</v>
+        <v>548618</v>
       </c>
       <c r="R27" t="n">
-        <v>7015265</v>
+        <v>7015211</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3293,6 +3293,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3319,32 +3324,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137810</v>
+        <v>129137876</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3354,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548538</v>
+        <v>548475</v>
       </c>
       <c r="R28" t="n">
-        <v>7015259</v>
+        <v>7015265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,7 +3421,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137806</v>
+        <v>129137810</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3451,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548632</v>
+        <v>548538</v>
       </c>
       <c r="R29" t="n">
-        <v>7015246</v>
+        <v>7015259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,32 +3518,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129125929</v>
+        <v>129137806</v>
       </c>
       <c r="B30" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548372</v>
+        <v>548632</v>
       </c>
       <c r="R30" t="n">
-        <v>7014829</v>
+        <v>7015246</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,32 +3615,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137749</v>
+        <v>129125929</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>97598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548618</v>
+        <v>548372</v>
       </c>
       <c r="R31" t="n">
-        <v>7015211</v>
+        <v>7014829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3681,11 +3686,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Läte ( övriga läten) 3 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4016,7 +4016,7 @@
         <v>129137789</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>129137896</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>129126213</v>
       </c>
       <c r="B37" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>129137895</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137909</v>
+        <v>129137814</v>
       </c>
       <c r="B43" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548610</v>
+        <v>548376</v>
       </c>
       <c r="R43" t="n">
-        <v>7015229</v>
+        <v>7015053</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137814</v>
+        <v>129137843</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5018,21 +5018,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548376</v>
+        <v>548488</v>
       </c>
       <c r="R45" t="n">
-        <v>7015053</v>
+        <v>7015296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5104,32 +5104,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137783</v>
+        <v>129137909</v>
       </c>
       <c r="B46" t="n">
-        <v>98724</v>
+        <v>82878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548595</v>
+        <v>548610</v>
       </c>
       <c r="R46" t="n">
-        <v>7015162</v>
+        <v>7015229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5175,11 +5175,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5206,32 +5201,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137891</v>
+        <v>129137822</v>
       </c>
       <c r="B47" t="n">
-        <v>98724</v>
+        <v>57648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5241,10 +5236,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548627</v>
+        <v>548346</v>
       </c>
       <c r="R47" t="n">
-        <v>7015253</v>
+        <v>7015026</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5277,11 +5272,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5308,32 +5298,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137786</v>
+        <v>129137766</v>
       </c>
       <c r="B48" t="n">
-        <v>98724</v>
+        <v>97604</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5343,10 +5333,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548402</v>
+        <v>548366</v>
       </c>
       <c r="R48" t="n">
-        <v>7015096</v>
+        <v>7014942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5383,7 +5373,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>15 stycken kan finnas mer I mossan</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5410,32 +5400,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137766</v>
+        <v>129137783</v>
       </c>
       <c r="B49" t="n">
-        <v>97601</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5445,10 +5435,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548366</v>
+        <v>548595</v>
       </c>
       <c r="R49" t="n">
-        <v>7014942</v>
+        <v>7015162</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5485,7 +5475,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>5 exemplar</t>
+          <t>160 stycken ca möjlitvis mer.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5512,32 +5502,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137792</v>
+        <v>129137891</v>
       </c>
       <c r="B50" t="n">
-        <v>105790</v>
+        <v>98727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5547,10 +5537,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548368</v>
+        <v>548627</v>
       </c>
       <c r="R50" t="n">
-        <v>7014860</v>
+        <v>7015253</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,7 +5577,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5614,32 +5604,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137843</v>
+        <v>129137792</v>
       </c>
       <c r="B51" t="n">
-        <v>91550</v>
+        <v>105793</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5649,10 +5639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548488</v>
+        <v>548368</v>
       </c>
       <c r="R51" t="n">
-        <v>7015296</v>
+        <v>7014860</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,6 +5675,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5711,32 +5706,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137822</v>
+        <v>129137786</v>
       </c>
       <c r="B52" t="n">
-        <v>57648</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5746,10 +5741,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548346</v>
+        <v>548402</v>
       </c>
       <c r="R52" t="n">
-        <v>7015026</v>
+        <v>7015096</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5782,6 +5777,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>15 stycken kan finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5905,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129137905</v>
+        <v>129137882</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,21 +5916,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548618</v>
+        <v>548510</v>
       </c>
       <c r="R54" t="n">
-        <v>7015116</v>
+        <v>7015191</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129126001</v>
+        <v>129137746</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6013,21 +6013,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548299</v>
+        <v>548355</v>
       </c>
       <c r="R55" t="n">
-        <v>7014876</v>
+        <v>7014874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6073,6 +6073,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6099,7 +6104,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129137739</v>
+        <v>129137845</v>
       </c>
       <c r="B56" t="n">
         <v>57727</v>
@@ -6134,10 +6139,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548460</v>
+        <v>548531</v>
       </c>
       <c r="R56" t="n">
-        <v>7014976</v>
+        <v>7014817</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6174,7 +6179,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6201,7 +6206,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129137845</v>
+        <v>129137739</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6236,10 +6241,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548531</v>
+        <v>548460</v>
       </c>
       <c r="R57" t="n">
-        <v>7014817</v>
+        <v>7014976</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6276,7 +6281,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack av tretåig hackspett på gran  ( äldre exemplar) tyder på att dom använt området under lång tid).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6303,10 +6308,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129137746</v>
+        <v>129137860</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6314,21 +6319,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6338,10 +6343,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548355</v>
+        <v>548481</v>
       </c>
       <c r="R58" t="n">
-        <v>7014874</v>
+        <v>7015172</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6378,7 +6383,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska spår</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6405,7 +6410,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129137860</v>
+        <v>129137859</v>
       </c>
       <c r="B59" t="n">
         <v>57887</v>
@@ -6440,10 +6445,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548481</v>
+        <v>548434</v>
       </c>
       <c r="R59" t="n">
-        <v>7015172</v>
+        <v>7014792</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6480,7 +6485,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6507,10 +6512,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129137859</v>
+        <v>129126001</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6518,21 +6523,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6542,10 +6547,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548434</v>
+        <v>548299</v>
       </c>
       <c r="R60" t="n">
-        <v>7014792</v>
+        <v>7014876</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6578,11 +6583,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Lockläte/ övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6609,10 +6609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129137882</v>
+        <v>129137905</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548510</v>
+        <v>548618</v>
       </c>
       <c r="R61" t="n">
-        <v>7015191</v>
+        <v>7015116</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129137769</v>
+        <v>129137910</v>
       </c>
       <c r="B62" t="n">
-        <v>80177</v>
+        <v>92835</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548487</v>
+        <v>548510</v>
       </c>
       <c r="R62" t="n">
-        <v>7015073</v>
+        <v>7014986</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6803,7 +6803,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129137875</v>
+        <v>129137769</v>
       </c>
       <c r="B63" t="n">
         <v>80177</v>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548581</v>
+        <v>548487</v>
       </c>
       <c r="R63" t="n">
-        <v>7015017</v>
+        <v>7015073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129137910</v>
+        <v>129137875</v>
       </c>
       <c r="B64" t="n">
-        <v>92832</v>
+        <v>80177</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548510</v>
+        <v>548581</v>
       </c>
       <c r="R64" t="n">
-        <v>7014986</v>
+        <v>7015017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7000,7 +7000,7 @@
         <v>129137782</v>
       </c>
       <c r="B65" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7099,32 +7099,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129137890</v>
+        <v>129137858</v>
       </c>
       <c r="B66" t="n">
-        <v>98724</v>
+        <v>56917</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548594</v>
+        <v>548400</v>
       </c>
       <c r="R66" t="n">
-        <v>7015211</v>
+        <v>7015152</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7201,32 +7201,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129137791</v>
+        <v>129137857</v>
       </c>
       <c r="B67" t="n">
-        <v>105790</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548452</v>
+        <v>548502</v>
       </c>
       <c r="R67" t="n">
-        <v>7014769</v>
+        <v>7015176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7272,6 +7272,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7298,10 +7303,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129137857</v>
+        <v>129137811</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7309,21 +7314,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7333,10 +7338,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548502</v>
+        <v>548458</v>
       </c>
       <c r="R68" t="n">
-        <v>7015176</v>
+        <v>7015205</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7369,11 +7374,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7400,10 +7400,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129137858</v>
+        <v>129137762</v>
       </c>
       <c r="B69" t="n">
-        <v>56917</v>
+        <v>97604</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7411,21 +7411,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548400</v>
+        <v>548603</v>
       </c>
       <c r="R69" t="n">
-        <v>7015152</v>
+        <v>7014709</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7471,11 +7471,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>1 ex, förbiflygande</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7502,32 +7497,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129137762</v>
+        <v>129137890</v>
       </c>
       <c r="B70" t="n">
-        <v>97601</v>
+        <v>98727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7537,10 +7532,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548603</v>
+        <v>548594</v>
       </c>
       <c r="R70" t="n">
-        <v>7014709</v>
+        <v>7015211</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7573,6 +7568,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7599,32 +7599,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129137811</v>
+        <v>129137791</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>105793</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548458</v>
+        <v>548452</v>
       </c>
       <c r="R71" t="n">
-        <v>7015205</v>
+        <v>7014769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7696,30 +7696,34 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129137902</v>
+        <v>129137780</v>
       </c>
       <c r="B72" t="n">
-        <v>91570</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7727,10 +7731,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548480</v>
+        <v>548594</v>
       </c>
       <c r="R72" t="n">
-        <v>7015285</v>
+        <v>7015114</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7763,6 +7767,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7891,34 +7900,30 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129137780</v>
+        <v>129137902</v>
       </c>
       <c r="B74" t="n">
-        <v>98724</v>
+        <v>91573</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -7926,10 +7931,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548594</v>
+        <v>548480</v>
       </c>
       <c r="R74" t="n">
-        <v>7015114</v>
+        <v>7015285</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7962,11 +7967,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8289,32 +8289,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129137759</v>
+        <v>129137818</v>
       </c>
       <c r="B78" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548487</v>
+        <v>548329</v>
       </c>
       <c r="R78" t="n">
-        <v>7014855</v>
+        <v>7014932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129137818</v>
+        <v>129137813</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548329</v>
+        <v>548374</v>
       </c>
       <c r="R79" t="n">
-        <v>7014932</v>
+        <v>7015064</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8483,32 +8483,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129137779</v>
+        <v>129137759</v>
       </c>
       <c r="B80" t="n">
-        <v>98724</v>
+        <v>97598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548620</v>
+        <v>548487</v>
       </c>
       <c r="R80" t="n">
-        <v>7014685</v>
+        <v>7014855</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8554,11 +8554,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8585,32 +8580,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129137813</v>
+        <v>129137779</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+  